--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +76,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -82,11 +94,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10269,7 +10287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10313,6 +10331,117 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2005_06_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2005_06_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2005_06_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2005_06_0141 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2005_06_0149 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0021</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2005_06_0021 'Baráž o Extraligu' (L15, parent=NODE_S2005_06_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0028</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2005_06_0028 'Baráž o I.ligu' (L15, parent=NODE_S2005_06_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0042</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2005_06_0042 'O postup do I.ligy' (L25, parent=NODE_S2005_06_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -13673,8 +13802,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -13754,7 +13881,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -27242,6 +27368,237 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0029</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0030</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0031</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0141</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0141 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0149</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0149 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0021</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2005_06_0021 'Baráž o Extraligu' (L15, parent=NODE_S2005_06_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0028</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2005_06_0028 'Baráž o I.ligu' (L15, parent=NODE_S2005_06_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0042</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2005_06_0042 'O postup do I.ligy' (L25, parent=NODE_S2005_06_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10287,7 +10287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10337,7 +10337,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2005_06_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -10349,7 +10349,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2005_06_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10361,7 +10361,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2005_06_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10373,7 +10373,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2005_06_0141 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10385,7 +10385,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2005_06_0149 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10395,14 +10395,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S2005_06_0021</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2005_06_0021 'Baráž o Extraligu' (L15, parent=NODE_S2005_06_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10412,14 +10407,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S2005_06_0028</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2005_06_0028 'Baráž o I.ligu' (L15, parent=NODE_S2005_06_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -10429,17 +10419,168 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NODE_S2005_06_0042</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2005_06_0042 'O postup do I.ligy' (L25, parent=NODE_S2005_06_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chotěboř' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -13802,6 +13943,8 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
+    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -13832,6 +13975,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0001</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -13844,6 +13992,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0003</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -13856,6 +14009,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0003</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13868,6 +14026,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0036</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13881,6 +14044,7 @@
         </is>
       </c>
     </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -17384,12 +17548,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -17431,12 +17595,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -17814,12 +17978,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -17940,12 +18104,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -17982,12 +18146,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -18286,12 +18450,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -18370,12 +18534,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -18523,12 +18687,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>B-tým Spartak Chotěboř (CLUB_S1953_54_0316). Přejmenováno II → B (D21). prev na 52/53 0263 (A-tým, B 52/53 neexistoval). || Chotěboř = Spartak Chotěboř (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Havlíčkův Brod). S-P = Semily-Pardubice. city Chotěboř.</t>
+          <t>B-tým Spartak Chotěboř (CLUB_S1953_54_0316). Přejmenováno II → B (D21). prev na 52/53 0263 (A-tým, B 52/53 neexistoval). || Chotěboř = Spartak Chotěboř (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Havlíčkův Brod). S-P = Semily-Pardubice. city Chotěboř. || TBD: city 'Chotěboř' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Chotěboř</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -19202,12 +19366,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -19375,12 +19539,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -21636,12 +21800,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -22009,12 +22173,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -22728,12 +22892,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -23877,12 +24041,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou.</t>
+          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou. || TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>SB Světlá nad Sázavou</t>
+          <t>Světlá nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -24507,12 +24671,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -24759,12 +24923,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno.</t>
+          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno. || TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>HLC Bulldogs Brno</t>
+          <t>Bulldogs Brno</t>
         </is>
       </c>
     </row>
@@ -27374,11 +27538,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -27423,21 +27587,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0029</t>
+          <t>CLUB_S2005_06_0007</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -27445,21 +27607,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0030</t>
+          <t>CLUB_S2005_06_0008</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -27467,21 +27627,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0031</t>
+          <t>CLUB_S2005_06_0017</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -27489,21 +27647,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0141</t>
+          <t>CLUB_S2005_06_0020</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0141 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -27511,21 +27667,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0149</t>
+          <t>CLUB_S2005_06_0021</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0149 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -27533,21 +27687,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S2005_06_0021</t>
+          <t>CLUB_S2005_06_0028</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2005_06_0021 'Baráž o Extraligu' (L15, parent=NODE_S2005_06_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -27555,21 +27707,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NODE_S2005_06_0028</t>
+          <t>CLUB_S2005_06_0030</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2005_06_0028 'Baráž o I.ligu' (L15, parent=NODE_S2005_06_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -27577,24 +27727,282 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NODE_S2005_06_0042</t>
+          <t>CLUB_S2005_06_0036</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2005_06_0042 'O postup do I.ligy' (L25, parent=NODE_S2005_06_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: city 'Chotěboř' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0058</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0062</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0069</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0118</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0118</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0127</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0145</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0157</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0168</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0173</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0192</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0196</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0198</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10287,7 +10287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10349,7 +10349,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10361,7 +10361,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10373,7 +10373,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10385,7 +10385,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10397,7 +10397,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10409,7 +10409,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -10421,7 +10421,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chotěboř' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10433,7 +10433,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -10445,7 +10445,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10457,7 +10457,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10469,7 +10469,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10481,7 +10481,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -10493,94 +10493,10 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -10597,7 +10513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10656,6 +10572,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10698,6 +10619,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC Sparta Praha.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10745,6 +10671,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10787,6 +10718,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10829,6 +10765,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10871,6 +10812,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10913,6 +10859,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10955,6 +10906,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10997,6 +10953,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11039,6 +11000,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11081,6 +11047,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11123,6 +11094,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11165,6 +11141,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11207,6 +11188,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11249,6 +11235,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11291,6 +11282,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11333,6 +11329,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11375,6 +11376,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11417,6 +11423,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11459,6 +11470,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11501,6 +11517,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11543,6 +11564,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11585,6 +11611,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11627,6 +11658,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11669,6 +11705,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11711,6 +11752,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11753,6 +11799,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11795,6 +11846,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11837,6 +11893,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11884,6 +11945,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11926,6 +11992,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12052,6 +12123,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12178,6 +12254,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0036</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12220,6 +12301,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0037</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12262,6 +12348,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0038</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12304,6 +12395,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0039</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12346,6 +12442,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0040</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12388,6 +12489,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0041</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12430,6 +12536,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0042</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12472,6 +12583,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0043</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12514,6 +12630,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0044</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12556,6 +12677,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0045</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12598,6 +12724,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0046</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12640,6 +12771,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0047</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12682,6 +12818,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0048</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12724,6 +12865,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0053</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12766,6 +12912,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0054</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12808,6 +12959,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0055</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12976,6 +13132,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0062</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -13228,6 +13389,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0060</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13270,6 +13436,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0061</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -13606,6 +13777,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0067</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13648,6 +13824,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0068</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13690,6 +13871,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0069</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -13898,6 +14084,11 @@
       <c r="K78" t="inlineStr">
         <is>
           <t>Kontejner L40</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S2004_05_0075</t>
         </is>
       </c>
     </row>
@@ -13963,6 +14154,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13980,6 +14176,11 @@
           <t>NODE_S2005_06_0001</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -13997,6 +14198,11 @@
           <t>NODE_S2005_06_0003</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14014,6 +14220,11 @@
           <t>NODE_S2005_06_0003</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -14031,6 +14242,11 @@
           <t>NODE_S2005_06_0036</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -14041,6 +14257,11 @@
       <c r="B88" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -17205,7 +17426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J190"/>
+  <dimension ref="A1:J184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -17595,12 +17816,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -17978,12 +18199,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -18146,12 +18367,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -18588,17 +18809,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0034</t>
+          <t>CLUB_S2005_06_0043</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HC Cormoran-auto Krásný  - VTJ Ještěd Liberec 4:1, 7:4</t>
+          <t>HC Uherské Hradiště</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HC Cormoran-auto Krásný  - VTJ Ještěd Liberec 4:1, 7:4</t>
+          <t>HC Uherské Hradiště</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -18608,34 +18829,34 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0139</t>
+          <t>CLUB_S2004_05_0212</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Lokomotiva Liberec B (B-tym, 40_Libereckému). Almanach uvadi „(Slavoj Liberec)" v zavorce - POZOR: dle Wiki D42 (Pavlovo upresneni 04/2026) Lokomotiva Liberec vznikla teprve 1956, Slavoj Liberec NENI predchudce ale jiny klub! Komentar v almanachu k overeni Pavlem (D40). Lokomotiva Liberec = HC Liberec / Bili Tygri (Wiki D42 dolozeno pro 57/58). Genealogie: TJ Lokomotiva Liberec (1956) -&gt; TJ Stadion Liberec (1961) -&gt; TJ PS Stadion Liberec (1970, PS = Pozemni stavby) -&gt; HC Stadion Liberec (1990) -&gt; HC Liberec (1994) -&gt; Bili Tygri Liberec (2000-dnes). city Liberec. || Lokomotiva Liberec B 57/58 (40_Liberecký, B-tym). Liberec = Bílí Tygři Liberec (Wiki D42 - Pavlovo upresneni 04/2026, OPRAVA puvodni ústavy z 04/2026!). Kořeny od 1934 (NE 1956 jak chybne uvedla puvodni ústava!). Genealogie: Rapid Horní Růžodol (1934-1950) -&gt; Sokol Kolora / Jiskra Kolora Liberec (1950-1955, vcleneni do textilniho podniku Kolora) -&gt; Lokomotiva Liberec (prosinec 1955, slouceni Jiskra Kolora + Slovan KNV + Slovan Severočeské tiskárny) -&gt; TJ Stadion Liberec (cerven 1961) -&gt; HC Stadion PS Liberec (1974/76, Pozemni stavby) -&gt; HC Stadion Liberec (1989, 1994 Syner) -&gt; Bílí Tygři Liberec (21.8.2000). Patterns: Sokol Rapid Liberec, Kolora Liberec, Sokol Kolora Liberec, Jiskra Kolora Liberec, Lokomotiva Liberec. city Liberec. || Liberec - vsechny librecke kluby z chain Bili Tygri Liberec (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Rapid Liberec (1934) -&gt; Kolora -&gt; Lokomotiva (1955) -&gt; Stadion (1961) -&gt; Bili Tygri (2000+). Vsechny libercke B-tymy + paralelni Slavia VSS (akademicky) + Dukla Liberec (vojensky 1960-1978) + Jiskra Kolora (textilni podnik). city Liberec.</t>
+          <t>Spartak Uherské Hradiště. city ✓. || Uherské Hradiště (Wiki - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj. POZN: blizko Uherskeho Hradiste byly Sokol Stare Mesto, Tatran Uhersky Ostroh atd. city Uherské Hradiště.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Liberec</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0035</t>
+          <t>CLUB_S2005_06_0045</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem  - HC Rokycany 2:0, 4:4</t>
+          <t>HC Žďár nad Sázavou (II)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem  - HC Rokycany 2:0, 4:4</t>
+          <t>HC Žďár nad Sázavou (II)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -18645,34 +18866,34 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0137</t>
+          <t>CLUB_S2004_05_0081</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Roudnice nad Labem</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0036</t>
+          <t>CLUB_S2005_06_0046</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HC Chotěboř  - HC Hluboká nad Vltavou  8:5, 7:3</t>
+          <t>HC Mělník</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HC Chotěboř  - HC Hluboká nad Vltavou  8:5, 7:3</t>
+          <t>HC Mělník</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -18682,34 +18903,34 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0181</t>
+          <t>CLUB_S2004_05_0100</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>B-tým Spartak Chotěboř (CLUB_S1953_54_0316). Přejmenováno II → B (D21). prev na 52/53 0263 (A-tým, B 52/53 neexistoval). || Chotěboř = Spartak Chotěboř (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Havlíčkův Brod). S-P = Semily-Pardubice. city Chotěboř. || TBD: city 'Chotěboř' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Mělník = HC Junior Mělník (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. city Mělník.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Hluboká nad Vltavou</t>
+          <t>Junior Mělník</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0037</t>
+          <t>CLUB_S2005_06_0047</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HC Dvůr Králové nad Labem  - HC Mělník  2:2, 2:4</t>
+          <t>HC Uničov (II)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HC Dvůr Králové nad Labem  - HC Mělník  2:2, 2:4</t>
+          <t>HC Uničov (II)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -18719,256 +18940,286 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0166</t>
+          <t>CLUB_S2004_05_0096</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Dvůr Králové nL Labem (Wiki - registr ustavy 04/2026). Východocesky kraj. Hokej dlouhodoba tradice - SK Dvůr Králové. city Dvůr Králové nad Labem.</t>
+          <t>Uničov = TJ Spartak Uničov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Uničov.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Dvůr Králové nad Labem</t>
+          <t>Uničov</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0038</t>
+          <t>CLUB_S2005_06_0049</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HC Mělník - HC Chotěboř 5:0, 2:3</t>
+          <t>HC Cormoran-auto Krásný</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HC Mělník - HC Chotěboř 5:0, 2:3</t>
+          <t>HC Cormoran-auto Krásný</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KVAL</t>
+          <t>30_Praha</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0181</t>
+          <t>CLUB_S2004_05_0054</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>B-tým Spartak Chotěboř (CLUB_S1953_54_0316). Přejmenováno II → B (D21). prev na 52/53 0263 (A-tým, B 52/53 neexistoval). || Chotěboř = Spartak Chotěboř (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Havlíčkův Brod). S-P = Semily-Pardubice. city Chotěboř.</t>
+          <t>Praha = HC Cormoran auto Krásný (Wiki D42 - registr ustavy 04/2026). Praha. city Praha.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Chotěboř</t>
+          <t>Cormoran auto Krásný</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0039</t>
+          <t>CLUB_S2005_06_0050</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HC Cormoran-auto Krásný - HC Roudnice nad Labem 3:2, 2:6</t>
+          <t>HC SPEI výfuky</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HC Cormoran-auto Krásný - HC Roudnice nad Labem 3:2, 2:6</t>
+          <t>HC SPEI výfuky</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KVAL</t>
+          <t>30_Praha</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0137</t>
+          <t>CLUB_S2004_05_0053</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
+          <t>Praha = HC SpeI výfuky (Wiki D42 - registr ustavy 04/2026). Praha. Patterns: SPEI výfuky. city Praha.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Roudnice nad Labem</t>
+          <t>SPEI výfuky</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0043</t>
+          <t>CLUB_S2005_06_0051</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HC Uherské Hradiště</t>
+          <t>HC Benátky nad Jizerou B (STČ)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HC Uherské Hradiště</t>
+          <t>HC Benátky nad Jizerou B (STČ)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KVAL</t>
+          <t>30_Praha</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0212</t>
+          <t>CLUB_S2004_05_0060</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Spartak Uherské Hradiště. city ✓. || Uherské Hradiště (Wiki - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj. POZN: blizko Uherskeho Hradiste byly Sokol Stare Mesto, Tatran Uhersky Ostroh atd. city Uherské Hradiště.</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Uherské Hradiště</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0045</t>
+          <t>CLUB_S2005_06_0052</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HC Žďár nad Sázavou (II)</t>
+          <t>HC Kobra Praha B</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HC Žďár nad Sázavou (II)</t>
+          <t>HC Kobra Praha B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KVAL</t>
+          <t>30_Praha</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0081</t>
+          <t>CLUB_S2004_05_0056</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Žďár nad Sázavou</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0046</t>
+          <t>CLUB_S2005_06_0053</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HC Mělník</t>
+          <t>HC Comet Praha</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HC Mělník</t>
+          <t>HC Comet Praha</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KVAL</t>
+          <t>30_Praha</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0100</t>
+          <t>CLUB_S2004_05_0061</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Mělník = HC Junior Mělník (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. city Mělník.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Junior Mělník</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0047</t>
+          <t>CLUB_S2005_06_0054</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HC Uničov (II)</t>
+          <t>TJ Bohemians Praha</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HC Uničov (II)</t>
+          <t>TJ Bohemians Praha</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KVAL</t>
+          <t>30_Praha</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0096</t>
+          <t>CLUB_S2004_05_0055</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Uničov = TJ Spartak Uničov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Uničov.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Uničov</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0049</t>
+          <t>CLUB_S2005_06_0055</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HC Cormoran-auto Krásný</t>
+          <t>TJ Sokol Žižkov</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HC Cormoran-auto Krásný</t>
+          <t>TJ Sokol Žižkov</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -18983,34 +19234,34 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0054</t>
+          <t>CLUB_S2004_05_0059</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Praha = HC Cormoran auto Krásný (Wiki D42 - registr ustavy 04/2026). Praha. city Praha.</t>
+          <t>Praha (Žižkov) = TJ Sokol Žižkov (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 3. city Praha (Žižkov).</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Cormoran auto Krásný</t>
+          <t>Žižkov</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0050</t>
+          <t>CLUB_S2005_06_0056</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HC SPEI výfuky</t>
+          <t>HC Olympik Praha</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HC SPEI výfuky</t>
+          <t>HC Olympik Praha</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -19025,34 +19276,34 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0053</t>
+          <t>CLUB_S2004_05_0058</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Praha = HC SpeI výfuky (Wiki D42 - registr ustavy 04/2026). Praha. Patterns: SPEI výfuky. city Praha.</t>
+          <t>Praha = HC Olympik Praha (Wiki D42 - registr ustavy 04/2026). Praha. Patterns: Olympik. city Praha.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SPEI výfuky</t>
+          <t>Olympik Praha</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0051</t>
+          <t>CLUB_S2005_06_0057</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HC Benátky nad Jizerou B (STČ)</t>
+          <t>HKB Smíchov</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HC Benátky nad Jizerou B (STČ)</t>
+          <t>HKB Smíchov</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -19067,286 +19318,291 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0060</t>
+          <t>CLUB_S2004_05_0057</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
+          <t>Praha (Smíchov) = HKB Smíchov (Wiki D42 - registr ustavy 04/2026). Praha 5. Patterns: HK Buldoci Smíchov -&gt; HKB. city Praha (Smíchov).</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>HKB Smíchov</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0052</t>
+          <t>CLUB_S2005_06_0058</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HC Kobra Praha B</t>
+          <t>HC Jablonec nad Nisou</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HC Kobra Praha B</t>
+          <t>HC Jablonec nad Nisou</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>30_Praha</t>
+          <t>30_2liga</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>L40</t>
+          <t>L30</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0056</t>
+          <t>CLUB_S2004_05_0062</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0053</t>
+          <t>CLUB_S2005_06_0059</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HC Comet Praha</t>
+          <t>HC Klatovy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HC Comet Praha</t>
+          <t>HC Klatovy</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>30_Praha</t>
+          <t>30_2liga</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>L40</t>
+          <t>L30</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0061</t>
+          <t>CLUB_S2004_05_0079</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Klatovy = SHC Klatovy (Wiki - registr ustavy 04/2026). Zapadocesky kraj. - Patterns: Spartak Klatovy, SHC. city Klatovy. || Stupno = TJ Banik Stupno / Jodasta Stupno (Wiki D42 - registr ustavy 04/2026). Zapadocesky/Plzensky kraj (okres Rokycany). Patterns: Sokol Stupno -&gt; Banik Stupno -&gt; Jodasta Stupno. city Stupno.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Klatovy</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0054</t>
+          <t>CLUB_S2005_06_0060</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TJ Bohemians Praha</t>
+          <t>HC Řisuty</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TJ Bohemians Praha</t>
+          <t>HC Řisuty (N)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30_Praha</t>
+          <t>30_2liga</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>L40</t>
+          <t>L30</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0055</t>
+          <t>CLUB_S2004_05_0047</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Řisuty = TJ Sokol Řisuty (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Řisuty.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Řisuty</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0055</t>
+          <t>CLUB_S2005_06_0061</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TJ Sokol Žižkov</t>
+          <t>HC Sokolov</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TJ Sokol Žižkov</t>
+          <t>HC Sokolov</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>30_Praha</t>
+          <t>30_2liga</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>L40</t>
+          <t>L30</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0059</t>
+          <t>CLUB_S2004_05_0069</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Praha (Žižkov) = TJ Sokol Žižkov (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 3. city Praha (Žižkov).</t>
+          <t>B-tým TJ Spartak Praha Sokolovo (CLUB_S1953_54_0001 v 1. lize). Doplnění „Praha" do názvu (Pavlovo rozhodnutí — plný název klubu, ne zkrácená forma). city: Sokolovo = čtvrť Prahy (D23) → „Praha". Smart fix prev → 52/53 0001 (A-tým, B 52/53 neexistoval). || Spartak Praha Sokolovo B 53/54 (B-tým, 30_PHA_mesto). Sparta Praha = HC Sparta Praha (Wiki D18 / D42). Genealogie: AC Sparta Praha (1903) -&gt; Sokol Sparta Bubeneč (1948) -&gt; ZSJ Bratrství Sparta Praha (1949) -&gt; ZSJ Sparta ČKD Sokolovo Praha (1951, ČKD = Českomoravská-Kolben-Daněk) -&gt; TJ Spartak Praha Sokolovo (1952) -&gt; TJ Sparta ČKD Praha (1965) -&gt; HC Sparta Praha (1990). city Praha (D23, Bubeneč = čtvrť Prahy 7). || Sokolov = HC Baník Sokolov (Wiki - registr ustavy 04/2026). ZALOZEN 1945 jako SK FHD Dolní Rychnov (FHD = Falknovske hnedouhelne doly - Sokolov se drive jmenoval Falknov nL Ohri). Genealogie: SK FHD (1945) -&gt; TJ Banik Sokolov (1953+ DSO) -&gt; NHL (1 sezona) -&gt; 1969 nahradil zruseny Duklu Litomerice v A skupine CNHL -&gt; NHL (1 sezona) -&gt; 1990 znovu 1.NHL -&gt; 1997 sestup do 2.ligy -&gt; 2002 prejmenovani na HC Banik Sokolov -&gt; 2019/20 do Maxa Ligy. Falknov nad Ohri se 1948 prejmenoval na Sokolov. city Sokolov.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Žižkov</t>
+          <t>Sokolov</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0056</t>
+          <t>CLUB_S2005_06_0062</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HC Olympik Praha</t>
+          <t>HC Klášterec nad Ohří</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HC Olympik Praha</t>
+          <t>HC Klášterec nad Ohří</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>30_Praha</t>
+          <t>30_2liga</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>L40</t>
+          <t>L30</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0058</t>
+          <t>CLUB_S2004_05_0066</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Praha = HC Olympik Praha (Wiki D42 - registr ustavy 04/2026). Praha. Patterns: Olympik. city Praha.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Olympik Praha</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0057</t>
+          <t>CLUB_S2005_06_0063</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HKB Smíchov</t>
+          <t>HC Most</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HKB Smíchov</t>
+          <t>HC Most</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>30_Praha</t>
+          <t>30_2liga</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>L40</t>
+          <t>L30</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0057</t>
+          <t>CLUB_S2004_05_0067</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Praha (Smíchov) = HKB Smíchov (Wiki D42 - registr ustavy 04/2026). Praha 5. Patterns: HK Buldoci Smíchov -&gt; HKB. city Praha (Smíchov).</t>
+          <t>Baník Most. city ✓. || Baník Most 53/54 (30_Ústecký). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Most = HC Most / Baník Most (Wiki D42 - Pavlovo upresneni 04/2026, hokej.cz). Genealogie: HO Uhlomost (1946, Hokejovy oddil Uhlomost) -&gt; Sokol Uhlomost (1948-49) -&gt; Uhlomost (1952) -&gt; TJ Baník Most (1953+, SHD = Severočeské hnědouhelné doly, 'uhlí + Most' = puvodni nazev Uhlomost) -&gt;... -&gt; HC Baník SHD Most (80. leta) -&gt; HC Most (1991) -&gt; 2017 sestup z 1.ligy + presun do Slaneho -&gt; 2017 Mostečtí lvi (novy klub v Most, ne navazujici, sezona 2017/18+). Patterns: Sokol Uhlomost, Uhlomost, Baník Most, TJ Baník Most. Sponzorske patronace pozdejsi: SHD = Severočeské hnědouhelné doly (statni podnik). city Most. POZN: 'Sokol Neuměřice – Kamenný Most' = JINÉ MÍSTO (Kamenný Most je obec u Neuměřic ve Středocesku, ne v meste Most). || Baník Most 53/54 (30_Ústecký). KLICOVY ROK 1953 DSO reforma + slouceni s Baník Oldřich. Most = MOSTEČTÍ LVI (Wiki D42 + hokej.cz - Pavlovo upresneni 04/2026). Genealogie historicka: Uhlolom Most (1949+) -&gt; Sokol Uhlomost (1951+, slouceni) -&gt; Uhlomost (1952) -&gt; Baník Most (1953+ DSO reforma + slouceni s Banik Oldrich) -&gt; TJ Baník Most (1958+) -&gt;... -&gt; HC Most (do 2017, sestup do Slaného) -&gt; MOSTEČTÍ LVI (2017+ NOVY klub). Klub zalozen historicky kolem 1945 (po valce). city Most. POZOR: Mostek (Královehradecky) a Kamenny Most (Středočesky) = JINA mesta! NE Most / Mostecti Lvi chain. || Banik Most 53/54 (30_Ústecký). KLICOVY ROK 1953 DSO reforma -&gt; Banik (horníci). Most = HC Most (1946-2017) -&gt; Mostečtí lvi (2017-dnes) (Wiki D42 + Pavlovo upresneni 04/2026). DVE ERY mosteckeho hokeje! **1. era - HC Most (1946-2017):** 1946 zalozeni HO Uhlomost (Hokejovy oddil Uhlomost - podnik Uhlomost = uhelny prumysl, hnedouhelne doly v Mosteckem revíru). 1953+ Banik Most (DSO reforma, Banik = obecny DSO horniku). 1991-2007 stabilni 2.liga. 2005+ posledni nazev HC Most. 2007 postup do 1.ligy (2 sezony, navrat 2009). 2011 zpet 1.liga (6 let, ale bez play-off). **2016/17 sestup z 1.ligy + STEHOVANI klubu do Slaneho!** **2. era - Mostecti lvi (2017-dnes):** Vznikl uplne novy klub za podpory mesta Most (statutarni mesto Most = 100% spolecnik Mostecky hokejovy klub s.r.o.). Sport Most z.s. = mladez (od 2015), Mostecky hokejovy klub s.r.o. = dospeli (od 2017). Spolecne registracni cislo MOSTEČTÍ LVI. 2017/18 Krajska liga -&gt; 2018/19 do 2.ligy (kde dnes). Patterns: Uhlomost/Sokol Uhlomost, Banik Most, TJ Banik Most, HC Most, Mostecti lvi. city Most. POZOR: Mostek = JINE MESTO Královéhradecky (mestys). Kamenny Most = JINE MESTO (obec u Prahy v Stredoceskem kraji). || Banik Most 53/54 (30_Ústecký, L30). KLICOVY ROK 1953 DSO reforma -&gt; TJ Baník Most. Banik = obecny DSO horniku/uhelne tezby. Most = HC Baník Most (1946-2017, presunut do Slaneho) -&gt; Mostečtí Lvi (2017-dnes) (Wiki D42 + Pavlovo upresneni + Wikipedia HC Most/Mostečtí Lvi - registr ustavy 04/2026). Genealogie HC Baník Most: 1946 HO Uhlomost (Hokejovy oddil Uhlomost - Most + uhli) -&gt; Sokol Uhlomost (1948-49, sokolska reorganizace) -&gt; Uhlomost (1952) -&gt; TJ Baník Most (1953+ DSO reforma, Baník = obecny DSO horniku/uhelne tezby) -&gt; TJ Baník SHD Most (SHD = Severočeské hnědouhelné doly) -&gt; 1990 TJ Baník Most -&gt; 1994 HC Baník Most -&gt; 2000 SK HC Baník Most -&gt; 2005 HC Most -&gt; **2017 odchod do Slaneho** (po sestupu z 1.ligy 2016/17). MILNIKY: 1976/77 postup do 2. ČNHL. 1990/91 postup do 2.ligy. 2007 postup do 1.ligy. Po odchodu HC Most v lete 2017 vznikla **Mostečtí Lvi** (zalozeni 2017 - NOSITEL HOKEJOVE TRADICE V MESTE, mestska zastupitelnost zalozila po odchodu HC Most do Slaneho), zalozeni mestskou zastupitelnosti) - zcela novy klub. 2018/19 postup do 2. ligy. Hraji v Krajske lize muzu UlK. Patterns: Sokol Uhlomost, Uhlomost, TJ Baník Most, Baník Most, HC Most, Mostečtí Lvi. city Most. POZOR: NE 'Mostek' (Královéhradecky kraj) ani 'Kamenny Most' (Praha) - JINA MESTA (D44 - identita = lokalita).</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>HKB Smíchov</t>
+          <t>Most</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0058</t>
+          <t>CLUB_S2005_06_0064</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HC Jablonec nad Nisou</t>
+          <t>HC Děčín</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HC Jablonec nad Nisou</t>
+          <t>HC Děčín</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -19361,34 +19617,34 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0062</t>
+          <t>CLUB_S2004_05_0065</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>B-tým Kovostroj Děčín (CLUB_S1951_52_0170). Smart fix prev: z 0498 (A-tým 50/51) na 0511 (B-tým 50/51 = „Kovostroj Děčín B"). || Oprava city: „Kovostroj Děčín" → „Děčín". Kovostroj Děčín B → Děčín. (B-tým 0170) || Kovostroj Děčín B 51/52 - B-tym. Děčín = HC Děčín (Wiki D42 + hokej.cz 04/2026). Genealogie: 1945 HO SK Podmokly-Děčín (zalozeni) -&gt; Sociakol Děčín (49/50, podnik Sociakol) -&gt; Kovostroj Děčín (50/51+, podnik Kovostroj - strojirensky zavod) -&gt; Spartak Děčín (53/54+ DSO reforma) -&gt; Baník Děčín (55/56+, prejmenovani z dolarskeho podniku) -&gt;... -&gt; 1999 HC Děčín. Klicove milniky: zimni stadion zastreseny 1983, do 2.ligy 1993/94 (akce '20 let' v 2013). Patterns: Sociakol Děčín, Kovostroj Děčín, Spartak Děčín, Baník Děčín. city Děčín. || Kovostroj Děčín B 51/52 (20_Ústecký okresni, B-tym). Děčín = HC Děčín (Wiki D42 + hokej.cz - Pavlovo upresneni 04/2026). Genealogie: 1945 zalozen jako HO SK Podmokly-Děčín -&gt; Sociakol Děčín (1949) -&gt; Kovostroj Děčín (1950+, podnik Kovostroj - kovovyrobni zavod) -&gt; Spartak Děčín (1953+, DSO reforma) -&gt; Baník Děčín (1955+) -&gt;... -&gt; 1999 HC Děčín (dnes). KLICOVE milniky: 1983 zastreseni zimniho stadionu, 1993/94 postup do 2. ligy. city Děčín. POZOR: NE Děčín-Bynov (mestska cast) - oznaceno separatne. || Kovostroj Děčín B 51/52 (20_Ústecký okresni, B-tym). Děčín = HC Děčín (Wiki D42 - registr ustavy 04/2026). Genealogie: HO SK Podmokly-Děčín (1945, zalozeni) -&gt; Sociakol Děčín (1948-50, Sociakol = Sociální kolektiv?) -&gt; Kovostroj Děčín (1950+, podnik Kovostroj - kovoobrabeci stroje) -&gt; Spartak Děčín (1953+ DSO reforma) -&gt; Banik Děčín (1955+, Banik = obecny DSO horniku/tezbarskeho prumyslu) -&gt;... -&gt; HC Děčín (1999, soucasny nazev). KLICOVE: Zimni stadion zastrešen az 1983! Od 1993/94 ve 2.lize. Patterns: Sociakol Děčín, Kovostroj Děčín, Spartak Děčín, Banik Děčín. city Děčín. POZN: 49/50 jointni zaznamy 'Sociakol Děčín – Arma Ústí nad Labem' a 'Benzina Roudnice - Sociakol Děčín/Arma Ústí nad Labem' = sdileny tym tří mest (Děčín + Ústí + Roudnice). To se delalo v 49/50 nez se kluby zformovaly. Železničáři Děčín (49/50) = patrne predchudce ČSD Dynamo Děčín (50/51).</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0059</t>
+          <t>CLUB_S2005_06_0065</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HC Klatovy</t>
+          <t>HC Kobra Praha</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HC Klatovy</t>
+          <t>HC Kobra Praha</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -19403,34 +19659,34 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0079</t>
+          <t>CLUB_S2004_05_0068</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Klatovy = SHC Klatovy (Wiki - registr ustavy 04/2026). Zapadocesky kraj. - Patterns: Spartak Klatovy, SHC. city Klatovy. || Stupno = TJ Banik Stupno / Jodasta Stupno (Wiki D42 - registr ustavy 04/2026). Zapadocesky/Plzensky kraj (okres Rokycany). Patterns: Sokol Stupno -&gt; Banik Stupno -&gt; Jodasta Stupno. city Stupno.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Klatovy</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0060</t>
+          <t>CLUB_S2005_06_0066</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HC Řisuty</t>
+          <t>HC Hvězda Praha</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HC Řisuty (N)</t>
+          <t>HC Hvězda Praha</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -19438,11 +19694,6 @@
           <t>30_2liga</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>L30</t>
@@ -19450,34 +19701,34 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0047</t>
+          <t>CLUB_S2004_05_0070</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Řisuty = TJ Sokol Řisuty (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Řisuty.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Řisuty</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0061</t>
+          <t>CLUB_S2005_06_0067</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HC Sokolov</t>
+          <t>HC Slaný</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HC Sokolov</t>
+          <t>HC Slaný</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -19492,34 +19743,34 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0069</t>
+          <t>CLUB_S2004_05_0073</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>B-tým TJ Spartak Praha Sokolovo (CLUB_S1953_54_0001 v 1. lize). Doplnění „Praha" do názvu (Pavlovo rozhodnutí — plný název klubu, ne zkrácená forma). city: Sokolovo = čtvrť Prahy (D23) → „Praha". Smart fix prev → 52/53 0001 (A-tým, B 52/53 neexistoval). || Spartak Praha Sokolovo B 53/54 (B-tým, 30_PHA_mesto). Sparta Praha = HC Sparta Praha (Wiki D18 / D42). Genealogie: AC Sparta Praha (1903) -&gt; Sokol Sparta Bubeneč (1948) -&gt; ZSJ Bratrství Sparta Praha (1949) -&gt; ZSJ Sparta ČKD Sokolovo Praha (1951, ČKD = Českomoravská-Kolben-Daněk) -&gt; TJ Spartak Praha Sokolovo (1952) -&gt; TJ Sparta ČKD Praha (1965) -&gt; HC Sparta Praha (1990). city Praha (D23, Bubeneč = čtvrť Prahy 7). || Sokolov = HC Baník Sokolov (Wiki - registr ustavy 04/2026). ZALOZEN 1945 jako SK FHD Dolní Rychnov (FHD = Falknovske hnedouhelne doly - Sokolov se drive jmenoval Falknov nL Ohri). Genealogie: SK FHD (1945) -&gt; TJ Banik Sokolov (1953+ DSO) -&gt; NHL (1 sezona) -&gt; 1969 nahradil zruseny Duklu Litomerice v A skupine CNHL -&gt; NHL (1 sezona) -&gt; 1990 znovu 1.NHL -&gt; 1997 sestup do 2.ligy -&gt; 2002 prejmenovani na HC Banik Sokolov -&gt; 2019/20 do Maxa Ligy. Falknov nad Ohri se 1948 prejmenoval na Sokolov. city Sokolov.</t>
+          <t>Dukla Slaný. Almanach uvádí „(DA Kyjev)" - význam k vyjasneni Pavlem (možná identita předchozího klubu, ale nepotvrzeno). city Slaný (město v názvu, D33). prev k overeni. || Slaný = HK Lev Slaný (Wiki + hklevslany.cz - registr ustavy 04/2026). KLUB ZALOZEN 1933. Genealogie: 1933 zalozeni -&gt; 1953 Spartak Slaný (postup do krajske souteze) -&gt; 1960 postup do divize -&gt; TJ ČKD Slaný (NHL (poprve!) -&gt; 1990/91 znovu do 2.NHL -&gt; 2012 prejmenovani na HK Lev Slaný. POZN: HC Most se sem prestehoval po sestupu 2017! city Slaný.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Sokolov</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0062</t>
+          <t>CLUB_S2005_06_0068</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HC Klášterec nad Ohří</t>
+          <t>HC Teplice</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HC Klášterec nad Ohří</t>
+          <t>HC Teplice</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -19534,34 +19785,34 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0066</t>
+          <t>CLUB_S2004_05_0072</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří</t>
+          <t>Teplice</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0063</t>
+          <t>CLUB_S2005_06_0069</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HC Most</t>
+          <t>HC Louny</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HC Most</t>
+          <t>HC Louny</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -19576,34 +19827,34 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0067</t>
+          <t>CLUB_S2004_05_0071</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Baník Most. city ✓. || Baník Most 53/54 (30_Ústecký). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Most = HC Most / Baník Most (Wiki D42 - Pavlovo upresneni 04/2026, hokej.cz). Genealogie: HO Uhlomost (1946, Hokejovy oddil Uhlomost) -&gt; Sokol Uhlomost (1948-49) -&gt; Uhlomost (1952) -&gt; TJ Baník Most (1953+, SHD = Severočeské hnědouhelné doly, 'uhlí + Most' = puvodni nazev Uhlomost) -&gt;... -&gt; HC Baník SHD Most (80. leta) -&gt; HC Most (1991) -&gt; 2017 sestup z 1.ligy + presun do Slaneho -&gt; 2017 Mostečtí lvi (novy klub v Most, ne navazujici, sezona 2017/18+). Patterns: Sokol Uhlomost, Uhlomost, Baník Most, TJ Baník Most. Sponzorske patronace pozdejsi: SHD = Severočeské hnědouhelné doly (statni podnik). city Most. POZN: 'Sokol Neuměřice – Kamenný Most' = JINÉ MÍSTO (Kamenný Most je obec u Neuměřic ve Středocesku, ne v meste Most). || Baník Most 53/54 (30_Ústecký). KLICOVY ROK 1953 DSO reforma + slouceni s Baník Oldřich. Most = MOSTEČTÍ LVI (Wiki D42 + hokej.cz - Pavlovo upresneni 04/2026). Genealogie historicka: Uhlolom Most (1949+) -&gt; Sokol Uhlomost (1951+, slouceni) -&gt; Uhlomost (1952) -&gt; Baník Most (1953+ DSO reforma + slouceni s Banik Oldrich) -&gt; TJ Baník Most (1958+) -&gt;... -&gt; HC Most (do 2017, sestup do Slaného) -&gt; MOSTEČTÍ LVI (2017+ NOVY klub). Klub zalozen historicky kolem 1945 (po valce). city Most. POZOR: Mostek (Královehradecky) a Kamenny Most (Středočesky) = JINA mesta! NE Most / Mostecti Lvi chain. || Banik Most 53/54 (30_Ústecký). KLICOVY ROK 1953 DSO reforma -&gt; Banik (horníci). Most = HC Most (1946-2017) -&gt; Mostečtí lvi (2017-dnes) (Wiki D42 + Pavlovo upresneni 04/2026). DVE ERY mosteckeho hokeje! **1. era - HC Most (1946-2017):** 1946 zalozeni HO Uhlomost (Hokejovy oddil Uhlomost - podnik Uhlomost = uhelny prumysl, hnedouhelne doly v Mosteckem revíru). 1953+ Banik Most (DSO reforma, Banik = obecny DSO horniku). 1991-2007 stabilni 2.liga. 2005+ posledni nazev HC Most. 2007 postup do 1.ligy (2 sezony, navrat 2009). 2011 zpet 1.liga (6 let, ale bez play-off). **2016/17 sestup z 1.ligy + STEHOVANI klubu do Slaneho!** **2. era - Mostecti lvi (2017-dnes):** Vznikl uplne novy klub za podpory mesta Most (statutarni mesto Most = 100% spolecnik Mostecky hokejovy klub s.r.o.). Sport Most z.s. = mladez (od 2015), Mostecky hokejovy klub s.r.o. = dospeli (od 2017). Spolecne registracni cislo MOSTEČTÍ LVI. 2017/18 Krajska liga -&gt; 2018/19 do 2.ligy (kde dnes). Patterns: Uhlomost/Sokol Uhlomost, Banik Most, TJ Banik Most, HC Most, Mostecti lvi. city Most. POZOR: Mostek = JINE MESTO Královéhradecky (mestys). Kamenny Most = JINE MESTO (obec u Prahy v Stredoceskem kraji). || Banik Most 53/54 (30_Ústecký, L30). KLICOVY ROK 1953 DSO reforma -&gt; TJ Baník Most. Banik = obecny DSO horniku/uhelne tezby. Most = HC Baník Most (1946-2017, presunut do Slaneho) -&gt; Mostečtí Lvi (2017-dnes) (Wiki D42 + Pavlovo upresneni + Wikipedia HC Most/Mostečtí Lvi - registr ustavy 04/2026). Genealogie HC Baník Most: 1946 HO Uhlomost (Hokejovy oddil Uhlomost - Most + uhli) -&gt; Sokol Uhlomost (1948-49, sokolska reorganizace) -&gt; Uhlomost (1952) -&gt; TJ Baník Most (1953+ DSO reforma, Baník = obecny DSO horniku/uhelne tezby) -&gt; TJ Baník SHD Most (SHD = Severočeské hnědouhelné doly) -&gt; 1990 TJ Baník Most -&gt; 1994 HC Baník Most -&gt; 2000 SK HC Baník Most -&gt; 2005 HC Most -&gt; **2017 odchod do Slaneho** (po sestupu z 1.ligy 2016/17). MILNIKY: 1976/77 postup do 2. ČNHL. 1990/91 postup do 2.ligy. 2007 postup do 1.ligy. Po odchodu HC Most v lete 2017 vznikla **Mostečtí Lvi** (zalozeni 2017 - NOSITEL HOKEJOVE TRADICE V MESTE, mestska zastupitelnost zalozila po odchodu HC Most do Slaneho), zalozeni mestskou zastupitelnosti) - zcela novy klub. 2018/19 postup do 2. ligy. Hraji v Krajske lize muzu UlK. Patterns: Sokol Uhlomost, Uhlomost, TJ Baník Most, Baník Most, HC Most, Mostečtí Lvi. city Most. POZOR: NE 'Mostek' (Královéhradecky kraj) ani 'Kamenny Most' (Praha) - JINA MESTA (D44 - identita = lokalita).</t>
+          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Most</t>
+          <t>Louny</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0064</t>
+          <t>CLUB_S2005_06_0071</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HC Děčín</t>
+          <t>HC Vrchlabí</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HC Děčín</t>
+          <t>HC Vrchlabí (N)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -19611,6 +19862,11 @@
           <t>30_2liga</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>L30</t>
@@ -19618,34 +19874,34 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0065</t>
+          <t>CLUB_S2004_05_0164</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>B-tým Kovostroj Děčín (CLUB_S1951_52_0170). Smart fix prev: z 0498 (A-tým 50/51) na 0511 (B-tým 50/51 = „Kovostroj Děčín B"). || Oprava city: „Kovostroj Děčín" → „Děčín". Kovostroj Děčín B → Děčín. (B-tým 0170) || Kovostroj Děčín B 51/52 - B-tym. Děčín = HC Děčín (Wiki D42 + hokej.cz 04/2026). Genealogie: 1945 HO SK Podmokly-Děčín (zalozeni) -&gt; Sociakol Děčín (49/50, podnik Sociakol) -&gt; Kovostroj Děčín (50/51+, podnik Kovostroj - strojirensky zavod) -&gt; Spartak Děčín (53/54+ DSO reforma) -&gt; Baník Děčín (55/56+, prejmenovani z dolarskeho podniku) -&gt;... -&gt; 1999 HC Děčín. Klicove milniky: zimni stadion zastreseny 1983, do 2.ligy 1993/94 (akce '20 let' v 2013). Patterns: Sociakol Děčín, Kovostroj Děčín, Spartak Děčín, Baník Děčín. city Děčín. || Kovostroj Děčín B 51/52 (20_Ústecký okresni, B-tym). Děčín = HC Děčín (Wiki D42 + hokej.cz - Pavlovo upresneni 04/2026). Genealogie: 1945 zalozen jako HO SK Podmokly-Děčín -&gt; Sociakol Děčín (1949) -&gt; Kovostroj Děčín (1950+, podnik Kovostroj - kovovyrobni zavod) -&gt; Spartak Děčín (1953+, DSO reforma) -&gt; Baník Děčín (1955+) -&gt;... -&gt; 1999 HC Děčín (dnes). KLICOVE milniky: 1983 zastreseni zimniho stadionu, 1993/94 postup do 2. ligy. city Děčín. POZOR: NE Děčín-Bynov (mestska cast) - oznaceno separatne. || Kovostroj Děčín B 51/52 (20_Ústecký okresni, B-tym). Děčín = HC Děčín (Wiki D42 - registr ustavy 04/2026). Genealogie: HO SK Podmokly-Děčín (1945, zalozeni) -&gt; Sociakol Děčín (1948-50, Sociakol = Sociální kolektiv?) -&gt; Kovostroj Děčín (1950+, podnik Kovostroj - kovoobrabeci stroje) -&gt; Spartak Děčín (1953+ DSO reforma) -&gt; Banik Děčín (1955+, Banik = obecny DSO horniku/tezbarskeho prumyslu) -&gt;... -&gt; HC Děčín (1999, soucasny nazev). KLICOVE: Zimni stadion zastrešen az 1983! Od 1993/94 ve 2.lize. Patterns: Sociakol Děčín, Kovostroj Děčín, Spartak Děčín, Banik Děčín. city Děčín. POZN: 49/50 jointni zaznamy 'Sociakol Děčín – Arma Ústí nad Labem' a 'Benzina Roudnice - Sociakol Děčín/Arma Ústí nad Labem' = sdileny tym tří mest (Děčín + Ústí + Roudnice). To se delalo v 49/50 nez se kluby zformovaly. Železničáři Děčín (49/50) = patrne predchudce ČSD Dynamo Děčín (50/51).</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Děčín</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0065</t>
+          <t>CLUB_S2005_06_0073</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HC Kobra Praha</t>
+          <t>HC Benátky nad Jizerou</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HC Kobra Praha</t>
+          <t>HC Benátky nad Jizerou</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -19660,12 +19916,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0068</t>
+          <t>CLUB_S2004_05_0063</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -19677,17 +19933,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0066</t>
+          <t>CLUB_S2005_06_0074</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HC Hvězda Praha</t>
+          <t>HC Chrudim</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HC Hvězda Praha</t>
+          <t>HC Chrudim</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -19702,34 +19958,34 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0070</t>
+          <t>CLUB_S2004_05_0083</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Chrudim = TJ Spartak Chrudim (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. city Chrudim.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Chrudim</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0067</t>
+          <t>CLUB_S2005_06_0075</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HC Slaný</t>
+          <t>HC Tábor</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HC Slaný</t>
+          <t>HC Tábor</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -19744,34 +20000,34 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0073</t>
+          <t>CLUB_S2004_05_0077</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Dukla Slaný. Almanach uvádí „(DA Kyjev)" - význam k vyjasneni Pavlem (možná identita předchozího klubu, ale nepotvrzeno). city Slaný (město v názvu, D33). prev k overeni. || Slaný = HK Lev Slaný (Wiki + hklevslany.cz - registr ustavy 04/2026). KLUB ZALOZEN 1933. Genealogie: 1933 zalozeni -&gt; 1953 Spartak Slaný (postup do krajske souteze) -&gt; 1960 postup do divize -&gt; TJ ČKD Slaný (NHL (poprve!) -&gt; 1990/91 znovu do 2.NHL -&gt; 2012 prejmenovani na HK Lev Slaný. POZN: HC Most se sem prestehoval po sestupu 2017! city Slaný.</t>
+          <t>VTJ Tábor byl statutárně "B" tým Dukly Jihlava, a proto se nemohl ucházet o účast v 1. CHL. || DA = Dum armady. Almanach: DA Otava (PDA Tabor?) - vztah PDA. || Oprava city dle D33 (04/2026): "Tábor" -&gt; prazdne (DA/PDA bez mesta v nazvu = city vzdy prazdne). || DA Otava 54/55 (30_Jihočeský). 1954 prejmenovani PDA -&gt; DA Otava (Otava = reka u Tabora). Vojensky klub Tábor: PDA / DA Otava / Dukla Tábor (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: PDA Tábor (1952-53, Pred Dukla armada / Posadkove dum armady) -&gt; DA Otava (1954-1956, Dum armady Otava - reka u Tabora) -&gt; Dukla Tábor (DA Otava) (1956-57+) -&gt; Dukla Tábor (1957-58) -&gt; konec po 1957/58 (almanach 58/59, 59/60 neobsahuje vojensky klub v Tábore). POZN: Po obnoveni VTJ Tábor (1970-1993) jako B-tym Dukly Jihlava, v 1993 fuze s civilnim Vodni stavby Tábor = HC VS VTJ -&gt; vojaci konec (Pavlovo: 'pak chvíli společná a pak vojáci konec'). city Tábor. Samostatny od hlavniho civilniho chain HC Tábor. || Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Hlavni chain: DSK Tábor (1921) -&gt; Sokol -&gt; Spartak Tábor -&gt; Tatran Tábor -&gt; Dukla Tábor (vojensky paralelni) -&gt; HC Tábor. **DA Otava** (Doprava-arm Otava) = paralelni klub. Otava = reka, NE Otavany (Strakonice). city Tábor.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Slaný</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0068</t>
+          <t>CLUB_S2005_06_0076</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HC Teplice</t>
+          <t>HC Nymburk</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HC Teplice</t>
+          <t>HC Nymburk</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -19786,34 +20042,34 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0072</t>
+          <t>CLUB_S2004_05_0064</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
+          <t>Nymburk = TJ Lokomotiva Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **Lokomotiva** = železničárský klub (Nymburk = velky železničárský uzel ČSD). Nymburk je dnes druhe nejvetsi mesto okresu (po Pode bradech). Patterns: Sokol -&gt; Lokomotiva Nymburk. city Nymburk.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0069</t>
+          <t>CLUB_S2005_06_0077</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HC Louny</t>
+          <t>HC ZVVZ Milevsko</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HC Louny</t>
+          <t>HC ZVVZ Milevsko</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -19828,34 +20084,34 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0071</t>
+          <t>CLUB_S2004_05_0078</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny.</t>
+          <t>Spartak Milevsko = HC Milevsko 1934 (Wiki D42 - registr ustavy 04/2026). Chain SK Milevsko (1934) -&gt; Sokol -&gt; Spartak -&gt; ZVVZ. city Milevsko.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Louny</t>
+          <t>Milevsko</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0071</t>
+          <t>CLUB_S2005_06_0078</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HC Vrchlabí</t>
+          <t>HC Pelhřimov</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HC Vrchlabí (N)</t>
+          <t>HC Pelhřimov</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -19863,11 +20119,6 @@
           <t>30_2liga</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>L30</t>
@@ -19875,34 +20126,34 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0164</t>
+          <t>CLUB_S2004_05_0080</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Spartak Pelhřimov = Ledni Medvedi Pelhřimov (Wiki D42 - registr ustavy 04/2026). Klub od 22.11.1932 (HCP). city Pelhřimov.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Agrostroj Pelhřimov</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0073</t>
+          <t>CLUB_S2005_06_0079</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HC Benátky nad Jizerou</t>
+          <t>HC Strakonice</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HC Benátky nad Jizerou</t>
+          <t>HC Strakonice</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -19917,34 +20168,34 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0063</t>
+          <t>CLUB_S2004_05_0076</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
+          <t>DSO Jiskra Strakonice — DSO prefix ponechán almanachově (D35). Jiný klub od DSO Spartak Strakonice (CLUB_S1953_54_0139). || DSO Jiskra Strakonice 53/54. Strakonice = Spartak ČZ Strakonice (Wiki D42 - Pavlovo 04/2026). Strakonice -&gt; Fezko -&gt; ČZ -&gt; DSO Spartak/Jiskra (53/54+) -&gt; Spartak ČZ (57/58+). city Strakonice. || Strakonice = HC Strakonice (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Sokol Strakonice -&gt; Fezko Strakonice (textilni podnik, autopotahy) -&gt; ČZ Strakonice (Ceske zavody motocyklove) -&gt; HC Strakonice. city Strakonice.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Strakonice</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0074</t>
+          <t>CLUB_S2005_06_0080</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HC Chrudim</t>
+          <t>HC Kolín</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HC Chrudim</t>
+          <t>HC Kolín</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -19959,34 +20210,34 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0083</t>
+          <t>CLUB_S2004_05_0084</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Chrudim = TJ Spartak Chrudim (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. city Chrudim.</t>
+          <t>Smart fix prev: chybělo → 51/52 0042 (Tatra Kolín). Pravděpodobně B-tým Tatra Kolín (CLUB_S1952_53_0025), ale almanach má A-tým bez B suffixu — kolegova nepreciznnost. || B-tým Tatra Kolín (CLUB_S1952_53_0025). Přejmenováno z holého „Tatra Kolín" na „Tatra Kolín B" (D21 striktně — kolegova nedůslednost). || Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0075</t>
+          <t>CLUB_S2005_06_0081</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HC Tábor</t>
+          <t>HC Žďár nad Sázavou</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HC Tábor</t>
+          <t>HC Žďár nad Sázavou</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -20001,34 +20252,34 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0077</t>
+          <t>CLUB_S2004_05_0081</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>VTJ Tábor byl statutárně "B" tým Dukly Jihlava, a proto se nemohl ucházet o účast v 1. CHL. || DA = Dum armady. Almanach: DA Otava (PDA Tabor?) - vztah PDA. || Oprava city dle D33 (04/2026): "Tábor" -&gt; prazdne (DA/PDA bez mesta v nazvu = city vzdy prazdne). || DA Otava 54/55 (30_Jihočeský). 1954 prejmenovani PDA -&gt; DA Otava (Otava = reka u Tabora). Vojensky klub Tábor: PDA / DA Otava / Dukla Tábor (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: PDA Tábor (1952-53, Pred Dukla armada / Posadkove dum armady) -&gt; DA Otava (1954-1956, Dum armady Otava - reka u Tabora) -&gt; Dukla Tábor (DA Otava) (1956-57+) -&gt; Dukla Tábor (1957-58) -&gt; konec po 1957/58 (almanach 58/59, 59/60 neobsahuje vojensky klub v Tábore). POZN: Po obnoveni VTJ Tábor (1970-1993) jako B-tym Dukly Jihlava, v 1993 fuze s civilnim Vodni stavby Tábor = HC VS VTJ -&gt; vojaci konec (Pavlovo: 'pak chvíli společná a pak vojáci konec'). city Tábor. Samostatny od hlavniho civilniho chain HC Tábor. || Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Hlavni chain: DSK Tábor (1921) -&gt; Sokol -&gt; Spartak Tábor -&gt; Tatran Tábor -&gt; Dukla Tábor (vojensky paralelni) -&gt; HC Tábor. **DA Otava** (Doprava-arm Otava) = paralelni klub. Otava = reka, NE Otavany (Strakonice). city Tábor.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Tábor</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0076</t>
+          <t>CLUB_S2005_06_0083</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HC Nymburk</t>
+          <t>HC Šternberk</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HC Nymburk</t>
+          <t>HC Šternberk</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -20043,34 +20294,34 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0064</t>
+          <t>CLUB_S2004_05_0090</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Nymburk = TJ Lokomotiva Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **Lokomotiva** = železničárský klub (Nymburk = velky železničárský uzel ČSD). Nymburk je dnes druhe nejvetsi mesto okresu (po Pode bradech). Patterns: Sokol -&gt; Lokomotiva Nymburk. city Nymburk.</t>
+          <t>Smart fix prev: 51/52 0390 (neexistuje) → 0388. Oprava city z „Chronotechna Šternberk" na „Šternberk". Identity transition: 51/52 měl chybně „Sokol Chronotechnika" — opravený název „Chronotechna" (správný název závodu, potvrzeno Pavlem) — retroaktivně opraveno i v 51/52. || Šternberk = Dukla/Chronotechnika Šternberk (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Chronotechna = vyrobce hodinek. Dukla = vojensky. city Šternberk.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Nymburk</t>
+          <t>Šternberk</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0077</t>
+          <t>CLUB_S2005_06_0084</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HC ZVVZ Milevsko</t>
+          <t>HC Blansko</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HC ZVVZ Milevsko</t>
+          <t>HC Blansko</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -20085,34 +20336,34 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0078</t>
+          <t>CLUB_S2004_05_0087</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Spartak Milevsko = HC Milevsko 1934 (Wiki D42 - registr ustavy 04/2026). Chain SK Milevsko (1934) -&gt; Sokol -&gt; Spartak -&gt; ZVVZ. city Milevsko.</t>
+          <t>Blansko = Spartak DZ Blansko (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. DZ = podnik. city Blansko.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Milevsko</t>
+          <t>Metra Blansko</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0078</t>
+          <t>CLUB_S2005_06_0085</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HC Pelhřimov</t>
+          <t>HC Orlová</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HC Pelhřimov</t>
+          <t>HC Orlová</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -20127,34 +20378,34 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0080</t>
+          <t>CLUB_S2004_05_0088</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Spartak Pelhřimov = Ledni Medvedi Pelhřimov (Wiki D42 - registr ustavy 04/2026). Klub od 22.11.1932 (HCP). city Pelhřimov.</t>
+          <t>A-tým Slovan Orlová. Oprava city: „Slovan Orlová" → „Orlová". Slovan a VHŠ Orlová = dva různé kluby (potvrzeno Pavlem 04/2026). Bez vazby na 52/53 0463 (Orlová Zimní důl) — samostatný. || Orlová = HC Orli Orlová (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Orlová.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Agrostroj Pelhřimov</t>
+          <t>Orlová</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0079</t>
+          <t>CLUB_S2005_06_0086</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HC Strakonice</t>
+          <t>HC Nový Jičín</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HC Strakonice</t>
+          <t>HC Nový Jičín</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -20169,34 +20420,34 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0076</t>
+          <t>CLUB_S2004_05_0093</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>DSO Jiskra Strakonice — DSO prefix ponechán almanachově (D35). Jiný klub od DSO Spartak Strakonice (CLUB_S1953_54_0139). || DSO Jiskra Strakonice 53/54. Strakonice = Spartak ČZ Strakonice (Wiki D42 - Pavlovo 04/2026). Strakonice -&gt; Fezko -&gt; ČZ -&gt; DSO Spartak/Jiskra (53/54+) -&gt; Spartak ČZ (57/58+). city Strakonice. || Strakonice = HC Strakonice (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Sokol Strakonice -&gt; Fezko Strakonice (textilni podnik, autopotahy) -&gt; ČZ Strakonice (Ceske zavody motocyklove) -&gt; HC Strakonice. city Strakonice.</t>
+          <t>Jičín (Wiki - registr ustavy 04/2026). Východocesky/Královéhradecky kraj. city Jičín. || Nový Jičín = HK Nový Jičín (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. liga. city Nový Jičín.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Strakonice</t>
+          <t>Nový Jičín</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0080</t>
+          <t>CLUB_S2005_06_0087</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HC Kolín</t>
+          <t>HC Valašské Meziříčí</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HC Kolín</t>
+          <t>HC Valašské Meziříčí</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -20211,34 +20462,34 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0084</t>
+          <t>CLUB_S2004_05_0097</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Smart fix prev: chybělo → 51/52 0042 (Tatra Kolín). Pravděpodobně B-tým Tatra Kolín (CLUB_S1952_53_0025), ale almanach má A-tým bez B suffixu — kolegova nepreciznnost. || B-tým Tatra Kolín (CLUB_S1952_53_0025). Přejmenováno z holého „Tatra Kolín" na „Tatra Kolín B" (D21 striktně — kolegova nedůslednost). || Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín.</t>
+          <t>Odstranění suffixu „A" (kolegova nedůslednost). Rozšíření „Val.Meziříčí" → „Valašské Meziříčí" (plný název v clean i city). || PS Valašské Meziříčí 52/53. PS = Poz.stavby? Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Valašské Meziříčí = mesto v Zlinsky kraji (Gottwaldovský/Zlinsky), Vsetinsky/Roznovsky region. Tatran Val.Meziříčí, PS, Tesla Val.Meziříčí. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || PS Valašské Meziříčí 52/53. PS = Poz.stavby. Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Mesto v Zlinsky kraji, Vsetinsky region. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || Valašské Meziříčí = HC Bobři Valašské Meziříčí (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Zlinsky kraj. Tesla Valašské Meziříčí (podnik) -&gt; PS Valašské Meziříčí (Pozemni stavby) -&gt; TJ -&gt; Bobri. POZOR: NE Velke Mezirici (Vysocina). city Valašské Meziříčí.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Kolín</t>
+          <t>Valašské Meziříčí</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0081</t>
+          <t>CLUB_S2005_06_0088</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HC Žďár nad Sázavou</t>
+          <t>HC Šumperk</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HC Žďár nad Sázavou</t>
+          <t>HC Šumperk</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -20253,34 +20504,34 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0081</t>
+          <t>CLUB_S2004_05_0094</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>city ✓ (DSO Baník Šumperk → Šumperk, DSO prefix éry, D28). || Šumperk = DRACI PARS Šumperk (Wiki - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. - Draci Šumperk. Pars = puvodni podnik. Patterns: Sokol Sumperk, Spartak Sumperk. city Šumperk.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Žďár nad Sázavou</t>
+          <t>Šumperk</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0083</t>
+          <t>CLUB_S2005_06_0089</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HC Šternberk</t>
+          <t>HC Velká Bíteš</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HC Šternberk</t>
+          <t>HC Velká Bíteš</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -20295,34 +20546,34 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0090</t>
+          <t>CLUB_S2004_05_0082</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Smart fix prev: 51/52 0390 (neexistuje) → 0388. Oprava city z „Chronotechna Šternberk" na „Šternberk". Identity transition: 51/52 měl chybně „Sokol Chronotechnika" — opravený název „Chronotechna" (správný název závodu, potvrzeno Pavlem) — retroaktivně opraveno i v 51/52. || Šternberk = Dukla/Chronotechnika Šternberk (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Chronotechna = vyrobce hodinek. Dukla = vojensky. city Šternberk.</t>
+          <t>Velká Bíteš = Sokol/Spartak Velká Bíteš (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sazavou). city Velká Bíteš.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Šternberk</t>
+          <t>Velká Bíteš</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0084</t>
+          <t>CLUB_S2005_06_0090</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HC Blansko</t>
+          <t>SHK Hodonín</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HC Blansko</t>
+          <t>SHK Hodonín</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -20337,34 +20588,34 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0087</t>
+          <t>CLUB_S2004_05_0092</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Blansko = Spartak DZ Blansko (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. DZ = podnik. city Blansko.</t>
+          <t>Hodonín = SHK Hodonín (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: ŠK Hodonín. **SHK** = Sportovni hokejovy klub. city Hodonín.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Metra Blansko</t>
+          <t>SHK Hodonín</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0085</t>
+          <t>CLUB_S2005_06_0091</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HC Orlová</t>
+          <t>HC Zubr Přerov</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HC Orlová</t>
+          <t>HC Zubr Přerov</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -20379,34 +20630,34 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0088</t>
+          <t>CLUB_S2004_05_0095</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>A-tým Slovan Orlová. Oprava city: „Slovan Orlová" → „Orlová". Slovan a VHŠ Orlová = dva různé kluby (potvrzeno Pavlem 04/2026). Bez vazby na 52/53 0463 (Orlová Zimní důl) — samostatný. || Orlová = HC Orli Orlová (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. city Orlová.</t>
+          <t>Oprava city: „Meopta Přerov" → „Přerov" (Meopta = závod optiky). || Meopta Přerov 52/53 (20_Olomoucký okresni). KLICOVE - PRVNI vyskyt jmena Meopta v almanachu (predchudce 1953 oficialniho prejmenovani). Přerov = HC Zubr Přerov (Wiki D42 - screenshot Pavlovo 04/2026). Genealogie: 1928 SK Přerov (Sportovní klub Přerov) -&gt; Sokol Přerov / Slavia Přerov (1948-52, sokol/civilni linie) -&gt; 1953 TJ Spartak Meopta Přerov (Meopta = znamy opticky podnik v Přerově) -&gt; 1975 TJ Meochema Přerov -&gt; 1995 HC Přerov -&gt; 2000 HC Minor 2000 Přerov -&gt; 2006 HC Zubr Přerov (dnes). Patterns: Sokol Přerov, ZSJ Slavia Přerov, Sokol Slavia Přerov, Meopta Přerov, Spartak Meopta Přerov, TJ Meopta Přerov, Přerovské strojírny (paralelni - viz nize). POZOR: 'Přerov nad Labem' (Polabí, Středočeský sheet) je JINE MESTO! Meopta = znamy opticky podnik v Přerově (po 1990 Meopta-optika). city Přerov. || Meopta Přerov 52/53 (20_Olomoucký). KLICOVY ROK 1952 -&gt; Meopta (opticke pristroje). Přerov = HC ZUBR Přerov (Wiki D42 + hokej.cz history - 04/2026). Genealogie: SK Přerov (listopad 1928) -&gt; Sokol Přerov (1948) -&gt; ZSJ Slavia ROL Přerov (1949-50, ROL = podnik?) -&gt; Sokol Slavia Přerov (1951) -&gt; Meopta Přerov (1952+, podnik MEOPTA = opticke pristroje, MS dorost 49/50!) -&gt; Spartak Meopta Přerov (1953-1975, DSO reforma) -&gt; TJ Meochema Přerov (1975-1995) -&gt; HC Přerov (1995) -&gt; HC Minor 2000 Přerov (2000-2006) -&gt; HC ZUBR Přerov (2006-dnes). KLICOVE: Přerov 1955/56 vitez krajskeho preboru, postup do divize. Patterns: Sokol Přerov, ZSJ Slavia Přerov, Sokol Slavia, Meopta Přerov, Spartak Meopta, TJ Meopta. city Přerov. POZOR: NE Přerov nad Labem (Stredocesky)! || Přerov = HC Zubr Přerov (Wiki D42 - registr ustavy 04/2026). Vsechny prerovske kluby. Hlavni chain: SK Přerov (1928) -&gt; Sokol/Slavia -&gt; ZSJ Meopta -&gt; Spartak Meopta Přerov -&gt; TJ Meopta -&gt; HC Zubr Přerov. Meopta = opticky podnik, ROL = potravinarsky. MEOCHEMA Přerov 1975-1995 = fuze Meopta+Chemia. city Přerov.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Orlová</t>
+          <t>Přerov</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0086</t>
+          <t>CLUB_S2005_06_0092</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HC Nový Jičín</t>
+          <t>HC Kroměříž</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HC Nový Jičín</t>
+          <t>HC Kroměříž</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -20421,34 +20672,34 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0093</t>
+          <t>CLUB_S2004_05_0091</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Jičín (Wiki - registr ustavy 04/2026). Východocesky/Královéhradecky kraj. city Jičín. || Nový Jičín = HK Nový Jičín (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. liga. city Nový Jičín.</t>
+          <t>B-tym Spartak Kroměříž (PAL = závod). clean: II -&gt; B. Oprava city: "PAL Kroměříž" -&gt; "Kroměříž". || Kroměříž = HK Kroměříž (Wiki - registr ustavy 04/2026). Severomoravsky/Zlinsky kraj. Mestske vyznamne - HK Kromeriz Patterns: PAL Kroměříž (podnik), HK Kromeriz. city Kroměříž.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Nový Jičín</t>
+          <t>Kroměříž</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0087</t>
+          <t>CLUB_S2005_06_0093</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HC Valašské Meziříčí</t>
+          <t>HC Uničov</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HC Valašské Meziříčí</t>
+          <t>HC Uničov</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -20463,286 +20714,296 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0097</t>
+          <t>CLUB_S2004_05_0096</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Odstranění suffixu „A" (kolegova nedůslednost). Rozšíření „Val.Meziříčí" → „Valašské Meziříčí" (plný název v clean i city). || PS Valašské Meziříčí 52/53. PS = Poz.stavby? Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Valašské Meziříčí = mesto v Zlinsky kraji (Gottwaldovský/Zlinsky), Vsetinsky/Roznovsky region. Tatran Val.Meziříčí, PS, Tesla Val.Meziříčí. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || PS Valašské Meziříčí 52/53. PS = Poz.stavby. Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Mesto v Zlinsky kraji, Vsetinsky region. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || Valašské Meziříčí = HC Bobři Valašské Meziříčí (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Zlinsky kraj. Tesla Valašské Meziříčí (podnik) -&gt; PS Valašské Meziříčí (Pozemni stavby) -&gt; TJ -&gt; Bobri. POZOR: NE Velke Mezirici (Vysocina). city Valašské Meziříčí.</t>
+          <t>Uničov = TJ Spartak Uničov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Uničov.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Valašské Meziříčí</t>
+          <t>Uničov</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0088</t>
+          <t>CLUB_S2005_06_0094</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HC Šumperk</t>
+          <t>HC Junior Mělník</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HC Šumperk</t>
+          <t>HC Junior Mělník</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>30_2liga</t>
+          <t>30_Středočeský</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>L30</t>
+          <t>L40</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0094</t>
+          <t>CLUB_S2004_05_0100</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>city ✓ (DSO Baník Šumperk → Šumperk, DSO prefix éry, D28). || Šumperk = DRACI PARS Šumperk (Wiki - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. - Draci Šumperk. Pars = puvodni podnik. Patterns: Sokol Sumperk, Spartak Sumperk. city Šumperk.</t>
+          <t>Mělník = HC Junior Mělník (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. city Mělník.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Šumperk</t>
+          <t>Junior Mělník</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0089</t>
+          <t>CLUB_S2005_06_0095</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HC Velká Bíteš</t>
+          <t>SKLH Benešov</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HC Velká Bíteš</t>
+          <t>SKLH Benešov</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>30_2liga</t>
+          <t>30_Středočeský</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>L30</t>
+          <t>L40</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0082</t>
+          <t>CLUB_S2004_05_0099</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Velká Bíteš = Sokol/Spartak Velká Bíteš (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sazavou). city Velká Bíteš.</t>
+          <t>Benešov = SKLH Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **SKLH** = Sportovni klub ledniho hokeje. city Benešov.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Velká Bíteš</t>
+          <t>SKLH Benešov</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0090</t>
+          <t>CLUB_S2005_06_0096</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SHK Hodonín</t>
+          <t>HC Slavoj Velké Popovice</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SHK Hodonín</t>
+          <t>HC Slavoj Velké Popovice</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>30_2liga</t>
+          <t>30_Středočeský</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>L30</t>
+          <t>L40</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0092</t>
+          <t>CLUB_S2004_05_0102</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Hodonín = SHK Hodonín (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: ŠK Hodonín. **SHK** = Sportovni hokejovy klub. city Hodonín.</t>
+          <t>Pivovar Velké Popovice – Sokol Voděrady 50/51 joint Velké Popovice = JINÉ MĚSTO (obec u Říčan, Pivovar Kozel). Wiki D42 - Pavlovo upresneni 04/2026. city Velké Popovice (NIKDY Voděrady). || Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>SHK Hodonín</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0091</t>
+          <t>CLUB_S2005_06_0097</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HC Zubr Přerov</t>
+          <t>HC Jesenice</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HC Zubr Přerov</t>
+          <t>HC Jesenice</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>30_2liga</t>
+          <t>30_Středočeský</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>L30</t>
+          <t>L40</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0095</t>
+          <t>CLUB_S2004_05_0103</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Oprava city: „Meopta Přerov" → „Přerov" (Meopta = závod optiky). || Meopta Přerov 52/53 (20_Olomoucký okresni). KLICOVE - PRVNI vyskyt jmena Meopta v almanachu (predchudce 1953 oficialniho prejmenovani). Přerov = HC Zubr Přerov (Wiki D42 - screenshot Pavlovo 04/2026). Genealogie: 1928 SK Přerov (Sportovní klub Přerov) -&gt; Sokol Přerov / Slavia Přerov (1948-52, sokol/civilni linie) -&gt; 1953 TJ Spartak Meopta Přerov (Meopta = znamy opticky podnik v Přerově) -&gt; 1975 TJ Meochema Přerov -&gt; 1995 HC Přerov -&gt; 2000 HC Minor 2000 Přerov -&gt; 2006 HC Zubr Přerov (dnes). Patterns: Sokol Přerov, ZSJ Slavia Přerov, Sokol Slavia Přerov, Meopta Přerov, Spartak Meopta Přerov, TJ Meopta Přerov, Přerovské strojírny (paralelni - viz nize). POZOR: 'Přerov nad Labem' (Polabí, Středočeský sheet) je JINE MESTO! Meopta = znamy opticky podnik v Přerově (po 1990 Meopta-optika). city Přerov. || Meopta Přerov 52/53 (20_Olomoucký). KLICOVY ROK 1952 -&gt; Meopta (opticke pristroje). Přerov = HC ZUBR Přerov (Wiki D42 + hokej.cz history - 04/2026). Genealogie: SK Přerov (listopad 1928) -&gt; Sokol Přerov (1948) -&gt; ZSJ Slavia ROL Přerov (1949-50, ROL = podnik?) -&gt; Sokol Slavia Přerov (1951) -&gt; Meopta Přerov (1952+, podnik MEOPTA = opticke pristroje, MS dorost 49/50!) -&gt; Spartak Meopta Přerov (1953-1975, DSO reforma) -&gt; TJ Meochema Přerov (1975-1995) -&gt; HC Přerov (1995) -&gt; HC Minor 2000 Přerov (2000-2006) -&gt; HC ZUBR Přerov (2006-dnes). KLICOVE: Přerov 1955/56 vitez krajskeho preboru, postup do divize. Patterns: Sokol Přerov, ZSJ Slavia Přerov, Sokol Slavia, Meopta Přerov, Spartak Meopta, TJ Meopta. city Přerov. POZOR: NE Přerov nad Labem (Stredocesky)! || Přerov = HC Zubr Přerov (Wiki D42 - registr ustavy 04/2026). Vsechny prerovske kluby. Hlavni chain: SK Přerov (1928) -&gt; Sokol/Slavia -&gt; ZSJ Meopta -&gt; Spartak Meopta Přerov -&gt; TJ Meopta -&gt; HC Zubr Přerov. Meopta = opticky podnik, ROL = potravinarsky. MEOCHEMA Přerov 1975-1995 = fuze Meopta+Chemia. city Přerov.</t>
+          <t>Jesenice = TJ Sokol Jesenice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Praha-zapad). city Jesenice.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Přerov</t>
+          <t>Jesenice</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0092</t>
+          <t>CLUB_S2005_06_0098</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HC Kroměříž</t>
+          <t>EarthForce Příbram</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HC Kroměříž</t>
+          <t>EarthForce Příbram (N)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>30_2liga</t>
+          <t>30_Středočeský</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>L30</t>
+          <t>L40</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0091</t>
+          <t>CLUB_S2004_05_0110</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>B-tym Spartak Kroměříž (PAL = závod). clean: II -&gt; B. Oprava city: "PAL Kroměříž" -&gt; "Kroměříž". || Kroměříž = HK Kroměříž (Wiki - registr ustavy 04/2026). Severomoravsky/Zlinsky kraj. Mestske vyznamne - HK Kromeriz Patterns: PAL Kroměříž (podnik), HK Kromeriz. city Kroměříž.</t>
+          <t>Příbram = HC Baník Příbram (Wiki + hcpribram.cz historie - registr ustavy 04/2026). KLUB ZALOZEN 1933 jako LK Příbram. Genealogie: LK Příbram (1933) -&gt; SK Horymír (slouceni 1944/45) -&gt; 1951 Banský inspektorat Jachymovskych dolu (URANOVE DOLY!) city Příbram.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Kroměříž</t>
+          <t>Příbram</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0093</t>
+          <t>CLUB_S2005_06_0099</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HC Uničov</t>
+          <t>HC Žabonosy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HC Uničov</t>
+          <t>HC Žabonosy (N)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>30_2liga</t>
+          <t>30_Středočeský</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>L30</t>
+          <t>L40</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0096</t>
+          <t>CLUB_S2004_05_0116</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Uničov = TJ Spartak Uničov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (okres Olomouc). city Uničov.</t>
+          <t>Žabonosy = Sokol Žabonosy (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). city Žabonosy.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Uničov</t>
+          <t>Žabonosy</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0094</t>
+          <t>CLUB_S2005_06_0100</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HC Junior Mělník</t>
+          <t>HC Rakovník</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HC Junior Mělník</t>
+          <t>HC Rakovník</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -20757,34 +21018,34 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0100</t>
+          <t>CLUB_S2004_05_0101</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mělník = HC Junior Mělník (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. city Mělník.</t>
+          <t>Rakovník = HC Rakovník (Wiki - registr ustavy 04/2026). Stredocesky klub. Historicky stacheny pod krajskymi soutezemi. letech. Hraje krajske souteze. Patterns: Spartak Rakovník, Banik Rakovník. city Rakovník. || Všetaty = TJ Sokol Všetaty (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Mělník). Pripsano 'Všetaty u Prahy' v 50. letech. city Všetaty.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Junior Mělník</t>
+          <t>Rakovník</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0095</t>
+          <t>CLUB_S2005_06_0101</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SKLH Benešov</t>
+          <t>HOSK Dobříš</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SKLH Benešov</t>
+          <t>HOSK Dobříš</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -20799,34 +21060,34 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0099</t>
+          <t>CLUB_S2004_05_0104</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Benešov = SKLH Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **SKLH** = Sportovni klub ledniho hokeje. city Benešov.</t>
+          <t>Dobříš = HOSK Dobříš (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Příbram). **HOSK** = Hokejovy oddil sportovniho klubu. city Dobříš.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>SKLH Benešov</t>
+          <t>HOSK Dobříš</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0096</t>
+          <t>CLUB_S2005_06_0102</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HC Slavoj Velké Popovice</t>
+          <t>SK Černošice</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HC Slavoj Velké Popovice</t>
+          <t>SK Černošice (N)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -20834,6 +21095,11 @@
           <t>30_Středočeský</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>L40</t>
@@ -20841,34 +21107,34 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0102</t>
+          <t>CLUB_S2004_05_0052</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Pivovar Velké Popovice – Sokol Voděrady 50/51 joint Velké Popovice = JINÉ MĚSTO (obec u Říčan, Pivovar Kozel). Wiki D42 - Pavlovo upresneni 04/2026. city Velké Popovice (NIKDY Voděrady). || Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Černošice = Sokol Černošice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Praha-zapad). city Černošice.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Velké Popovice</t>
+          <t>Černošice</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0097</t>
+          <t>CLUB_S2005_06_0103</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HC Jesenice</t>
+          <t>HK Kralupy nad Vltavou</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HC Jesenice</t>
+          <t>HK Kralupy nad Vltavou (N)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -20876,6 +21142,11 @@
           <t>30_Středočeský</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>L40</t>
@@ -20883,34 +21154,34 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0103</t>
+          <t>CLUB_S2004_05_0117</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Jesenice = TJ Sokol Jesenice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Praha-zapad). city Jesenice.</t>
+          <t>Po skončení soutěže převzal licenci na 1. ligu od HC Hodonín. || Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Jesenice</t>
+          <t>Kralupy nad Vltavou</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0098</t>
+          <t>CLUB_S2005_06_0104</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EarthForce Příbram</t>
+          <t>TJ Felbabka</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EarthForce Příbram (N)</t>
+          <t>TJ Felbabka</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -20918,11 +21189,6 @@
           <t>30_Středočeský</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>L40</t>
@@ -20930,34 +21196,34 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0110</t>
+          <t>CLUB_S2004_05_0105</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Příbram = HC Baník Příbram (Wiki + hcpribram.cz historie - registr ustavy 04/2026). KLUB ZALOZEN 1933 jako LK Příbram. Genealogie: LK Příbram (1933) -&gt; SK Horymír (slouceni 1944/45) -&gt; 1951 Banský inspektorat Jachymovskych dolu (URANOVE DOLY!) city Příbram.</t>
+          <t>Felbabka = TJ Sokol Felbabka (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). 'BER' = Beroun skupina. city Felbabka.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Felbabka</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0099</t>
+          <t>CLUB_S2005_06_0105</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HC Žabonosy</t>
+          <t>TJ SC Kolín B</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HC Žabonosy (N)</t>
+          <t>TJ SC Kolín B (N)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -20975,36 +21241,31 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0116</t>
-        </is>
-      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Žabonosy = Sokol Žabonosy (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). city Žabonosy.</t>
+          <t>Kolín = TJ SC Kolín B (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **SC** = Sportovny club. 'B' = druzstvo B. city Kolín.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Žabonosy</t>
+          <t>SC Kolín B</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0100</t>
+          <t>CLUB_S2005_06_0106</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HC Rakovník</t>
+          <t>HC Roudnice nad Labem (UnL)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HC Rakovník</t>
+          <t>HC Roudnice nad Labem (UnL)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -21019,34 +21280,34 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0101</t>
+          <t>CLUB_S2004_05_0119</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Rakovník = HC Rakovník (Wiki - registr ustavy 04/2026). Stredocesky klub. Historicky stacheny pod krajskymi soutezemi. letech. Hraje krajske souteze. Patterns: Spartak Rakovník, Banik Rakovník. city Rakovník. || Všetaty = TJ Sokol Všetaty (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Mělník). Pripsano 'Všetaty u Prahy' v 50. letech. city Všetaty.</t>
+          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Rakovník</t>
+          <t>Roudnice nad Labem</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0101</t>
+          <t>CLUB_S2005_06_0107</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HOSK Dobříš</t>
+          <t>Spartak Příbram</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HOSK Dobříš</t>
+          <t>Spartak Příbram</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -21061,34 +21322,34 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0104</t>
+          <t>CLUB_S2004_05_0110</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Dobříš = HOSK Dobříš (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Příbram). **HOSK** = Hokejovy oddil sportovniho klubu. city Dobříš.</t>
+          <t>Příbram = HC Baník Příbram (Wiki + hcpribram.cz historie - registr ustavy 04/2026). KLUB ZALOZEN 1933 jako LK Příbram. Genealogie: LK Příbram (1933) -&gt; SK Horymír (slouceni 1944/45) -&gt; 1951 Banský inspektorat Jachymovskych dolu (URANOVE DOLY!) city Příbram.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>HOSK Dobříš</t>
+          <t>Příbram</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0102</t>
+          <t>CLUB_S2005_06_0108</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SK Černošice</t>
+          <t>SKLH Benešov B</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SK Černošice (N)</t>
+          <t>SKLH Benešov B (S)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -21098,7 +21359,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -21108,34 +21369,34 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0052</t>
+          <t>CLUB_S2004_05_0099</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Černošice = Sokol Černošice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Praha-zapad). city Černošice.</t>
+          <t>Benešov = SKLH Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **SKLH** = Sportovni klub ledniho hokeje. city Benešov.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Černošice</t>
+          <t>SKLH Benešov</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0103</t>
+          <t>CLUB_S2005_06_0109</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HK Kralupy nad Vltavou</t>
+          <t>HC Zlonice</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HK Kralupy nad Vltavou (N)</t>
+          <t>HC Zlonice</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -21143,11 +21404,6 @@
           <t>30_Středočeský</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>L40</t>
@@ -21155,34 +21411,34 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0117</t>
+          <t>CLUB_S2004_05_0118</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Po skončení soutěže převzal licenci na 1. ligu od HC Hodonín. || Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou.</t>
+          <t>Zlonice = TJ Tatran Zlonice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Zlonice.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Kralupy nad Vltavou</t>
+          <t>Zlonice</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0104</t>
+          <t>CLUB_S2005_06_0110</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TJ Felbabka</t>
+          <t>HC 1988 Kladno</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TJ Felbabka</t>
+          <t>HC 1988 Kladno (S)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -21190,6 +21446,11 @@
           <t>30_Středočeský</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>L40</t>
@@ -21197,34 +21458,34 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0105</t>
+          <t>CLUB_S2004_05_0107</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Felbabka = TJ Sokol Felbabka (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). 'BER' = Beroun skupina. city Felbabka.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZSJ SONP Kladno → Sokol Spojené ocelárny → DSO Baník Kladno SONP. 52/53 přejmenování (D28). || Baník Kladno 52/53 (10_liga). KLÍČOVÝ ROK přejmenování - DSO Baník Kladno SONP od 1953. Kladno = Rytíři Kladno (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: HOSK Kladno (1924, Hokejovy odbor SK Kladno) -&gt; TJ Sokol Kladno (1948) -&gt; TJ Sokol SONP Kladno (1949, SONP = Spojené ocelárny narodni podnik) -&gt; DSO Baník Kladno SONP (1953) -&gt; TJ SONP Kladno (1958) -&gt; TJ Poldi SONP Kladno (1977) -&gt; TJ Poldi Kladno (1989) -&gt; HC Kladno / Poldi / Velvana / Vagnerplast / Rabat / GEUS OKNA /... -&gt; Rytíři Kladno (2011-dnes). SONP = Spojene ocelarny narodni podnik (Poldi). city Kladno. Patterns: Sokol SONP Kladno, ZSJ SONP Kladno, SONP Kladno, Baník Kladno, Baník SONP Kladno, Poldi Kladno. || Kladno = Rytíři Kladno (Wiki D42 - registr ustavy 04/2026). Vsechny kladenske kluby chain HOSK Kladno (1924) -&gt; Sokol -&gt; ZSJ SONP (1949+, SONP = Spojene ocelarny np) -&gt; Banik SONP -&gt; Banik Poldi -&gt; Poldi SONP -&gt; Poldi Kladno -&gt; HC Kladno -&gt; Rytiri Kladno. SONP a Poldi jsou kladenske ocelarny - nazvy klubu odrazely podnikove vazby. city Kladno.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Felbabka</t>
+          <t>Kladno</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0105</t>
+          <t>CLUB_S2005_06_0111</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TJ SC Kolín B</t>
+          <t>Hvězda Kladno</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TJ SC Kolín B (N)</t>
+          <t>Hvězda Kladno</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -21232,41 +21493,41 @@
           <t>30_Středočeský</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0112</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Kolín = TJ SC Kolín B (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **SC** = Sportovny club. 'B' = druzstvo B. city Kolín.</t>
+          <t>Kladno = TJ Hvězda Kladno (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **Hvězda** = pojmenovani po Rude hvezde (SNB). city Kladno.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>SC Kolín B</t>
+          <t>Hvězda Kladno</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0106</t>
+          <t>CLUB_S2005_06_0112</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem (UnL)</t>
+          <t>HK Králův Dvůr</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem (UnL)</t>
+          <t>HK Králův Dvůr</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -21281,34 +21542,34 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0119</t>
+          <t>CLUB_S2004_05_0113</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Královodvorské železárny. city Králův Dvůr.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Roudnice nad Labem</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0107</t>
+          <t>CLUB_S2005_06_0113</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Spartak Příbram</t>
+          <t>Stadion Kutná Hora B</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spartak Příbram</t>
+          <t>Stadion Kutná Hora B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -21323,34 +21584,34 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0110</t>
+          <t>CLUB_S2004_05_0121</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Příbram = HC Baník Příbram (Wiki + hcpribram.cz historie - registr ustavy 04/2026). KLUB ZALOZEN 1933 jako LK Příbram. Genealogie: LK Příbram (1933) -&gt; SK Horymír (slouceni 1944/45) -&gt; 1951 Banský inspektorat Jachymovskych dolu (URANOVE DOLY!) city Příbram.</t>
+          <t>Smart fix prev: chybělo → 50/51 0097 (ČKD Kutná Hora). Klub v 51/52 nehrál (mezera). Pozn.: Pavlovo zjištění 04/2026 — 50/51 0097 má v parentézi chybně „Viktoria Sedlec" (Sedlec je jiný klub, ne předchůdce). || Kutná Hora = HC Sparta/Dynamo Kutná Hora (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Hlavni chain: Sparta KH -&gt; Sokol -&gt; Dynamo Kutná Hora -&gt; HC Kutná Hora. UNESCO mesto. city Kutná Hora.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kutná Hora</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0108</t>
+          <t>CLUB_S2005_06_0114</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SKLH Benešov B</t>
+          <t>SSC Říčany</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SKLH Benešov B (S)</t>
+          <t>SSC Říčany</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -21358,11 +21619,6 @@
           <t>30_Středočeský</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>L40</t>
@@ -21370,34 +21626,34 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0099</t>
+          <t>CLUB_S2004_05_0122</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Benešov = SKLH Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **SKLH** = Sportovni klub ledniho hokeje. city Benešov.</t>
+          <t>Říčany = TJ SSC Říčany (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Praha-vychod). **SSC** = Stredisko sportovni cinnosti. Patterns: Sokol Říčany -&gt; SSC Říčany. city Říčany.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>SKLH Benešov</t>
+          <t>SSC Říčany</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0109</t>
+          <t>CLUB_S2005_06_0115</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HC Zlonice</t>
+          <t>HC Dobříš</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HC Zlonice</t>
+          <t>HC Dobříš</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -21412,34 +21668,34 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0118</t>
+          <t>CLUB_S2004_05_0115</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Zlonice = TJ Tatran Zlonice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Zlonice.</t>
+          <t>Jiskra Dobříš (Příbram, jako 58/59 0111). city OK. || Dobříš = Jiskra Dobříš (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). city Dobříš.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Zlonice</t>
+          <t>Dobříš</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0110</t>
+          <t>CLUB_S2005_06_0116</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HC 1988 Kladno</t>
+          <t>VHS HC Vodní Lvi Benešov se sloučil se SKLH Benešov</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HC 1988 Kladno (S)</t>
+          <t>VHS HC Vodní Lvi Benešov se sloučil se SKLH Benešov</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -21447,11 +21703,6 @@
           <t>30_Středočeský</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>L40</t>
@@ -21459,34 +21710,34 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0107</t>
+          <t>CLUB_S2004_05_0099</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZSJ SONP Kladno → Sokol Spojené ocelárny → DSO Baník Kladno SONP. 52/53 přejmenování (D28). || Baník Kladno 52/53 (10_liga). KLÍČOVÝ ROK přejmenování - DSO Baník Kladno SONP od 1953. Kladno = Rytíři Kladno (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: HOSK Kladno (1924, Hokejovy odbor SK Kladno) -&gt; TJ Sokol Kladno (1948) -&gt; TJ Sokol SONP Kladno (1949, SONP = Spojené ocelárny narodni podnik) -&gt; DSO Baník Kladno SONP (1953) -&gt; TJ SONP Kladno (1958) -&gt; TJ Poldi SONP Kladno (1977) -&gt; TJ Poldi Kladno (1989) -&gt; HC Kladno / Poldi / Velvana / Vagnerplast / Rabat / GEUS OKNA /... -&gt; Rytíři Kladno (2011-dnes). SONP = Spojene ocelarny narodni podnik (Poldi). city Kladno. Patterns: Sokol SONP Kladno, ZSJ SONP Kladno, SONP Kladno, Baník Kladno, Baník SONP Kladno, Poldi Kladno. || Kladno = Rytíři Kladno (Wiki D42 - registr ustavy 04/2026). Vsechny kladenske kluby chain HOSK Kladno (1924) -&gt; Sokol -&gt; ZSJ SONP (1949+, SONP = Spojene ocelarny np) -&gt; Banik SONP -&gt; Banik Poldi -&gt; Poldi SONP -&gt; Poldi Kladno -&gt; HC Kladno -&gt; Rytiri Kladno. SONP a Poldi jsou kladenske ocelarny - nazvy klubu odrazely podnikove vazby. city Kladno.</t>
+          <t>Benešov = SKLH Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **SKLH** = Sportovni klub ledniho hokeje. city Benešov.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>SKLH Benešov</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0111</t>
+          <t>CLUB_S2005_06_0117</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hvězda Kladno</t>
+          <t>HC Roudnice nad Labem nesměla postoupit, kvůli příslušnosti k jinému kraji</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hvězda Kladno</t>
+          <t>HC Roudnice nad Labem nesměla postoupit, kvůli příslušnosti k jinému kraji</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -21501,39 +21752,39 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0112</t>
+          <t>CLUB_S2004_05_0137</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Kladno = TJ Hvězda Kladno (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **Hvězda** = pojmenovani po Rude hvezde (SNB). city Kladno.</t>
+          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Hvězda Kladno</t>
+          <t>Roudnice nad Labem</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0112</t>
+          <t>CLUB_S2005_06_0118</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HK Králův Dvůr</t>
+          <t>Lokomotiva Veselí nad Lužnicí</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HK Králův Dvůr</t>
+          <t>Lokomotiva Veselí nad Lužnicí</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>30_Středočeský</t>
+          <t>30_Jihočeský</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -21543,39 +21794,39 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0113</t>
+          <t>CLUB_S2004_05_0125</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Královodvorské železárny. city Králův Dvůr.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Králův Dvůr</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0113</t>
+          <t>CLUB_S2005_06_0119</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Stadion Kutná Hora B</t>
+          <t>OLH Spartak Soběslav</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Stadion Kutná Hora B</t>
+          <t>OLH Spartak Soběslav</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>30_Středočeský</t>
+          <t>30_Jihočeský</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -21585,39 +21836,39 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0121</t>
+          <t>CLUB_S2004_05_0127</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Smart fix prev: chybělo → 50/51 0097 (ČKD Kutná Hora). Klub v 51/52 nehrál (mezera). Pozn.: Pavlovo zjištění 04/2026 — 50/51 0097 má v parentézi chybně „Viktoria Sedlec" (Sedlec je jiný klub, ne předchůdce). || Kutná Hora = HC Sparta/Dynamo Kutná Hora (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Hlavni chain: Sparta KH -&gt; Sokol -&gt; Dynamo Kutná Hora -&gt; HC Kutná Hora. UNESCO mesto. city Kutná Hora.</t>
+          <t>Soběslav = TJ Spartak Soběslav (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Tabor). Patterns: TJ Spartak Lada Soběslav. city Soběslav.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Kutná Hora</t>
+          <t>Lada Soběslav</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0114</t>
+          <t>CLUB_S2005_06_0120</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SSC Říčany</t>
+          <t>HC Milevsko B</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SSC Říčany</t>
+          <t>HC Milevsko B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>30_Středočeský</t>
+          <t>30_Jihočeský</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -21627,39 +21878,39 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0122</t>
+          <t>CLUB_S2004_05_0078</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Říčany = TJ SSC Říčany (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Praha-vychod). **SSC** = Stredisko sportovni cinnosti. Patterns: Sokol Říčany -&gt; SSC Říčany. city Říčany.</t>
+          <t>Spartak Milevsko = HC Milevsko 1934 (Wiki D42 - registr ustavy 04/2026). Chain SK Milevsko (1934) -&gt; Sokol -&gt; Spartak -&gt; ZVVZ. city Milevsko.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>SSC Říčany</t>
+          <t>Milevsko</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0115</t>
+          <t>CLUB_S2005_06_0121</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HC Dobříš</t>
+          <t>Slavoj Český Krumlov</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HC Dobříš</t>
+          <t>Slavoj Český Krumlov</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>30_Středočeský</t>
+          <t>30_Jihočeský</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -21669,39 +21920,39 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0115</t>
+          <t>CLUB_S2004_05_0123</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Jiskra Dobříš (Příbram, jako 58/59 0111). city OK. || Dobříš = Jiskra Dobříš (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). city Dobříš.</t>
+          <t>Slavoj Český Krumlov. city OK. || Český Krumlov = Slavoj Český Krumlov (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. POZOR: NE Moravský Krumlov (Jihomoravsky). UNESCO mesto. city Český Krumlov.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Dobříš</t>
+          <t>Český Krumlov</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0116</t>
+          <t>CLUB_S2005_06_0122</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VHS HC Vodní Lvi Benešov se sloučil se SKLH Benešov</t>
+          <t>HC Jaguars Lipolec</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>VHS HC Vodní Lvi Benešov se sloučil se SKLH Benešov</t>
+          <t>HC Jaguars Lipolec</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>30_Středočeský</t>
+          <t>30_Jihočeský</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -21709,41 +21960,36 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0099</t>
-        </is>
-      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Benešov = SKLH Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **SKLH** = Sportovni klub ledniho hokeje. city Benešov.</t>
+          <t>Lipolec = HC Jaguars Lipolec (Wiki D42 - registr ustavy 04/2026). K overeni mesta. Post-revolucni anglicky nazev. city Lipolec.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>SKLH Benešov</t>
+          <t>Jaguars Lipolec</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0117</t>
+          <t>CLUB_S2005_06_0123</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem nesměla postoupit, kvůli příslušnosti k jinému kraji</t>
+          <t>TJ Hluboká nad Vltavou Knights</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem nesměla postoupit, kvůli příslušnosti k jinému kraji</t>
+          <t>TJ Hluboká nad Vltavou Knights</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>30_Středočeský</t>
+          <t>30_Jihočeský</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -21753,34 +21999,34 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0137</t>
+          <t>CLUB_S2004_05_0124</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
+          <t>B-tym Tatran Hluboká nad Vltavou. clean: II → B. Oprava city: "Hluboká" → "Hluboká nad Vltavou" (plný název). || Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Roudnice nad Labem</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0118</t>
+          <t>CLUB_S2005_06_0124</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lokomotiva Veselí nad Lužnicí</t>
+          <t>HC Vimperk</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lokomotiva Veselí nad Lužnicí</t>
+          <t>HC Vimperk</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21795,34 +22041,34 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0125</t>
+          <t>CLUB_S2004_05_0126</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj Vimperk. city ✓. || Slavoj Vimperk 54/55 (30_Jihočeský). 1955 prejmenovani na Jiskra (Wiki). Vimperk = HC Vimperk (Wiki D42 - Pavlovo upresneni 04/2026, hokej.cz). Genealogie: 1950 Slavoj OPK Vimperk (zalozeni, OPK = ?) -&gt; TJ Jiskra Vimperk (1955) -&gt; TJ Šumavan Vimperk (1962) -&gt; HC Vimperk (1992-dnes). Patterns: Slavoj Vimperk, Jiskra Vimperk. city Vimperk. POZN: Almanach 50/51-52/53 obsahuje pouze 'Vimperk' bez prefixu, patrne pred zalozenim Slavoj 1950 nebo prve roky Slavoj. || Vimperk = HC Vimperk (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. Hlavni chain: Sokol -&gt; Slavoj Vimperk -&gt; Jiskra Vimperk -&gt; HC Vimperk. city Vimperk.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Vimperk</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0119</t>
+          <t>CLUB_S2005_06_0125</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>OLH Spartak Soběslav</t>
+          <t>HC Tábor B – FeKS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>OLH Spartak Soběslav</t>
+          <t>HC Tábor B – FeKS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -21837,34 +22083,34 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0127</t>
+          <t>CLUB_S2004_05_0077</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Soběslav = TJ Spartak Soběslav (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Tabor). Patterns: TJ Spartak Lada Soběslav. city Soběslav.</t>
+          <t>VTJ Tábor byl statutárně "B" tým Dukly Jihlava, a proto se nemohl ucházet o účast v 1. CHL. || DA = Dum armady. Almanach: DA Otava (PDA Tabor?) - vztah PDA. || Oprava city dle D33 (04/2026): "Tábor" -&gt; prazdne (DA/PDA bez mesta v nazvu = city vzdy prazdne). || DA Otava 54/55 (30_Jihočeský). 1954 prejmenovani PDA -&gt; DA Otava (Otava = reka u Tabora). Vojensky klub Tábor: PDA / DA Otava / Dukla Tábor (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: PDA Tábor (1952-53, Pred Dukla armada / Posadkove dum armady) -&gt; DA Otava (1954-1956, Dum armady Otava - reka u Tabora) -&gt; Dukla Tábor (DA Otava) (1956-57+) -&gt; Dukla Tábor (1957-58) -&gt; konec po 1957/58 (almanach 58/59, 59/60 neobsahuje vojensky klub v Tábore). POZN: Po obnoveni VTJ Tábor (1970-1993) jako B-tym Dukly Jihlava, v 1993 fuze s civilnim Vodni stavby Tábor = HC VS VTJ -&gt; vojaci konec (Pavlovo: 'pak chvíli společná a pak vojáci konec'). city Tábor. Samostatny od hlavniho civilniho chain HC Tábor. || Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Hlavni chain: DSK Tábor (1921) -&gt; Sokol -&gt; Spartak Tábor -&gt; Tatran Tábor -&gt; Dukla Tábor (vojensky paralelni) -&gt; HC Tábor. **DA Otava** (Doprava-arm Otava) = paralelni klub. Otava = reka, NE Otavany (Strakonice). city Tábor.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Lada Soběslav</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0120</t>
+          <t>CLUB_S2005_06_0126</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HC Milevsko B</t>
+          <t>HC Velká Radouň</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>HC Milevsko B</t>
+          <t>HC Velká Radouň</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -21879,34 +22125,34 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0078</t>
+          <t>CLUB_S2004_05_0128</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Spartak Milevsko = HC Milevsko 1934 (Wiki D42 - registr ustavy 04/2026). Chain SK Milevsko (1934) -&gt; Sokol -&gt; Spartak -&gt; ZVVZ. city Milevsko.</t>
+          <t>Horní Radouň = TJ Sokol Horní Radouň (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). city Horní Radouň.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Milevsko</t>
+          <t>Horní Radouň</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0121</t>
+          <t>CLUB_S2005_06_0127</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Slavoj Český Krumlov</t>
+          <t>David servis České Budějovice</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Slavoj Český Krumlov</t>
+          <t>David servis České Budějovice</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -21921,34 +22167,34 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0123</t>
+          <t>CLUB_S2004_05_0129</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Slavoj Český Krumlov. city OK. || Český Krumlov = Slavoj Český Krumlov (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. POZOR: NE Moravský Krumlov (Jihomoravsky). UNESCO mesto. city Český Krumlov.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Český Krumlov</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0122</t>
+          <t>CLUB_S2005_06_0128</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HC Jaguars Lipolec</t>
+          <t>TJ Božetice</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HC Jaguars Lipolec</t>
+          <t>TJ Božetice</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -21961,36 +22207,41 @@
           <t>L40</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0130</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Lipolec = HC Jaguars Lipolec (Wiki D42 - registr ustavy 04/2026). K overeni mesta. Post-revolucni anglicky nazev. city Lipolec.</t>
+          <t>Božetice = TJ Sokol Božetice (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Pisek). city Božetice.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Jaguars Lipolec</t>
+          <t>Božetice</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0123</t>
+          <t>CLUB_S2005_06_0129</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TJ Hluboká nad Vltavou Knights</t>
+          <t>VTJ Ještěd Liberec</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TJ Hluboká nad Vltavou Knights</t>
+          <t>VTJ Ještěd Liberec</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>30_Jihočeský</t>
+          <t>30_Liberecký-Ústecký</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -22000,39 +22251,39 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0124</t>
+          <t>CLUB_S2004_05_0139</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>B-tym Tatran Hluboká nad Vltavou. clean: II → B. Oprava city: "Hluboká" → "Hluboká nad Vltavou" (plný název). || Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Lokomotiva Liberec B (B-tym, 40_Libereckému). Almanach uvadi „(Slavoj Liberec)" v zavorce - POZOR: dle Wiki D42 (Pavlovo upresneni 04/2026) Lokomotiva Liberec vznikla teprve 1956, Slavoj Liberec NENI predchudce ale jiny klub! Komentar v almanachu k overeni Pavlem (D40). Lokomotiva Liberec = HC Liberec / Bili Tygri (Wiki D42 dolozeno pro 57/58). Genealogie: TJ Lokomotiva Liberec (1956) -&gt; TJ Stadion Liberec (1961) -&gt; TJ PS Stadion Liberec (1970, PS = Pozemni stavby) -&gt; HC Stadion Liberec (1990) -&gt; HC Liberec (1994) -&gt; Bili Tygri Liberec (2000-dnes). city Liberec. || Lokomotiva Liberec B 57/58 (40_Liberecký, B-tym). Liberec = Bílí Tygři Liberec (Wiki D42 - Pavlovo upresneni 04/2026, OPRAVA puvodni ústavy z 04/2026!). Kořeny od 1934 (NE 1956 jak chybne uvedla puvodni ústava!). Genealogie: Rapid Horní Růžodol (1934-1950) -&gt; Sokol Kolora / Jiskra Kolora Liberec (1950-1955, vcleneni do textilniho podniku Kolora) -&gt; Lokomotiva Liberec (prosinec 1955, slouceni Jiskra Kolora + Slovan KNV + Slovan Severočeské tiskárny) -&gt; TJ Stadion Liberec (cerven 1961) -&gt; HC Stadion PS Liberec (1974/76, Pozemni stavby) -&gt; HC Stadion Liberec (1989, 1994 Syner) -&gt; Bílí Tygři Liberec (21.8.2000). Patterns: Sokol Rapid Liberec, Kolora Liberec, Sokol Kolora Liberec, Jiskra Kolora Liberec, Lokomotiva Liberec. city Liberec. || Liberec - vsechny librecke kluby z chain Bili Tygri Liberec (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Rapid Liberec (1934) -&gt; Kolora -&gt; Lokomotiva (1955) -&gt; Stadion (1961) -&gt; Bili Tygri (2000+). Vsechny libercke B-tymy + paralelni Slavia VSS (akademicky) + Dukla Liberec (vojensky 1960-1978) + Jiskra Kolora (textilni podnik). city Liberec.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Hluboká nad Vltavou</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0124</t>
+          <t>CLUB_S2005_06_0130</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HC Vimperk</t>
+          <t>HK Lomnice nad Popelkou (HK)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HC Vimperk</t>
+          <t>HK Lomnice nad Popelkou (HK)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>30_Jihočeský</t>
+          <t>30_Liberecký-Ústecký</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -22042,39 +22293,39 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0126</t>
+          <t>CLUB_S2004_05_0189</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Slavoj Vimperk. city ✓. || Slavoj Vimperk 54/55 (30_Jihočeský). 1955 prejmenovani na Jiskra (Wiki). Vimperk = HC Vimperk (Wiki D42 - Pavlovo upresneni 04/2026, hokej.cz). Genealogie: 1950 Slavoj OPK Vimperk (zalozeni, OPK = ?) -&gt; TJ Jiskra Vimperk (1955) -&gt; TJ Šumavan Vimperk (1962) -&gt; HC Vimperk (1992-dnes). Patterns: Slavoj Vimperk, Jiskra Vimperk. city Vimperk. POZN: Almanach 50/51-52/53 obsahuje pouze 'Vimperk' bez prefixu, patrne pred zalozenim Slavoj 1950 nebo prve roky Slavoj. || Vimperk = HC Vimperk (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. Hlavni chain: Sokol -&gt; Slavoj Vimperk -&gt; Jiskra Vimperk -&gt; HC Vimperk. city Vimperk.</t>
+          <t>Slavoj Lomnice. Oprava city: „Lomnice" → „Lomnice nad Popelkou" (plný název, Pavlovo upřesnění 04/2026). || Lomnice nL Popelkou = Slavoj/Jiskra Lomnice nL Popelkou (Wiki D42 - registr ustavy 04/2026). Liberecky kraj (okres Semily). city Lomnice nad Popelkou. POZOR: Vícero Lomnic v CR - Lomnice u Tisnova, Lomnice u Sokolova.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Vimperk</t>
+          <t>Lomnice nad Popelkou</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0125</t>
+          <t>CLUB_S2005_06_0131</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HC Tábor B – FeKS</t>
+          <t>HC Kohouti Česká Lípa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HC Tábor B – FeKS</t>
+          <t>HC Kohouti Česká Lípa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>30_Jihočeský</t>
+          <t>30_Liberecký-Ústecký</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -22084,39 +22335,44 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0077</t>
+          <t>CLUB_S2004_05_0138</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>VTJ Tábor byl statutárně "B" tým Dukly Jihlava, a proto se nemohl ucházet o účast v 1. CHL. || DA = Dum armady. Almanach: DA Otava (PDA Tabor?) - vztah PDA. || Oprava city dle D33 (04/2026): "Tábor" -&gt; prazdne (DA/PDA bez mesta v nazvu = city vzdy prazdne). || DA Otava 54/55 (30_Jihočeský). 1954 prejmenovani PDA -&gt; DA Otava (Otava = reka u Tabora). Vojensky klub Tábor: PDA / DA Otava / Dukla Tábor (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: PDA Tábor (1952-53, Pred Dukla armada / Posadkove dum armady) -&gt; DA Otava (1954-1956, Dum armady Otava - reka u Tabora) -&gt; Dukla Tábor (DA Otava) (1956-57+) -&gt; Dukla Tábor (1957-58) -&gt; konec po 1957/58 (almanach 58/59, 59/60 neobsahuje vojensky klub v Tábore). POZN: Po obnoveni VTJ Tábor (1970-1993) jako B-tym Dukly Jihlava, v 1993 fuze s civilnim Vodni stavby Tábor = HC VS VTJ -&gt; vojaci konec (Pavlovo: 'pak chvíli společná a pak vojáci konec'). city Tábor. Samostatny od hlavniho civilniho chain HC Tábor. || Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Hlavni chain: DSK Tábor (1921) -&gt; Sokol -&gt; Spartak Tábor -&gt; Tatran Tábor -&gt; Dukla Tábor (vojensky paralelni) -&gt; HC Tábor. **DA Otava** (Doprava-arm Otava) = paralelni klub. Otava = reka, NE Otavany (Strakonice). city Tábor.</t>
+          <t>Almanach uvádí v závorce „(I.B)" = úroveň soutěže (I.A třída / I.B třída / II. třída krajské soutěže). Kolega zapsal úroveň do clean - patří do level/district pole. Strip ze clean. || Česká Lípa = HC Česká Lípa (Wiki - registr ustavy 04/2026). DNES KLUB ZALOZEN 1989 jako VTJ Česká Lípa - NOSITEL HOKEJOVE TRADICE V MESTE (formalne klub zalozen 1989 jako VTJ, ale kontinuita s hokejovou tradici Česke Lipy) - stare ceskolipske kluby 50.let tvori predchudce dnesnich linii. Stare ceskolipske kluby 50.let zanikly behem 60.-80.let. Pozdeji existoval i HC Predators Česká Lípa (1989-2011, paralelni). 2007/08 koupili 2.ligu licenci od Strakonic. city Česká Lípa.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Tábor</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0126</t>
+          <t>CLUB_S2005_06_0132</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HC Velká Radouň</t>
+          <t>HC Svárov Česká Lípa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HC Velká Radouň</t>
+          <t>HC Svárov Česká Lípa (N)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>30_Jihočeský</t>
+          <t>30_Liberecký-Ústecký</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -22126,39 +22382,39 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0128</t>
+          <t>CLUB_S2004_05_0138</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Horní Radouň = TJ Sokol Horní Radouň (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Jindřichův Hradec). city Horní Radouň.</t>
+          <t>Almanach uvádí v závorce „(I.B)" = úroveň soutěže (I.A třída / I.B třída / II. třída krajské soutěže). Kolega zapsal úroveň do clean - patří do level/district pole. Strip ze clean. || Česká Lípa = HC Česká Lípa (Wiki - registr ustavy 04/2026). DNES KLUB ZALOZEN 1989 jako VTJ Česká Lípa - NOSITEL HOKEJOVE TRADICE V MESTE (formalne klub zalozen 1989 jako VTJ, ale kontinuita s hokejovou tradici Česke Lipy) - stare ceskolipske kluby 50.let tvori predchudce dnesnich linii. Stare ceskolipske kluby 50.let zanikly behem 60.-80.let. Pozdeji existoval i HC Predators Česká Lípa (1989-2011, paralelni). 2007/08 koupili 2.ligu licenci od Strakonic. city Česká Lípa.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Horní Radouň</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0127</t>
+          <t>CLUB_S2005_06_0133</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>David servis České Budějovice</t>
+          <t>TJ Slovan Frýdlant</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>David servis České Budějovice</t>
+          <t>TJ Slovan Frýdlant</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>30_Jihočeský</t>
+          <t>30_Liberecký-Ústecký</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -22168,39 +22424,44 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0129</t>
+          <t>CLUB_S2004_05_0140</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Frýdlant. city ✓. || Frýdlant (Wiki - registr ustavy 04/2026). Liberecky kraj (Frydlant v Cechach). Hraje HC Frydlant okresni soutez. POZOR: ZAMENA! 'Frydlant nL Ostravici' je JINE MESTO Severomoravsky (Frydek-Mistek)! POZN: Frydlantsky a Frydek-Mistecky chain jsou JINE. city Frýdlant.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Frýdlant</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0128</t>
+          <t>CLUB_S2005_06_0134</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TJ Božetice</t>
+          <t>BHK Turnov</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TJ Božetice</t>
+          <t>BHK Turnov (N)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>30_Jihočeský</t>
+          <t>30_Liberecký-Ústecký</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -22208,36 +22469,31 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0130</t>
-        </is>
-      </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Božetice = TJ Sokol Božetice (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Pisek). city Božetice.</t>
+          <t>Turnov = BHK Turnov (Wiki D42 - registr ustavy 04/2026). Liberecky kraj (okres Semily). **BHK** = Bruslarsky hokejovy klub. city Turnov.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Božetice</t>
+          <t>BHK Turnov</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0129</t>
+          <t>CLUB_S2005_06_0135</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>VTJ Ještěd Liberec</t>
+          <t>HC Roudnice nad Labem</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VTJ Ještěd Liberec</t>
+          <t>HC Roudnice nad Labem</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -22252,34 +22508,34 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0139</t>
+          <t>CLUB_S2004_05_0119</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Lokomotiva Liberec B (B-tym, 40_Libereckému). Almanach uvadi „(Slavoj Liberec)" v zavorce - POZOR: dle Wiki D42 (Pavlovo upresneni 04/2026) Lokomotiva Liberec vznikla teprve 1956, Slavoj Liberec NENI predchudce ale jiny klub! Komentar v almanachu k overeni Pavlem (D40). Lokomotiva Liberec = HC Liberec / Bili Tygri (Wiki D42 dolozeno pro 57/58). Genealogie: TJ Lokomotiva Liberec (1956) -&gt; TJ Stadion Liberec (1961) -&gt; TJ PS Stadion Liberec (1970, PS = Pozemni stavby) -&gt; HC Stadion Liberec (1990) -&gt; HC Liberec (1994) -&gt; Bili Tygri Liberec (2000-dnes). city Liberec. || Lokomotiva Liberec B 57/58 (40_Liberecký, B-tym). Liberec = Bílí Tygři Liberec (Wiki D42 - Pavlovo upresneni 04/2026, OPRAVA puvodni ústavy z 04/2026!). Kořeny od 1934 (NE 1956 jak chybne uvedla puvodni ústava!). Genealogie: Rapid Horní Růžodol (1934-1950) -&gt; Sokol Kolora / Jiskra Kolora Liberec (1950-1955, vcleneni do textilniho podniku Kolora) -&gt; Lokomotiva Liberec (prosinec 1955, slouceni Jiskra Kolora + Slovan KNV + Slovan Severočeské tiskárny) -&gt; TJ Stadion Liberec (cerven 1961) -&gt; HC Stadion PS Liberec (1974/76, Pozemni stavby) -&gt; HC Stadion Liberec (1989, 1994 Syner) -&gt; Bílí Tygři Liberec (21.8.2000). Patterns: Sokol Rapid Liberec, Kolora Liberec, Sokol Kolora Liberec, Jiskra Kolora Liberec, Lokomotiva Liberec. city Liberec. || Liberec - vsechny librecke kluby z chain Bili Tygri Liberec (Wiki D42 - registr ustavy 04/2026). Hlavni chain: Rapid Liberec (1934) -&gt; Kolora -&gt; Lokomotiva (1955) -&gt; Stadion (1961) -&gt; Bili Tygri (2000+). Vsechny libercke B-tymy + paralelni Slavia VSS (akademicky) + Dukla Liberec (vojensky 1960-1978) + Jiskra Kolora (textilni podnik). city Liberec.</t>
+          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Liberec</t>
+          <t>Roudnice nad Labem</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0130</t>
+          <t>CLUB_S2005_06_0136</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HK Lomnice nad Popelkou (HK)</t>
+          <t>HC Draci Bílina</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HK Lomnice nad Popelkou (HK)</t>
+          <t>HC Draci Bílina</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -22294,39 +22550,39 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0189</t>
+          <t>CLUB_S2004_05_0135</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Slavoj Lomnice. Oprava city: „Lomnice" → „Lomnice nad Popelkou" (plný název, Pavlovo upřesnění 04/2026). || Lomnice nL Popelkou = Slavoj/Jiskra Lomnice nL Popelkou (Wiki D42 - registr ustavy 04/2026). Liberecky kraj (okres Semily). city Lomnice nad Popelkou. POZOR: Vícero Lomnic v CR - Lomnice u Tisnova, Lomnice u Sokolova.</t>
+          <t>Šumperk = TJ Lokomotiva Pramet Šumperk (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Pramet = vyrobce nářadí. city Šumperk.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Lomnice nad Popelkou</t>
+          <t>Pramet Šumperk</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0131</t>
+          <t>CLUB_S2005_06_0138</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HC Kohouti Česká Lípa</t>
+          <t>Primalex Rokycany</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HC Kohouti Česká Lípa</t>
+          <t>Primalex Rokycany</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>30_Liberecký-Ústecký</t>
+          <t>30_Plzeňský</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -22336,44 +22592,39 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0138</t>
+          <t>CLUB_S2004_05_0134</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Almanach uvádí v závorce „(I.B)" = úroveň soutěže (I.A třída / I.B třída / II. třída krajské soutěže). Kolega zapsal úroveň do clean - patří do level/district pole. Strip ze clean. || Česká Lípa = HC Česká Lípa (Wiki - registr ustavy 04/2026). DNES KLUB ZALOZEN 1989 jako VTJ Česká Lípa - NOSITEL HOKEJOVE TRADICE V MESTE (formalne klub zalozen 1989 jako VTJ, ale kontinuita s hokejovou tradici Česke Lipy) - stare ceskolipske kluby 50.let tvori predchudce dnesnich linii. Stare ceskolipske kluby 50.let zanikly behem 60.-80.let. Pozdeji existoval i HC Predators Česká Lípa (1989-2011, paralelni). 2007/08 koupili 2.ligu licenci od Strakonic. city Česká Lípa.</t>
+          <t>Rokycany = HC Prima Rokycany (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Prima** = sponzor. city Rokycany.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Česká Lípa</t>
+          <t>Prima Rokycany</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0132</t>
+          <t>CLUB_S2005_06_0139</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HC Svárov Česká Lípa</t>
+          <t>Apollo Kaznějov</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HC Svárov Česká Lípa (N)</t>
+          <t>Apollo Kaznějov</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>30_Liberecký-Ústecký</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>30_Plzeňský</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -22383,39 +22634,39 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0138</t>
+          <t>CLUB_S2004_05_0156</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Almanach uvádí v závorce „(I.B)" = úroveň soutěže (I.A třída / I.B třída / II. třída krajské soutěže). Kolega zapsal úroveň do clean - patří do level/district pole. Strip ze clean. || Česká Lípa = HC Česká Lípa (Wiki - registr ustavy 04/2026). DNES KLUB ZALOZEN 1989 jako VTJ Česká Lípa - NOSITEL HOKEJOVE TRADICE V MESTE (formalne klub zalozen 1989 jako VTJ, ale kontinuita s hokejovou tradici Česke Lipy) - stare ceskolipske kluby 50.let tvori predchudce dnesnich linii. Stare ceskolipske kluby 50.let zanikly behem 60.-80.let. Pozdeji existoval i HC Predators Česká Lípa (1989-2011, paralelni). 2007/08 koupili 2.ligu licenci od Strakonic. city Česká Lípa.</t>
+          <t>Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || Kaznějov = Jiskra Kaznějov (Wiki D42 - registr ustavy 04/2026). Zapadocesky/Plzensky kraj (okres Plzen-sever). city Kaznějov.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Česká Lípa</t>
+          <t>Kaznějov</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0133</t>
+          <t>CLUB_S2005_06_0140</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TJ Slovan Frýdlant</t>
+          <t>SKP Klatovy</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TJ Slovan Frýdlant</t>
+          <t>SKP Klatovy</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>30_Liberecký-Ústecký</t>
+          <t>30_Plzeňský</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -22425,44 +22676,39 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0140</t>
+          <t>CLUB_S2004_05_0155</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Spartak Frýdlant. city ✓. || Frýdlant (Wiki - registr ustavy 04/2026). Liberecky kraj (Frydlant v Cechach). Hraje HC Frydlant okresni soutez. POZOR: ZAMENA! 'Frydlant nL Ostravici' je JINE MESTO Severomoravsky (Frydek-Mistek)! POZN: Frydlantsky a Frydek-Mistecky chain jsou JINE. city Frýdlant.</t>
+          <t>Klatovy = SHC Klatovy (Wiki - registr ustavy 04/2026). Zapadocesky kraj. - Patterns: Spartak Klatovy, SHC. city Klatovy. || Stupno = TJ Banik Stupno / Jodasta Stupno (Wiki D42 - registr ustavy 04/2026). Zapadocesky/Plzensky kraj (okres Rokycany). Patterns: Sokol Stupno -&gt; Banik Stupno -&gt; Jodasta Stupno. city Stupno.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Frýdlant</t>
+          <t>Klatovy</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0134</t>
+          <t>CLUB_S2005_06_0141</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BHK Turnov</t>
+          <t>Pubec Plzeň</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BHK Turnov (N)</t>
+          <t>Pubec Plzeň</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>30_Liberecký-Ústecký</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>30_Plzeňský</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -22470,36 +22716,46 @@
           <t>L40</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0160</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Turnov = BHK Turnov (Wiki D42 - registr ustavy 04/2026). Liberecky kraj (okres Semily). **BHK** = Bruslarsky hokejovy klub. city Turnov.</t>
+          <t>Plzeň = HC Pubec Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Pubec** = sponzor. city Plzeň.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>BHK Turnov</t>
+          <t>Pubec Plzeň</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0135</t>
+          <t>CLUB_S2005_06_0142</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem</t>
+          <t>HC Tachov</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem</t>
+          <t>HC Tachov (N)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>30_Liberecký-Ústecký</t>
+          <t>30_Plzeňský</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -22507,41 +22763,36 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0119</t>
-        </is>
-      </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
+          <t>Tachov = TJ Plastimat Tachov (Wiki D42 - registr ustavy 04/2026). Plzensky/Tachovsky kraj. **Plastimat** = vyrobce plastovych vyrobku. city Tachov.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Roudnice nad Labem</t>
+          <t>Tachov</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0136</t>
+          <t>CLUB_S2005_06_0143</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HC Draci Bílina</t>
+          <t>TJ Internacional Blovice</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>HC Draci Bílina</t>
+          <t>TJ Internacional Blovice</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>30_Liberecký-Ústecký</t>
+          <t>30_Plzeňský</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -22551,34 +22802,34 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0135</t>
+          <t>CLUB_S2004_05_0158</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Šumperk = TJ Lokomotiva Pramet Šumperk (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Pramet = vyrobce nářadí. city Šumperk.</t>
+          <t>Blovice = HC Internacional Blovice (Wiki D42 - registr ustavy 04/2026). Plzensky kraj (okres Plzen-jih). Patterns: Inter Blovice. city Blovice.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Pramet Šumperk</t>
+          <t>Internacional Blovice</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0138</t>
+          <t>CLUB_S2005_06_0144</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Primalex Rokycany</t>
+          <t>SKP Rokycany</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Primalex Rokycany</t>
+          <t>SKP Rokycany</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -22593,34 +22844,34 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0134</t>
+          <t>CLUB_S2004_05_0154</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Rokycany = HC Prima Rokycany (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Prima** = sponzor. city Rokycany.</t>
+          <t>Baník Rokycany. city OK. || Rokycany = Banik/Sokol Kovohutě Rokycany (Wiki D42 - registr ustavy 04/2026). Zapadocesky/Plzensky kraj. Kovohute Rokycany = kovohutni podnik. city Rokycany.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Prima Rokycany</t>
+          <t>Rokycany</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0139</t>
+          <t>CLUB_S2005_06_0145</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Apollo Kaznějov</t>
+          <t>Ekonomické Stavby Plzeň</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Apollo Kaznějov</t>
+          <t>Ekonomické Stavby Plzeň</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -22635,34 +22886,34 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0156</t>
+          <t>CLUB_S2004_05_0157</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || Kaznějov = Jiskra Kaznějov (Wiki D42 - registr ustavy 04/2026). Zapadocesky/Plzensky kraj (okres Plzen-sever). city Kaznějov.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Kaznějov</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0140</t>
+          <t>CLUB_S2005_06_0146</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SKP Klatovy</t>
+          <t>Dogs Černíkov</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SKP Klatovy</t>
+          <t>Dogs Černíkov</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -22677,34 +22928,34 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0155</t>
+          <t>CLUB_S2004_05_0153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Klatovy = SHC Klatovy (Wiki - registr ustavy 04/2026). Zapadocesky kraj. - Patterns: Spartak Klatovy, SHC. city Klatovy. || Stupno = TJ Banik Stupno / Jodasta Stupno (Wiki D42 - registr ustavy 04/2026). Zapadocesky/Plzensky kraj (okres Rokycany). Patterns: Sokol Stupno -&gt; Banik Stupno -&gt; Jodasta Stupno. city Stupno.</t>
+          <t>Černíkov = HC Dogs Černíkov (Wiki D42 - registr ustavy 04/2026). Plzensky kraj (okres Domazlice). city Černíkov.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Klatovy</t>
+          <t>Dogs Černíkov</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0141</t>
+          <t>CLUB_S2005_06_0147</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Pubec Plzeň</t>
+          <t>Borgers Břasy</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Pubec Plzeň</t>
+          <t>Borgers Břasy</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -22719,34 +22970,34 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0160</t>
+          <t>CLUB_S2004_05_0162</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Plzeň = HC Pubec Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Pubec** = sponzor. city Plzeň.</t>
+          <t>Břasy = HC Borgers Břasy (Wiki D42 - registr ustavy 04/2026). Plzensky kraj (okres Rokycany). **Borgers** = sponzor (auto-dily). city Břasy.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Pubec Plzeň</t>
+          <t>Borgers Břasy</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0142</t>
+          <t>CLUB_S2005_06_0148</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HC Tachov</t>
+          <t>TJ Božkov</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>HC Tachov (N)</t>
+          <t>TJ Božkov</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -22754,41 +23005,41 @@
           <t>30_Plzeňský</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="F132" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0161</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tachov = TJ Plastimat Tachov (Wiki D42 - registr ustavy 04/2026). Plzensky/Tachovsky kraj. **Plastimat** = vyrobce plastovych vyrobku. city Tachov.</t>
+          <t>Plzeň (Božkov) = TJ Sokol Božkov (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Božkov** = mestska cast Plzne. city Plzeň (Božkov).</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Tachov</t>
+          <t>Božkov</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0143</t>
+          <t>CLUB_S2005_06_0149</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TJ Internacional Blovice</t>
+          <t>TJ Sušice</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TJ Internacional Blovice</t>
+          <t>TJ Sušice</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -22803,39 +23054,39 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0158</t>
+          <t>CLUB_S2004_05_0159</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Blovice = HC Internacional Blovice (Wiki D42 - registr ustavy 04/2026). Plzensky kraj (okres Plzen-jih). Patterns: Inter Blovice. city Blovice.</t>
+          <t>Sušice (Wiki - registr ustavy 04/2026). Zapadocesky/Plzensky kraj. city Sušice. || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Internacional Blovice</t>
+          <t>Sušice</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0144</t>
+          <t>CLUB_S2005_06_0150</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SKP Rokycany</t>
+          <t>Mattoni Karlovy Vary</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SKP Rokycany</t>
+          <t>Mattoni Karlovy Vary</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>30_Plzeňský</t>
+          <t>30_Karlovarský</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -22845,39 +23096,39 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0154</t>
+          <t>CLUB_S2004_05_0145</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Baník Rokycany. city OK. || Rokycany = Banik/Sokol Kovohutě Rokycany (Wiki D42 - registr ustavy 04/2026). Zapadocesky/Plzensky kraj. Kovohute Rokycany = kovohutni podnik. city Rokycany.</t>
+          <t>Dynamo Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - registr ustavy 04/2026). Chain SK Slavia KV (1932) -&gt; Dynamo -&gt; Slavia -&gt; Becherovka -&gt; Energie KV. city Karlovy Vary.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Rokycany</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0145</t>
+          <t>CLUB_S2005_06_0151</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>HC Mariánské Lázně</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>HC Mariánské Lázně</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>30_Plzeňský</t>
+          <t>30_Karlovarský</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -22887,39 +23138,39 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0157</t>
+          <t>CLUB_S2004_05_0149</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Mariánské Lázně (Wiki - registr ustavy 04/2026). Zapadocesky/Karlovarsky kraj. - hokej tradice mensi. city Mariánské Lázně.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Mariánské Lázně</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0146</t>
+          <t>CLUB_S2005_06_0152</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Dogs Černíkov</t>
+          <t>HC Cheb 2001</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dogs Černíkov</t>
+          <t>HC Cheb 2001</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>30_Plzeňský</t>
+          <t>30_Karlovarský</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -22929,39 +23180,39 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0153</t>
+          <t>CLUB_S2004_05_0147</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Černíkov = HC Dogs Černíkov (Wiki D42 - registr ustavy 04/2026). Plzensky kraj (okres Domazlice). city Černíkov.</t>
+          <t>Lokomotiva Cheb. city OK. || Lokomotiva Cheb 58/59 - PRVNI vyskyt Lokomotivy (zeleznicarsky klub - 1960 oficialni nazev TJ Lokomotiva Cheb). Cheb = HC Stadion Cheb (Wiki D42 + hokej.cz 04/2026). Genealogie: Cheb (49/50 prirodni led v Gottwaldovych sadech) -&gt; RH Cheb (51/52+ bezpecnostni klub Rude hvezdy) + Lokomotiva Cheb (zeleznicarsky klub TJ Lokomotiva Cheb od 1960) + Spartak Cheb (paralelni podnikovy) + DA Hvezda + Slavoj. **DNESNI HC Stadion Cheb zalozen 1978** jako TJ Stadion Cheb (Wiki) -&gt; 2008 HC Stadion Cheb. Patterns: Cheb, RH Cheb, Spartak Cheb, Lokomotiva Cheb, DA Hvězda Cheb. city Cheb. || Lokomotiva Cheb 58/59 (40_Karlovarský). KLICOVY ROK 1958 prejmenovani Železničáři -&gt; Lokomotiva. Lokomotiva Cheb = TJ Lokomotiva Cheb (Wiki D42 - registr ustavy 04/2026). Klub zaleznicaru. Genealogie: Železničáři Cheb (1951+) -&gt; Lokomotiva Cheb (1958+, DSO reforma + zmena na Lokomotiva). 'Dnesni nazev TJ Lokomotiva Cheb je od roku 1960' (podle TJ Lokomotiva oficial). Hokejovy oddil: 50.leta hriste v Gottwaldovych sadech na prirodnim lede. Paralelni od RH/Spartak/Stadion chebskych klubu. city Cheb. || Lokomotiva Cheb 58/59 (40_Karlovarský). PRVNI vyskyt Lokomotivy Cheb (oficialni TJ od 1960). Předchudce Železničáři Cheb. Cheb (Wiki D42 + retromuseum.cz - registr ustavy 04/2026). MULTI-CHAIN MESTO - v 50.letech 4-5 paralelnich klubu. **HC Stadion Cheb** (1978-dnes, ZALOZEN 1978 jako TJ Stadion Cheb, 2008 prejmenovan): to je dnesni klub HOKEJE - vznikl ZNOVA, NENI primy nasledník zadneho 50.letech. **RH Cheb** (1951-1996): klub 5. brigady Pohranicni straze (DSO Ministerstva vnitra). Vojenska sokolska jednota Sokolovo (1951) -&gt; RH (1952+) -&gt; VTJ Dukla Hranicar (1966-1972, pod MO) -&gt; RH zpet -&gt; 1990 SK policie Union -&gt; FC Union -&gt; 1996 zanik. **TJ Lokomotiva Cheb** (oficialne 1960): zeleznicarsky klub, oddil hokeje od 50. let (1957 hraje na priroduicm lede v Gottwaldovych sadech). Sportovni areal Lokomotiva v Hradcanech (mestska cast Chebu). **Spartak Cheb / Eska**: stadion Esky Cheb, v 1952 prejmenovany Spartak Eska Cheb, v 1963 Spartak se stal soucasti RH Cheb. **DA Hvezda Cheb**: drobny **Slavoj Cheb**: drobny Patterns: RH Cheb, Spartak Cheb, Lokomotiva Cheb, DA Hvezda Cheb, Slavoj Cheb. city Cheb. POZOR: Tatran Luby u Chebu = JINE MESTO (Luby jsou samostatne mesto).</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Dogs Černíkov</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0147</t>
+          <t>CLUB_S2005_06_0153</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Borgers Břasy</t>
+          <t>HC PK Vřesová</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Borgers Břasy</t>
+          <t>HC PK Vřesová</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>30_Plzeňský</t>
+          <t>30_Karlovarský</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -22971,39 +23222,39 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0162</t>
+          <t>CLUB_S2004_05_0148</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Břasy = HC Borgers Břasy (Wiki D42 - registr ustavy 04/2026). Plzensky kraj (okres Rokycany). **Borgers** = sponzor (auto-dily). city Břasy.</t>
+          <t>Vřesová = TJ Kombinát Vřesová (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Sokolov). **Kombinát Vřesová** = hornicky podnik (drive KVUH = Karlovarske uhelne hnedouhelne doly). city Vřesová.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Borgers Břasy</t>
+          <t>Vřesová</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0148</t>
+          <t>CLUB_S2005_06_0154</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TJ Božkov</t>
+          <t>Farmáři Trstěnice</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TJ Božkov</t>
+          <t>Farmáři Trstěnice</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>30_Plzeňský</t>
+          <t>30_Karlovarský</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -23013,39 +23264,44 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0161</t>
+          <t>CLUB_S2004_05_0150</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Plzeň (Božkov) = TJ Sokol Božkov (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Božkov** = mestska cast Plzne. city Plzeň (Božkov).</t>
+          <t>Trstěnice u Chebu = HC Farmáři Trstěnice (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). Patterns: JZD Trstěnice. city Trstěnice u Chebu.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Božkov</t>
+          <t>Farmáři Trstěnice</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0149</t>
+          <t>CLUB_S2005_06_0155</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TJ Sušice</t>
+          <t>Stadion Cheb</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TJ Sušice</t>
+          <t>Stadion Cheb (N)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>30_Plzeňský</t>
+          <t>30_Karlovarský</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -23053,41 +23309,36 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0159</t>
-        </is>
-      </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Sušice (Wiki - registr ustavy 04/2026). Zapadocesky/Plzensky kraj. city Sušice. || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Cheb = TJ Stadion Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Stadion Cheb** = historicky klub Chebu. Patterns: Sokol -&gt; Stadion Cheb. city Cheb.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Sušice</t>
+          <t>Stadion Cheb</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0150</t>
+          <t>CLUB_S2005_06_0157</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mattoni Karlovy Vary</t>
+          <t>HC Jaroměř</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mattoni Karlovy Vary</t>
+          <t>HC Jaroměř</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>30_Karlovarský</t>
+          <t>30_Hradecký</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -23097,39 +23348,39 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0145</t>
+          <t>CLUB_S2004_05_0165</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Dynamo Karlovy Vary = HC Energie Karlovy Vary (Wiki D42 - registr ustavy 04/2026). Chain SK Slavia KV (1932) -&gt; Dynamo -&gt; Slavia -&gt; Becherovka -&gt; Energie KV. city Karlovy Vary.</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci. || Jaroměř = Jiskra ZAZ Jaroměř / Lina Jaroměř (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Náchod). ZAZ = podnik, Lina = podnik. city Jaroměř.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>Jaroměř</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0151</t>
+          <t>CLUB_S2005_06_0158</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HC Mariánské Lázně</t>
+          <t>HC Náchod</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>HC Mariánské Lázně</t>
+          <t>HC Náchod</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>30_Karlovarský</t>
+          <t>30_Hradecký</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -23139,39 +23390,39 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0149</t>
+          <t>CLUB_S2004_05_0168</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mariánské Lázně (Wiki - registr ustavy 04/2026). Zapadocesky/Karlovarsky kraj. - hokej tradice mensi. city Mariánské Lázně.</t>
+          <t>Jiskra Tepna Náchod (Tepna = závod). Oprava city: "Tepna Náchod" → "Náchod". || Náchod (Wiki - registr ustavy 04/2026). Východocesky/Královéhradecky kraj. city Náchod.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Mariánské Lázně</t>
+          <t>Náchod</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0152</t>
+          <t>CLUB_S2005_06_0159</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HC Cheb 2001</t>
+          <t>HC BaL Dvůr Králové</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>HC Cheb 2001</t>
+          <t>HC BaL Dvůr Králové</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>30_Karlovarský</t>
+          <t>30_Hradecký</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -23181,39 +23432,44 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0147</t>
+          <t>CLUB_S2004_05_0166</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Lokomotiva Cheb. city OK. || Lokomotiva Cheb 58/59 - PRVNI vyskyt Lokomotivy (zeleznicarsky klub - 1960 oficialni nazev TJ Lokomotiva Cheb). Cheb = HC Stadion Cheb (Wiki D42 + hokej.cz 04/2026). Genealogie: Cheb (49/50 prirodni led v Gottwaldovych sadech) -&gt; RH Cheb (51/52+ bezpecnostni klub Rude hvezdy) + Lokomotiva Cheb (zeleznicarsky klub TJ Lokomotiva Cheb od 1960) + Spartak Cheb (paralelni podnikovy) + DA Hvezda + Slavoj. **DNESNI HC Stadion Cheb zalozen 1978** jako TJ Stadion Cheb (Wiki) -&gt; 2008 HC Stadion Cheb. Patterns: Cheb, RH Cheb, Spartak Cheb, Lokomotiva Cheb, DA Hvězda Cheb. city Cheb. || Lokomotiva Cheb 58/59 (40_Karlovarský). KLICOVY ROK 1958 prejmenovani Železničáři -&gt; Lokomotiva. Lokomotiva Cheb = TJ Lokomotiva Cheb (Wiki D42 - registr ustavy 04/2026). Klub zaleznicaru. Genealogie: Železničáři Cheb (1951+) -&gt; Lokomotiva Cheb (1958+, DSO reforma + zmena na Lokomotiva). 'Dnesni nazev TJ Lokomotiva Cheb je od roku 1960' (podle TJ Lokomotiva oficial). Hokejovy oddil: 50.leta hriste v Gottwaldovych sadech na prirodnim lede. Paralelni od RH/Spartak/Stadion chebskych klubu. city Cheb. || Lokomotiva Cheb 58/59 (40_Karlovarský). PRVNI vyskyt Lokomotivy Cheb (oficialni TJ od 1960). Předchudce Železničáři Cheb. Cheb (Wiki D42 + retromuseum.cz - registr ustavy 04/2026). MULTI-CHAIN MESTO - v 50.letech 4-5 paralelnich klubu. **HC Stadion Cheb** (1978-dnes, ZALOZEN 1978 jako TJ Stadion Cheb, 2008 prejmenovan): to je dnesni klub HOKEJE - vznikl ZNOVA, NENI primy nasledník zadneho 50.letech. **RH Cheb** (1951-1996): klub 5. brigady Pohranicni straze (DSO Ministerstva vnitra). Vojenska sokolska jednota Sokolovo (1951) -&gt; RH (1952+) -&gt; VTJ Dukla Hranicar (1966-1972, pod MO) -&gt; RH zpet -&gt; 1990 SK policie Union -&gt; FC Union -&gt; 1996 zanik. **TJ Lokomotiva Cheb** (oficialne 1960): zeleznicarsky klub, oddil hokeje od 50. let (1957 hraje na priroduicm lede v Gottwaldovych sadech). Sportovni areal Lokomotiva v Hradcanech (mestska cast Chebu). **Spartak Cheb / Eska**: stadion Esky Cheb, v 1952 prejmenovany Spartak Eska Cheb, v 1963 Spartak se stal soucasti RH Cheb. **DA Hvezda Cheb**: drobny **Slavoj Cheb**: drobny Patterns: RH Cheb, Spartak Cheb, Lokomotiva Cheb, DA Hvezda Cheb, Slavoj Cheb. city Cheb. POZOR: Tatran Luby u Chebu = JINE MESTO (Luby jsou samostatne mesto).</t>
+          <t>Dvůr Králové nL Labem (Wiki - registr ustavy 04/2026). Východocesky kraj. Hokej dlouhodoba tradice - SK Dvůr Králové. city Dvůr Králové nad Labem.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Cheb</t>
+          <t>Dvůr Králové nad Labem</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0153</t>
+          <t>CLUB_S2005_06_0160</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HC PK Vřesová</t>
+          <t>HC Trutnov</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HC PK Vřesová</t>
+          <t>HC Trutnov (N)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>30_Karlovarský</t>
+          <t>30_Hradecký</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -23223,39 +23479,39 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0148</t>
+          <t>CLUB_S2004_05_0185</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Vřesová = TJ Kombinát Vřesová (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Sokolov). **Kombinát Vřesová** = hornicky podnik (drive KVUH = Karlovarske uhelne hnedouhelne doly). city Vřesová.</t>
+          <t>B-tým Baník Trutnov. city ✓. || Trutnov (Wiki - registr ustavy 04/2026). Východocesky/Královéhradecky kraj (Krkonoše). HC TJ Stadion Trutnov. Mensi klub v krajskych soutezich. city Trutnov.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Vřesová</t>
+          <t>Trutnov</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0154</t>
+          <t>CLUB_S2005_06_0161</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Farmáři Trstěnice</t>
+          <t>TJ Spartak Nové Město nad Metují</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Farmáři Trstěnice</t>
+          <t>TJ Spartak Nové Město nad Metují</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>30_Karlovarský</t>
+          <t>30_Hradecký</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -23265,44 +23521,39 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0150</t>
+          <t>CLUB_S2004_05_0167</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Trstěnice u Chebu = HC Farmáři Trstěnice (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). Patterns: JZD Trstěnice. city Trstěnice u Chebu.</t>
+          <t>Nové Město nL Metují = TJ Spartak Nové Město nL Metují (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Náchod). Genealogie: Sokol -&gt; Chirana (podnik) -&gt; Spartak NMnM -&gt; Dukla NMnM (vojensky paralelni). Jasna Nove Mesto = paralelni klub. POZOR: NE Nove Mesto pod Smrkem (Liberecky), NE Nove Mesto na Morave (Vysocina). city Nové Město nad Metují.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Farmáři Trstěnice</t>
+          <t>Nové Město pod Smrkem</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0155</t>
+          <t>CLUB_S2005_06_0162</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Stadion Cheb</t>
+          <t>HC Jičín</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Stadion Cheb (N)</t>
+          <t>HC Jičín</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>30_Karlovarský</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>30_Hradecký</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -23310,31 +23561,36 @@
           <t>L40</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0169</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Cheb = TJ Stadion Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Stadion Cheb** = historicky klub Chebu. Patterns: Sokol -&gt; Stadion Cheb. city Cheb.</t>
+          <t>DA Nový Jičín (město v názvu). city Nový Jičín. [Oprava chybne automaticke opravy 04/2026] || Jičín (Wiki - registr ustavy 04/2026). Východocesky/Královéhradecky kraj. city Jičín.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Stadion Cheb</t>
+          <t>Jičín</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0157</t>
+          <t>CLUB_S2005_06_0163</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HC Jaroměř</t>
+          <t>HC Hronov</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>HC Jaroměř</t>
+          <t>HC Hronov (N)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -23342,6 +23598,11 @@
           <t>30_Hradecký</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr">
         <is>
           <t>L40</t>
@@ -23349,34 +23610,34 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0165</t>
+          <t>CLUB_S2004_05_0186</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci. || Jaroměř = Jiskra ZAZ Jaroměř / Lina Jaroměř (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Náchod). ZAZ = podnik, Lina = podnik. city Jaroměř.</t>
+          <t>Hronov = TJ Jiskra Tepna Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna Hronov** = textilni podnik (pobocka Tepna Náchod). Patterns: Sokol -&gt; Jiskra Hronov -&gt; Jiskra Tepna Hronov -&gt; Tepna ČKD Hronov. NE Hronovce (SVK!). city Hronov.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Jaroměř</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0158</t>
+          <t>CLUB_S2005_06_0164</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HC Náchod</t>
+          <t>SK Třebechovice pod Orebem</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>HC Náchod</t>
+          <t>SK Třebechovice pod Orebem</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -23391,34 +23652,34 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0168</t>
+          <t>CLUB_S2004_05_0171</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Jiskra Tepna Náchod (Tepna = závod). Oprava city: "Tepna Náchod" → "Náchod". || Náchod (Wiki - registr ustavy 04/2026). Východocesky/Královéhradecky kraj. city Náchod.</t>
+          <t>Třebechovice pod Orebem = Jiskra Třebechovice (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Hradec Kralove). Patterns: Sokol -&gt; Jiskra. city Třebechovice pod Orebem.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Náchod</t>
+          <t>Třebechovice</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0159</t>
+          <t>CLUB_S2005_06_0165</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HC BaL Dvůr Králové</t>
+          <t>SK HC Opočno</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HC BaL Dvůr Králové</t>
+          <t>SK HC Opočno (N)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -23426,6 +23687,11 @@
           <t>30_Hradecký</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>L40</t>
@@ -23433,44 +23699,39 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0166</t>
+          <t>CLUB_S2004_05_0187</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Dvůr Králové nL Labem (Wiki - registr ustavy 04/2026). Východocesky kraj. Hokej dlouhodoba tradice - SK Dvůr Králové. city Dvůr Králové nad Labem.</t>
+          <t>Baník Most. city ✓. || Baník Most 53/54 (30_Ústecký). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Most = HC Most / Baník Most (Wiki D42 - Pavlovo upresneni 04/2026, hokej.cz). Genealogie: HO Uhlomost (1946, Hokejovy oddil Uhlomost) -&gt; Sokol Uhlomost (1948-49) -&gt; Uhlomost (1952) -&gt; TJ Baník Most (1953+, SHD = Severočeské hnědouhelné doly, 'uhlí + Most' = puvodni nazev Uhlomost) -&gt;... -&gt; HC Baník SHD Most (80. leta) -&gt; HC Most (1991) -&gt; 2017 sestup z 1.ligy + presun do Slaneho -&gt; 2017 Mostečtí lvi (novy klub v Most, ne navazujici, sezona 2017/18+). Patterns: Sokol Uhlomost, Uhlomost, Baník Most, TJ Baník Most. Sponzorske patronace pozdejsi: SHD = Severočeské hnědouhelné doly (statni podnik). city Most. POZN: 'Sokol Neuměřice – Kamenný Most' = JINÉ MÍSTO (Kamenný Most je obec u Neuměřic ve Středocesku, ne v meste Most). || Baník Most 53/54 (30_Ústecký). KLICOVY ROK 1953 DSO reforma + slouceni s Baník Oldřich. Most = MOSTEČTÍ LVI (Wiki D42 + hokej.cz - Pavlovo upresneni 04/2026). Genealogie historicka: Uhlolom Most (1949+) -&gt; Sokol Uhlomost (1951+, slouceni) -&gt; Uhlomost (1952) -&gt; Baník Most (1953+ DSO reforma + slouceni s Banik Oldrich) -&gt; TJ Baník Most (1958+) -&gt;... -&gt; HC Most (do 2017, sestup do Slaného) -&gt; MOSTEČTÍ LVI (2017+ NOVY klub). Klub zalozen historicky kolem 1945 (po valce). city Most. POZOR: Mostek (Královehradecky) a Kamenny Most (Středočesky) = JINA mesta! NE Most / Mostecti Lvi chain. || Banik Most 53/54 (30_Ústecký). KLICOVY ROK 1953 DSO reforma -&gt; Banik (horníci). Most = HC Most (1946-2017) -&gt; Mostečtí lvi (2017-dnes) (Wiki D42 + Pavlovo upresneni 04/2026). DVE ERY mosteckeho hokeje! **1. era - HC Most (1946-2017):** 1946 zalozeni HO Uhlomost (Hokejovy oddil Uhlomost - podnik Uhlomost = uhelny prumysl, hnedouhelne doly v Mosteckem revíru). 1953+ Banik Most (DSO reforma, Banik = obecny DSO horniku). 1991-2007 stabilni 2.liga. 2005+ posledni nazev HC Most. 2007 postup do 1.ligy (2 sezony, navrat 2009). 2011 zpet 1.liga (6 let, ale bez play-off). **2016/17 sestup z 1.ligy + STEHOVANI klubu do Slaneho!** **2. era - Mostecti lvi (2017-dnes):** Vznikl uplne novy klub za podpory mesta Most (statutarni mesto Most = 100% spolecnik Mostecky hokejovy klub s.r.o.). Sport Most z.s. = mladez (od 2015), Mostecky hokejovy klub s.r.o. = dospeli (od 2017). Spolecne registracni cislo MOSTEČTÍ LVI. 2017/18 Krajska liga -&gt; 2018/19 do 2.ligy (kde dnes). Patterns: Uhlomost/Sokol Uhlomost, Banik Most, TJ Banik Most, HC Most, Mostecti lvi. city Most. POZOR: Mostek = JINE MESTO Královéhradecky (mestys). Kamenny Most = JINE MESTO (obec u Prahy v Stredoceskem kraji). || Banik Most 53/54 (30_Ústecký, L30). KLICOVY ROK 1953 DSO reforma -&gt; TJ Baník Most. Banik = obecny DSO horniku/uhelne tezby. Most = HC Baník Most (1946-2017, presunut do Slaneho) -&gt; Mostečtí Lvi (2017-dnes) (Wiki D42 + Pavlovo upresneni + Wikipedia HC Most/Mostečtí Lvi - registr ustavy 04/2026). Genealogie HC Baník Most: 1946 HO Uhlomost (Hokejovy oddil Uhlomost - Most + uhli) -&gt; Sokol Uhlomost (1948-49, sokolska reorganizace) -&gt; Uhlomost (1952) -&gt; TJ Baník Most (1953+ DSO reforma, Baník = obecny DSO horniku/uhelne tezby) -&gt; TJ Baník SHD Most (SHD = Severočeské hnědouhelné doly) -&gt; 1990 TJ Baník Most -&gt; 1994 HC Baník Most -&gt; 2000 SK HC Baník Most -&gt; 2005 HC Most -&gt; **2017 odchod do Slaneho** (po sestupu z 1.ligy 2016/17). MILNIKY: 1976/77 postup do 2. ČNHL. 1990/91 postup do 2.ligy. 2007 postup do 1.ligy. Po odchodu HC Most v lete 2017 vznikla **Mostečtí Lvi** (zalozeni 2017 - NOSITEL HOKEJOVE TRADICE V MESTE, mestska zastupitelnost zalozila po odchodu HC Most do Slaneho), zalozeni mestskou zastupitelnosti) - zcela novy klub. 2018/19 postup do 2. ligy. Hraji v Krajske lize muzu UlK. Patterns: Sokol Uhlomost, Uhlomost, TJ Baník Most, Baník Most, HC Most, Mostečtí Lvi. city Most. POZOR: NE 'Mostek' (Královéhradecky kraj) ani 'Kamenny Most' (Praha) - JINA MESTA (D44 - identita = lokalita).</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Dvůr Králové nad Labem</t>
+          <t>Most</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0160</t>
+          <t>CLUB_S2005_06_0166</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>HC Trutnov</t>
+          <t>HC Chotěboř (STČ)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HC Trutnov (N)</t>
+          <t>HC Chotěboř (STČ)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>30_Hradecký</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>30_Pardubický</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -23480,39 +23741,39 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0185</t>
+          <t>CLUB_S2004_05_0181</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>B-tým Baník Trutnov. city ✓. || Trutnov (Wiki - registr ustavy 04/2026). Východocesky/Královéhradecky kraj (Krkonoše). HC TJ Stadion Trutnov. Mensi klub v krajskych soutezich. city Trutnov.</t>
+          <t>B-tým Spartak Chotěboř (CLUB_S1953_54_0316). Přejmenováno II → B (D21). prev na 52/53 0263 (A-tým, B 52/53 neexistoval). || Chotěboř = Spartak Chotěboř (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Havlíčkův Brod). S-P = Semily-Pardubice. city Chotěboř.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Trutnov</t>
+          <t>Chotěboř</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0161</t>
+          <t>CLUB_S2005_06_0167</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TJ Spartak Nové Město nad Metují</t>
+          <t>HC Litomyšl</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TJ Spartak Nové Město nad Metují</t>
+          <t>HC Litomyšl</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>30_Hradecký</t>
+          <t>30_Pardubický</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -23522,39 +23783,39 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0167</t>
+          <t>CLUB_S2004_05_0175</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Nové Město nL Metují = TJ Spartak Nové Město nL Metují (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Náchod). Genealogie: Sokol -&gt; Chirana (podnik) -&gt; Spartak NMnM -&gt; Dukla NMnM (vojensky paralelni). Jasna Nove Mesto = paralelni klub. POZOR: NE Nove Mesto pod Smrkem (Liberecky), NE Nove Mesto na Morave (Vysocina). city Nové Město nad Metují.</t>
+          <t>Litomyšl (Wiki - registr ustavy 04/2026). Východocesky/Pardubicky kraj. Slovan Litomysl - city Litomyšl.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Nové Město pod Smrkem</t>
+          <t>Slovan Litomyšl</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0162</t>
+          <t>CLUB_S2005_06_0168</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HC Jičín</t>
+          <t>HC Slovan Moravská Třebová</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HC Jičín</t>
+          <t>HC Slovan Moravská Třebová</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>30_Hradecký</t>
+          <t>30_Pardubický</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -23564,44 +23825,39 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0169</t>
+          <t>CLUB_S2004_05_0174</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>DA Nový Jičín (město v názvu). city Nový Jičín. [Oprava chybne automaticke opravy 04/2026] || Jičín (Wiki - registr ustavy 04/2026). Východocesky/Královéhradecky kraj. city Jičín.</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem. || Moravská Třebová = Slovan/Slavoj Moravská Třebová (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Svitavy). POZOR: NE Třebová Česká (Pardubicky), NE Trebon (Jihocesky). city Moravská Třebová.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Jičín</t>
+          <t>Moravská Třebová</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0163</t>
+          <t>CLUB_S2005_06_0169</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HC Hronov</t>
+          <t>Sokol Staré Jesenčany</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HC Hronov (N)</t>
+          <t>Sokol Staré Jesenčany</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>30_Hradecký</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>30_Pardubický</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -23611,39 +23867,39 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0186</t>
+          <t>CLUB_S2004_05_0176</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Hronov = TJ Jiskra Tepna Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna Hronov** = textilni podnik (pobocka Tepna Náchod). Patterns: Sokol -&gt; Jiskra Hronov -&gt; Jiskra Tepna Hronov -&gt; Tepna ČKD Hronov. NE Hronovce (SVK!). city Hronov.</t>
+          <t>Staré Jesenčany = TJ Sokol Staré Jesenčany (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Pardubice). city Staré Jesenčany.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Hronov</t>
+          <t>Staré Jesenčany</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0164</t>
+          <t>CLUB_S2005_06_0170</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SK Třebechovice pod Orebem</t>
+          <t>HC Hlinsko</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SK Třebechovice pod Orebem</t>
+          <t>HC Hlinsko</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>30_Hradecký</t>
+          <t>30_Pardubický</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -23653,44 +23909,39 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0171</t>
+          <t>CLUB_S2004_05_0180</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Třebechovice pod Orebem = Jiskra Třebechovice (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Hradec Kralove). Patterns: Sokol -&gt; Jiskra. city Třebechovice pod Orebem.</t>
+          <t>B-tým TJ Spartak Praha Sokolovo (CLUB_S1953_54_0001 v 1. lize). Doplnění „Praha" do názvu (Pavlovo rozhodnutí — plný název klubu, ne zkrácená forma). city: Sokolovo = čtvrť Prahy (D23) → „Praha". Smart fix prev → 52/53 0001 (A-tým, B 52/53 neexistoval). || Spartak Praha Sokolovo B 53/54 (B-tým, 30_PHA_mesto). Sparta Praha = HC Sparta Praha (Wiki D18 / D42). Genealogie: AC Sparta Praha (1903) -&gt; Sokol Sparta Bubeneč (1948) -&gt; ZSJ Bratrství Sparta Praha (1949) -&gt; ZSJ Sparta ČKD Sokolovo Praha (1951, ČKD = Českomoravská-Kolben-Daněk) -&gt; TJ Spartak Praha Sokolovo (1952) -&gt; TJ Sparta ČKD Praha (1965) -&gt; HC Sparta Praha (1990). city Praha (D23, Bubeneč = čtvrť Prahy 7). || Sokolov = HC Baník Sokolov (Wiki - registr ustavy 04/2026). ZALOZEN 1945 jako SK FHD Dolní Rychnov (FHD = Falknovske hnedouhelne doly - Sokolov se drive jmenoval Falknov nL Ohri). Genealogie: SK FHD (1945) -&gt; TJ Banik Sokolov (1953+ DSO) -&gt; NHL (1 sezona) -&gt; 1969 nahradil zruseny Duklu Litomerice v A skupine CNHL -&gt; NHL (1 sezona) -&gt; 1990 znovu 1.NHL -&gt; 1997 sestup do 2.ligy -&gt; 2002 prejmenovani na HC Banik Sokolov -&gt; 2019/20 do Maxa Ligy. Falknov nad Ohri se 1948 prejmenoval na Sokolov. city Sokolov.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Třebechovice</t>
+          <t>Sokolov</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0165</t>
+          <t>CLUB_S2005_06_0171</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SK HC Opočno</t>
+          <t>Spartak Choceň</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SK HC Opočno (N)</t>
+          <t>Spartak Choceň</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>30_Hradecký</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>30_Pardubický</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -23700,34 +23951,34 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0187</t>
+          <t>CLUB_S2004_05_0177</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Baník Most. city ✓. || Baník Most 53/54 (30_Ústecký). KLÍČOVÝ ROK přejmenování - DSO Baník 1953. Most = HC Most / Baník Most (Wiki D42 - Pavlovo upresneni 04/2026, hokej.cz). Genealogie: HO Uhlomost (1946, Hokejovy oddil Uhlomost) -&gt; Sokol Uhlomost (1948-49) -&gt; Uhlomost (1952) -&gt; TJ Baník Most (1953+, SHD = Severočeské hnědouhelné doly, 'uhlí + Most' = puvodni nazev Uhlomost) -&gt;... -&gt; HC Baník SHD Most (80. leta) -&gt; HC Most (1991) -&gt; 2017 sestup z 1.ligy + presun do Slaneho -&gt; 2017 Mostečtí lvi (novy klub v Most, ne navazujici, sezona 2017/18+). Patterns: Sokol Uhlomost, Uhlomost, Baník Most, TJ Baník Most. Sponzorske patronace pozdejsi: SHD = Severočeské hnědouhelné doly (statni podnik). city Most. POZN: 'Sokol Neuměřice – Kamenný Most' = JINÉ MÍSTO (Kamenný Most je obec u Neuměřic ve Středocesku, ne v meste Most). || Baník Most 53/54 (30_Ústecký). KLICOVY ROK 1953 DSO reforma + slouceni s Baník Oldřich. Most = MOSTEČTÍ LVI (Wiki D42 + hokej.cz - Pavlovo upresneni 04/2026). Genealogie historicka: Uhlolom Most (1949+) -&gt; Sokol Uhlomost (1951+, slouceni) -&gt; Uhlomost (1952) -&gt; Baník Most (1953+ DSO reforma + slouceni s Banik Oldrich) -&gt; TJ Baník Most (1958+) -&gt;... -&gt; HC Most (do 2017, sestup do Slaného) -&gt; MOSTEČTÍ LVI (2017+ NOVY klub). Klub zalozen historicky kolem 1945 (po valce). city Most. POZOR: Mostek (Královehradecky) a Kamenny Most (Středočesky) = JINA mesta! NE Most / Mostecti Lvi chain. || Banik Most 53/54 (30_Ústecký). KLICOVY ROK 1953 DSO reforma -&gt; Banik (horníci). Most = HC Most (1946-2017) -&gt; Mostečtí lvi (2017-dnes) (Wiki D42 + Pavlovo upresneni 04/2026). DVE ERY mosteckeho hokeje! **1. era - HC Most (1946-2017):** 1946 zalozeni HO Uhlomost (Hokejovy oddil Uhlomost - podnik Uhlomost = uhelny prumysl, hnedouhelne doly v Mosteckem revíru). 1953+ Banik Most (DSO reforma, Banik = obecny DSO horniku). 1991-2007 stabilni 2.liga. 2005+ posledni nazev HC Most. 2007 postup do 1.ligy (2 sezony, navrat 2009). 2011 zpet 1.liga (6 let, ale bez play-off). **2016/17 sestup z 1.ligy + STEHOVANI klubu do Slaneho!** **2. era - Mostecti lvi (2017-dnes):** Vznikl uplne novy klub za podpory mesta Most (statutarni mesto Most = 100% spolecnik Mostecky hokejovy klub s.r.o.). Sport Most z.s. = mladez (od 2015), Mostecky hokejovy klub s.r.o. = dospeli (od 2017). Spolecne registracni cislo MOSTEČTÍ LVI. 2017/18 Krajska liga -&gt; 2018/19 do 2.ligy (kde dnes). Patterns: Uhlomost/Sokol Uhlomost, Banik Most, TJ Banik Most, HC Most, Mostecti lvi. city Most. POZOR: Mostek = JINE MESTO Královéhradecky (mestys). Kamenny Most = JINE MESTO (obec u Prahy v Stredoceskem kraji). || Banik Most 53/54 (30_Ústecký, L30). KLICOVY ROK 1953 DSO reforma -&gt; TJ Baník Most. Banik = obecny DSO horniku/uhelne tezby. Most = HC Baník Most (1946-2017, presunut do Slaneho) -&gt; Mostečtí Lvi (2017-dnes) (Wiki D42 + Pavlovo upresneni + Wikipedia HC Most/Mostečtí Lvi - registr ustavy 04/2026). Genealogie HC Baník Most: 1946 HO Uhlomost (Hokejovy oddil Uhlomost - Most + uhli) -&gt; Sokol Uhlomost (1948-49, sokolska reorganizace) -&gt; Uhlomost (1952) -&gt; TJ Baník Most (1953+ DSO reforma, Baník = obecny DSO horniku/uhelne tezby) -&gt; TJ Baník SHD Most (SHD = Severočeské hnědouhelné doly) -&gt; 1990 TJ Baník Most -&gt; 1994 HC Baník Most -&gt; 2000 SK HC Baník Most -&gt; 2005 HC Most -&gt; **2017 odchod do Slaneho** (po sestupu z 1.ligy 2016/17). MILNIKY: 1976/77 postup do 2. ČNHL. 1990/91 postup do 2.ligy. 2007 postup do 1.ligy. Po odchodu HC Most v lete 2017 vznikla **Mostečtí Lvi** (zalozeni 2017 - NOSITEL HOKEJOVE TRADICE V MESTE, mestska zastupitelnost zalozila po odchodu HC Most do Slaneho), zalozeni mestskou zastupitelnosti) - zcela novy klub. 2018/19 postup do 2. ligy. Hraji v Krajske lize muzu UlK. Patterns: Sokol Uhlomost, Uhlomost, TJ Baník Most, Baník Most, HC Most, Mostečtí Lvi. city Most. POZOR: NE 'Mostek' (Královéhradecky kraj) ani 'Kamenny Most' (Praha) - JINA MESTA (D44 - identita = lokalita).</t>
+          <t>city ✓ (město na Orlickoústecku). || city ✓ (město). || Choceň (Wiki - registr ustavy 04/2026). Východocesky/Pardubicky kraj. city Choceň.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Most</t>
+          <t>Choceň</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0166</t>
+          <t>CLUB_S2005_06_0172</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HC Chotěboř (STČ)</t>
+          <t>Stadion Kutná Hora (STČ)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>HC Chotěboř (STČ)</t>
+          <t>Stadion Kutná Hora (STČ)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -23742,34 +23993,34 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0181</t>
+          <t>CLUB_S2004_05_0179</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>B-tým Spartak Chotěboř (CLUB_S1953_54_0316). Přejmenováno II → B (D21). prev na 52/53 0263 (A-tým, B 52/53 neexistoval). || Chotěboř = Spartak Chotěboř (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Havlíčkův Brod). S-P = Semily-Pardubice. city Chotěboř.</t>
+          <t>Smart fix prev: chybělo → 50/51 0097 (ČKD Kutná Hora). Klub v 51/52 nehrál (mezera). Pozn.: Pavlovo zjištění 04/2026 — 50/51 0097 má v parentézi chybně „Viktoria Sedlec" (Sedlec je jiný klub, ne předchůdce). || Kutná Hora = HC Sparta/Dynamo Kutná Hora (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Hlavni chain: Sparta KH -&gt; Sokol -&gt; Dynamo Kutná Hora -&gt; HC Kutná Hora. UNESCO mesto. city Kutná Hora.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Chotěboř</t>
+          <t>Kutná Hora</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0167</t>
+          <t>CLUB_S2005_06_0173</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HC Litomyšl</t>
+          <t>Sklo Bohemia Světlá nad Sázavou (STČ)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>HC Litomyšl</t>
+          <t>Sklo Bohemia Světlá nad Sázavou (STČ)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -23784,34 +24035,34 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0175</t>
+          <t>CLUB_S2004_05_0178</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Litomyšl (Wiki - registr ustavy 04/2026). Východocesky/Pardubicky kraj. Slovan Litomysl - city Litomyšl.</t>
+          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou. || TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Slovan Litomyšl</t>
+          <t>Světlá nad Sázavou</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0168</t>
+          <t>CLUB_S2005_06_0174</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HC Slovan Moravská Třebová</t>
+          <t>HC Skuteč</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>HC Slovan Moravská Třebová</t>
+          <t>HC Skuteč</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -23826,34 +24077,34 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0174</t>
+          <t>CLUB_S2004_05_0191</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem. || Moravská Třebová = Slovan/Slavoj Moravská Třebová (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Svitavy). POZOR: NE Třebová Česká (Pardubicky), NE Trebon (Jihocesky). city Moravská Třebová.</t>
+          <t>Jiskra Skuteč (district=Chrudim). || Skuteč = TJ Jiskra Skuteč (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim). Patterns: Sokol -&gt; Jiskra Skuteč. city Skuteč.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Moravská Třebová</t>
+          <t>Skuteč</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0169</t>
+          <t>CLUB_S2005_06_0175</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Sokol Staré Jesenčany</t>
+          <t>TJ Svitavy</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Sokol Staré Jesenčany</t>
+          <t>TJ Svitavy (N)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -23861,41 +24112,41 @@
           <t>30_Pardubický</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>L40</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0176</t>
-        </is>
-      </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Staré Jesenčany = TJ Sokol Staré Jesenčany (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Pardubice). city Staré Jesenčany.</t>
+          <t>Svit = Iskra Chemosvit (Wiki D42 - registr ustavy 04/2026). Slovensky kraj (Vysoke Tatry). Tatrasvit / Chemosvit = chemicky podnik. POZOR: NE Svit Gottwaldov (Bata, Zlin)! city Svit.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Staré Jesenčany</t>
+          <t>Svitavy</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0170</t>
+          <t>CLUB_S2005_06_0176</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HC Hlinsko</t>
+          <t>Spartak Polička</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>HC Hlinsko</t>
+          <t>Spartak Polička</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -23910,39 +24161,39 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0180</t>
+          <t>CLUB_S2004_05_0190</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>B-tým TJ Spartak Praha Sokolovo (CLUB_S1953_54_0001 v 1. lize). Doplnění „Praha" do názvu (Pavlovo rozhodnutí — plný název klubu, ne zkrácená forma). city: Sokolovo = čtvrť Prahy (D23) → „Praha". Smart fix prev → 52/53 0001 (A-tým, B 52/53 neexistoval). || Spartak Praha Sokolovo B 53/54 (B-tým, 30_PHA_mesto). Sparta Praha = HC Sparta Praha (Wiki D18 / D42). Genealogie: AC Sparta Praha (1903) -&gt; Sokol Sparta Bubeneč (1948) -&gt; ZSJ Bratrství Sparta Praha (1949) -&gt; ZSJ Sparta ČKD Sokolovo Praha (1951, ČKD = Českomoravská-Kolben-Daněk) -&gt; TJ Spartak Praha Sokolovo (1952) -&gt; TJ Sparta ČKD Praha (1965) -&gt; HC Sparta Praha (1990). city Praha (D23, Bubeneč = čtvrť Prahy 7). || Sokolov = HC Baník Sokolov (Wiki - registr ustavy 04/2026). ZALOZEN 1945 jako SK FHD Dolní Rychnov (FHD = Falknovske hnedouhelne doly - Sokolov se drive jmenoval Falknov nL Ohri). Genealogie: SK FHD (1945) -&gt; TJ Banik Sokolov (1953+ DSO) -&gt; NHL (1 sezona) -&gt; 1969 nahradil zruseny Duklu Litomerice v A skupine CNHL -&gt; NHL (1 sezona) -&gt; 1990 znovu 1.NHL -&gt; 1997 sestup do 2.ligy -&gt; 2002 prejmenovani na HC Banik Sokolov -&gt; 2019/20 do Maxa Ligy. Falknov nad Ohri se 1948 prejmenoval na Sokolov. city Sokolov.</t>
+          <t>Polička (Wiki - registr ustavy 04/2026). Východocesky/Pardubicky kraj. city Polička.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Sokolov</t>
+          <t>Polička</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0171</t>
+          <t>CLUB_S2005_06_0181</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Spartak Choceň</t>
+          <t>Jiskra Humpolec</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spartak Choceň</t>
+          <t>Jiskra Humpolec</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>30_Pardubický</t>
+          <t>30_Vysočina</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -23952,39 +24203,39 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0177</t>
+          <t>CLUB_S2004_05_0201</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>city ✓ (město na Orlickoústecku). || city ✓ (město). || Choceň (Wiki - registr ustavy 04/2026). Východocesky/Pardubicky kraj. city Choceň.</t>
+          <t>Smart fix prev: 51/52 nehrál (Humpolec mezera) → 50/51 0760 (Sokol Humpolec). Identity transition: Humpolec → Sokol Sukno Humpolec (52/53, „Sukno" = název závodu). || Sokol Sukno Humpolec 52/53 (20_Jihlavský okresni). KLÍČOVÝ ROK - patronat podniku SUKNO (textilni podnik). Humpolec = TJ Jiskra Humpolec (Wiki D42 - Pavlovo upresneni 04/2026, hokej.cz). Genealogie: Sokol Humpolec (1949-) -&gt; Sokol Sukno Humpolec (1952, patronat podniku SUKNO - textilni podnik v Humpolci, Humpolec proslulý vyrobou suken/laken) -&gt; Jiskra Humpolec (1953/54, DSO reforma) -&gt; TJ Jiskra Humpolec (dnes). city Humpolec (NE Sukno Humpolec - Sukno je podnik, ne mesto). || Humpolec = HC Humpolec (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihocesky kraj. Hlavni chain: Sokol Humpolec -&gt; Sukno Humpolec (textilní podnik) -&gt; Jiskra Humpolec -&gt; HC Humpolec. city Humpolec.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Choceň</t>
+          <t>Humpolec</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0172</t>
+          <t>CLUB_S2005_06_0182</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Stadion Kutná Hora (STČ)</t>
+          <t>SK Telč</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Stadion Kutná Hora (STČ)</t>
+          <t>SK Telč</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>30_Pardubický</t>
+          <t>30_Vysočina</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -23994,39 +24245,39 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0179</t>
+          <t>CLUB_S2004_05_0206</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Smart fix prev: chybělo → 50/51 0097 (ČKD Kutná Hora). Klub v 51/52 nehrál (mezera). Pozn.: Pavlovo zjištění 04/2026 — 50/51 0097 má v parentézi chybně „Viktoria Sedlec" (Sedlec je jiný klub, ne předchůdce). || Kutná Hora = HC Sparta/Dynamo Kutná Hora (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Hlavni chain: Sparta KH -&gt; Sokol -&gt; Dynamo Kutná Hora -&gt; HC Kutná Hora. UNESCO mesto. city Kutná Hora.</t>
+          <t>Oprava city: závodní „Motorpal" → „Telč". || Motorpal Telč 52/53 (20_Jihlavský). KLÍČOVÝ ROK - patronat podniku Motorpal (vstrikovaci systemy). Telč = SK Telč / Rytíři z Telče (Wiki D42 - Pavlovo 04/2026). Sokol Telč (49/50) -&gt; Motorpal Telč (52/53, podnik Motorpal - vyroba dieselovych vstrikovacich systemu) -&gt; Spartak Telč (53/54+, DSO reforma) -&gt; SK Telč -&gt; Rytíři z Telče (dnes). city Telč. || Motorpal Telč 52/53 (20_Jihlavský). KLÍČOVÝ ROK - patronat Motorpal (vstrikovaci systemy). Telč = SK Telč / Rytíři z Telče (Wiki D42 - Pavlovo 04/2026). Sokol -&gt; Motorpal (52/53) -&gt; Spartak (53/54+, DSO) -&gt; SK Telč. city Telč. || Telč = HC Telč (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. Hlavni chain: Sokol Telč -&gt; Spartak Telč -&gt; Motorpal Telč (vstrikovaci system) -&gt; HC Telč. UNESCO mesto. city Telč.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Kutná Hora</t>
+          <t>Telč</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0173</t>
+          <t>CLUB_S2005_06_0183</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Sklo Bohemia Světlá nad Sázavou (STČ)</t>
+          <t>Sokol Čechočovice</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sklo Bohemia Světlá nad Sázavou (STČ)</t>
+          <t>Sokol Čechočovice</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>30_Pardubický</t>
+          <t>30_Vysočina</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -24036,39 +24287,39 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0178</t>
+          <t>CLUB_S2004_05_0204</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Světlá nad Sázavou = HC SB Světlá nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj (okres Havlickuv Brod). '(VYS)' = Vysocina. **SB** = pravdepodobne stavebni podnik. city Světlá nad Sázavou. || TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Čechočovice = Sokol Čechočovice (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). city Čechočovice. || Vladislav = Sokol/Jiskra Vladislav (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). 'Vladislav' jako jmenowy nazev. city Vladislav.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Světlá nad Sázavou</t>
+          <t>Čechočovice</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0174</t>
+          <t>CLUB_S2005_06_0184</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>HC Skuteč</t>
+          <t>TJ Náměšť nad Oslavou</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>HC Skuteč</t>
+          <t>TJ Náměšť nad Oslavou</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>30_Pardubický</t>
+          <t>30_Vysočina</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -24078,44 +24329,39 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0191</t>
+          <t>CLUB_S2004_05_0205</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Jiskra Skuteč (district=Chrudim). || Skuteč = TJ Jiskra Skuteč (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim). Patterns: Sokol -&gt; Jiskra Skuteč. city Skuteč.</t>
+          <t>Náměšť nad Oslavou = TJ Jiskra Náměšť (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Třebíč). **Náměšť nL Oslavou** = vyznamne **vojenske letiste** (zakladna 22. letecke zakladny). 'B' = druzstvo B. Zámek Náměšť nL Oslavou = národní kulturní pamatka (UNESCO). NE Náměšť na Hané (Severomoravsky/Olomoucko)! city Náměšť nad Oslavou.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Skuteč</t>
+          <t>Náměšť nad Oslavou</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0175</t>
+          <t>CLUB_S2005_06_0185</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TJ Svitavy</t>
+          <t>HAS Jihlava</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TJ Svitavy (N)</t>
+          <t>HAS Jihlava</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>30_Pardubický</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>30_Vysočina</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -24123,36 +24369,41 @@
           <t>L40</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0202</t>
+        </is>
+      </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Svit = Iskra Chemosvit (Wiki D42 - registr ustavy 04/2026). Slovensky kraj (Vysoke Tatry). Tatrasvit / Chemosvit = chemicky podnik. POZOR: NE Svit Gottwaldov (Bata, Zlin)! city Svit.</t>
+          <t>Jihlava = HAS Jihlava (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **HAS** = pravdepodobne Hokejovy ASociacni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Svitavy</t>
+          <t>HAS Jihlava</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0176</t>
+          <t>CLUB_S2005_06_0186</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Spartak Polička</t>
+          <t>HHK Velké Meziříčí</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spartak Polička</t>
+          <t>HHK Velké Meziříčí</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>30_Pardubický</t>
+          <t>30_Vysočina</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -24162,39 +24413,39 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0190</t>
+          <t>CLUB_S2004_05_0043</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Polička (Wiki - registr ustavy 04/2026). Východocesky/Pardubicky kraj. city Polička.</t>
+          <t>Sokol Velké Meziříčí. Jiný klub od 0484 (CLUB_S1954_55_0484 bez prefixu). || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK Velké Meziříčí (Wiki D42 - Pavlovo 04/2026). Velké Meziříčí (50/51-) -&gt; Sokol Velké Meziříčí (54/55) -&gt; Spartak Velké Meziříčí (56/57+, DSO reforma) -&gt; kontinuita -&gt; HHK Velké Meziříčí. Patterns: Velké Meziříčí, Sokol VM, Spartak VM. POZOR: 50/51 0731 'České Meziříčí' je JINE MESTO (Královéhradecký). Tatran Valašské Meziříčí je tez JINE MESTO (Gottwaldovský/Zlinsky). city Velké Meziříčí. || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK VM (Wiki D42 - Pavlovo 04/2026). Sokol VM -&gt; Spartak VM (56/57+). NE České ani Valašské Meziříčí. city Velké Meziříčí. || Velké Meziříčí = Spartak/HC Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. POZOR: NE Valašské Meziříčí (Severomoravsky/Zlinsky)! city Velké Meziříčí.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Polička</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0181</t>
+          <t>CLUB_S2005_06_0187</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Jiskra Humpolec</t>
+          <t>HHK Velké Meziříčí B (VYS)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jiskra Humpolec</t>
+          <t>HHK Velké Meziříčí B (VYS)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>30_Vysočina</t>
+          <t>30_Jihomoravský-Zlín</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -24204,39 +24455,39 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0201</t>
+          <t>CLUB_S2004_05_0043</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Smart fix prev: 51/52 nehrál (Humpolec mezera) → 50/51 0760 (Sokol Humpolec). Identity transition: Humpolec → Sokol Sukno Humpolec (52/53, „Sukno" = název závodu). || Sokol Sukno Humpolec 52/53 (20_Jihlavský okresni). KLÍČOVÝ ROK - patronat podniku SUKNO (textilni podnik). Humpolec = TJ Jiskra Humpolec (Wiki D42 - Pavlovo upresneni 04/2026, hokej.cz). Genealogie: Sokol Humpolec (1949-) -&gt; Sokol Sukno Humpolec (1952, patronat podniku SUKNO - textilni podnik v Humpolci, Humpolec proslulý vyrobou suken/laken) -&gt; Jiskra Humpolec (1953/54, DSO reforma) -&gt; TJ Jiskra Humpolec (dnes). city Humpolec (NE Sukno Humpolec - Sukno je podnik, ne mesto). || Humpolec = HC Humpolec (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihocesky kraj. Hlavni chain: Sokol Humpolec -&gt; Sukno Humpolec (textilní podnik) -&gt; Jiskra Humpolec -&gt; HC Humpolec. city Humpolec.</t>
+          <t>Sokol Velké Meziříčí. Jiný klub od 0484 (CLUB_S1954_55_0484 bez prefixu). || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK Velké Meziříčí (Wiki D42 - Pavlovo 04/2026). Velké Meziříčí (50/51-) -&gt; Sokol Velké Meziříčí (54/55) -&gt; Spartak Velké Meziříčí (56/57+, DSO reforma) -&gt; kontinuita -&gt; HHK Velké Meziříčí. Patterns: Velké Meziříčí, Sokol VM, Spartak VM. POZOR: 50/51 0731 'České Meziříčí' je JINE MESTO (Královéhradecký). Tatran Valašské Meziříčí je tez JINE MESTO (Gottwaldovský/Zlinsky). city Velké Meziříčí. || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK VM (Wiki D42 - Pavlovo 04/2026). Sokol VM -&gt; Spartak VM (56/57+). NE České ani Valašské Meziříčí. city Velké Meziříčí. || Velké Meziříčí = Spartak/HC Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. POZOR: NE Valašské Meziříčí (Severomoravsky/Zlinsky)! city Velké Meziříčí.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Humpolec</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0182</t>
+          <t>CLUB_S2005_06_0188</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SK Telč</t>
+          <t>HC Uherský Brod (ZLI)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SK Telč</t>
+          <t>HC Uherský Brod (ZLI)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>30_Vysočina</t>
+          <t>30_Jihomoravský-Zlín</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -24246,39 +24497,39 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0206</t>
+          <t>CLUB_S2004_05_0210</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Oprava city: závodní „Motorpal" → „Telč". || Motorpal Telč 52/53 (20_Jihlavský). KLÍČOVÝ ROK - patronat podniku Motorpal (vstrikovaci systemy). Telč = SK Telč / Rytíři z Telče (Wiki D42 - Pavlovo 04/2026). Sokol Telč (49/50) -&gt; Motorpal Telč (52/53, podnik Motorpal - vyroba dieselovych vstrikovacich systemu) -&gt; Spartak Telč (53/54+, DSO reforma) -&gt; SK Telč -&gt; Rytíři z Telče (dnes). city Telč. || Motorpal Telč 52/53 (20_Jihlavský). KLÍČOVÝ ROK - patronat Motorpal (vstrikovaci systemy). Telč = SK Telč / Rytíři z Telče (Wiki D42 - Pavlovo 04/2026). Sokol -&gt; Motorpal (52/53) -&gt; Spartak (53/54+, DSO) -&gt; SK Telč. city Telč. || Telč = HC Telč (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. Hlavni chain: Sokol Telč -&gt; Spartak Telč -&gt; Motorpal Telč (vstrikovaci system) -&gt; HC Telč. UNESCO mesto. city Telč.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Telč</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0183</t>
+          <t>CLUB_S2005_06_0189</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Sokol Čechočovice</t>
+          <t>HC Nedvědice</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Sokol Čechočovice</t>
+          <t>HC Nedvědice</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>30_Vysočina</t>
+          <t>30_Jihomoravský-Zlín</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -24288,39 +24539,39 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0204</t>
+          <t>CLUB_S2004_05_0209</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Čechočovice = Sokol Čechočovice (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). city Čechočovice. || Vladislav = Sokol/Jiskra Vladislav (Wiki D42 - registr ustavy 04/2026). Vysocina kraj (okres Třebíč). 'Vladislav' jako jmenowy nazev. city Vladislav.</t>
+          <t>B-tým Spartak Nedvědice. city ✓. || Nedvědice = Spartak Nedvědice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov, dnes Vysocina). MEZ = Moravske elektrotechnicke zavody (Vsetin pobocka). city Nedvědice.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Čechočovice</t>
+          <t>Nedvědice</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0184</t>
+          <t>CLUB_S2005_06_0190</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TJ Náměšť nad Oslavou</t>
+          <t>SK Minerva Boskovice</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TJ Náměšť nad Oslavou</t>
+          <t>SK Minerva Boskovice</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>30_Vysočina</t>
+          <t>30_Jihomoravský-Zlín</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -24330,39 +24581,39 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0205</t>
+          <t>CLUB_S2004_05_0211</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou = TJ Jiskra Náměšť (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Třebíč). **Náměšť nL Oslavou** = vyznamne **vojenske letiste** (zakladna 22. letecke zakladny). 'B' = druzstvo B. Zámek Náměšť nL Oslavou = národní kulturní pamatka (UNESCO). NE Náměšť na Hané (Severomoravsky/Olomoucko)! city Náměšť nad Oslavou.</t>
+          <t>doplněno při sjednocení club_id || Boskovice = TJ Minerva Boskovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). **Minerva** = vyrobce kancelarskych a hospodynskych stroju (psaci stroje). city Boskovice.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou</t>
+          <t>Minerva Boskovice</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0185</t>
+          <t>CLUB_S2005_06_0191</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HAS Jihlava</t>
+          <t>HC Uherské Hradiště (ZLI)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>HAS Jihlava</t>
+          <t>HC Uherské Hradiště (ZLI)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>30_Vysočina</t>
+          <t>30_Jihomoravský-Zlín</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -24372,39 +24623,39 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0202</t>
+          <t>CLUB_S2004_05_0212</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Jihlava = HAS Jihlava (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **HAS** = pravdepodobne Hokejovy ASociacni klub. city Jihlava.</t>
+          <t>Spartak Uherské Hradiště. city ✓. || Uherské Hradiště (Wiki - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj. POZN: blizko Uherskeho Hradiste byly Sokol Stare Mesto, Tatran Uhersky Ostroh atd. city Uherské Hradiště.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>HAS Jihlava</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0186</t>
+          <t>CLUB_S2005_06_0192</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí</t>
+          <t>HC Moravské Budějovice (VYS)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí</t>
+          <t>HC Moravské Budějovice (VYS)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>30_Vysočina</t>
+          <t>30_Jihomoravský-Zlín</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -24414,34 +24665,34 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0043</t>
+          <t>CLUB_S2004_05_0203</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Sokol Velké Meziříčí. Jiný klub od 0484 (CLUB_S1954_55_0484 bez prefixu). || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK Velké Meziříčí (Wiki D42 - Pavlovo 04/2026). Velké Meziříčí (50/51-) -&gt; Sokol Velké Meziříčí (54/55) -&gt; Spartak Velké Meziříčí (56/57+, DSO reforma) -&gt; kontinuita -&gt; HHK Velké Meziříčí. Patterns: Velké Meziříčí, Sokol VM, Spartak VM. POZOR: 50/51 0731 'České Meziříčí' je JINE MESTO (Královéhradecký). Tatran Valašské Meziříčí je tez JINE MESTO (Gottwaldovský/Zlinsky). city Velké Meziříčí. || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK VM (Wiki D42 - Pavlovo 04/2026). Sokol VM -&gt; Spartak VM (56/57+). NE České ani Valašské Meziříčí. city Velké Meziříčí. || Velké Meziříčí = Spartak/HC Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. POZOR: NE Valašské Meziříčí (Severomoravsky/Zlinsky)! city Velké Meziříčí.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Velké Meziříčí</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0187</t>
+          <t>CLUB_S2005_06_0193</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí B (VYS)</t>
+          <t>IHC Břeclav</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí B (VYS)</t>
+          <t>IHC Břeclav</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24456,34 +24707,34 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0043</t>
+          <t>CLUB_S2004_05_0214</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Sokol Velké Meziříčí. Jiný klub od 0484 (CLUB_S1954_55_0484 bez prefixu). || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK Velké Meziříčí (Wiki D42 - Pavlovo 04/2026). Velké Meziříčí (50/51-) -&gt; Sokol Velké Meziříčí (54/55) -&gt; Spartak Velké Meziříčí (56/57+, DSO reforma) -&gt; kontinuita -&gt; HHK Velké Meziříčí. Patterns: Velké Meziříčí, Sokol VM, Spartak VM. POZOR: 50/51 0731 'České Meziříčí' je JINE MESTO (Královéhradecký). Tatran Valašské Meziříčí je tez JINE MESTO (Gottwaldovský/Zlinsky). city Velké Meziříčí. || Sokol Velké Meziříčí 54/55 (30_Jihlavský). Velké Meziříčí = HHK VM (Wiki D42 - Pavlovo 04/2026). Sokol VM -&gt; Spartak VM (56/57+). NE České ani Valašské Meziříčí. city Velké Meziříčí. || Velké Meziříčí = Spartak/HC Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. POZOR: NE Valašské Meziříčí (Severomoravsky/Zlinsky)! city Velké Meziříčí.</t>
+          <t>Břeclav = IHC Břeclav (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **IHC** = post-revolucni Independent Hockey Club. Patterns: HC Colligo Břeclav. city Břeclav.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Velké Meziříčí</t>
+          <t>IHC Břeclav</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0188</t>
+          <t>CLUB_S2005_06_0194</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HC Uherský Brod (ZLI)</t>
+          <t>HK Slovan Rosice</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>HC Uherský Brod (ZLI)</t>
+          <t>HK Slovan Rosice</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -24498,34 +24749,34 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0210</t>
+          <t>CLUB_S2004_05_0213</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Rosice = TJ Dynamo Rosice B (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Rosice u Brna (Jihomoravsky/Brno-venkov, banicke), Rosice nL Labem (Vychodocesky/Pardubice). 'B' = druzstvo. K overeni. city Rosice.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rosice</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0189</t>
+          <t>CLUB_S2005_06_0195</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HC Nedvědice</t>
+          <t>HK Kroměříž VTJ B (ZLI)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>HC Nedvědice</t>
+          <t>HK Kroměříž VTJ B (ZLI)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -24540,34 +24791,34 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0209</t>
+          <t>CLUB_S2004_05_0216</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>B-tým Spartak Nedvědice. city ✓. || Nedvědice = Spartak Nedvědice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov, dnes Vysocina). MEZ = Moravske elektrotechnicke zavody (Vsetin pobocka). city Nedvědice.</t>
+          <t>Odstranění suffixu „A" (kolegova nedůslednost). Rozšíření „Val.Meziříčí" → „Valašské Meziříčí" (plný název v clean i city). || PS Valašské Meziříčí 52/53. PS = Poz.stavby? Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Valašské Meziříčí = mesto v Zlinsky kraji (Gottwaldovský/Zlinsky), Vsetinsky/Roznovsky region. Tatran Val.Meziříčí, PS, Tesla Val.Meziříčí. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || PS Valašské Meziříčí 52/53. PS = Poz.stavby. Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Mesto v Zlinsky kraji, Vsetinsky region. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || Valašské Meziříčí = HC Bobři Valašské Meziříčí (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Zlinsky kraj. Tesla Valašské Meziříčí (podnik) -&gt; PS Valašské Meziříčí (Pozemni stavby) -&gt; TJ -&gt; Bobri. POZOR: NE Velke Mezirici (Vysocina). city Valašské Meziříčí.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Nedvědice</t>
+          <t>Valašské Meziříčí</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0190</t>
+          <t>CLUB_S2005_06_0196</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SK Minerva Boskovice</t>
+          <t>HC Žraloci Vyškov</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SK Minerva Boskovice</t>
+          <t>HC Žraloci Vyškov</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -24582,34 +24833,34 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0211</t>
+          <t>CLUB_S2004_05_0215</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>doplněno při sjednocení club_id || Boskovice = TJ Minerva Boskovice (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Blansko). **Minerva** = vyrobce kancelarskych a hospodynskych stroju (psaci stroje). city Boskovice.</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem. || Vyškov = Hokej Vyškov (Wiki - registr ustavy 04/2026). Jihomoravsky kraj. Mensi okresni klub - liga. city Vyškov.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Minerva Boskovice</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0191</t>
+          <t>CLUB_S2005_06_0197</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HC Uherské Hradiště (ZLI)</t>
+          <t>TJ Lokomotiva Uherský Ostroh (ZLI)</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>HC Uherské Hradiště (ZLI)</t>
+          <t>TJ Lokomotiva Uherský Ostroh (ZLI)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -24624,34 +24875,34 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0212</t>
+          <t>CLUB_S2004_05_0218</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Spartak Uherské Hradiště. city ✓. || Uherské Hradiště (Wiki - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj. POZN: blizko Uherskeho Hradiste byly Sokol Stare Mesto, Tatran Uhersky Ostroh atd. city Uherské Hradiště.</t>
+          <t>TJ Tatran Uherský Ostroh. Oprava clean+city: "Uhersky" → "Uherský" (diakritika). prev k overeni Pavlem - mozny kandidat 55/56 0037 Tatran Uherský Ostroh (stejny clean!). || Uherský Ostroh = Tatran Uherský Ostroh (Wiki D42 - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj (okres Uherske Hradiste). Dyas = podnik. city Uherský Ostroh.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Uherské Hradiště</t>
+          <t>Uherský Ostroh</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0192</t>
+          <t>CLUB_S2005_06_0198</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HC Moravské Budějovice (VYS)</t>
+          <t>HLC Bulldogs Brno</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>HC Moravské Budějovice (VYS)</t>
+          <t>HLC Bulldogs Brno</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -24666,34 +24917,34 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0203</t>
+          <t>CLUB_S2004_05_0217</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno. || TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Bulldogs Brno</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0193</t>
+          <t>CLUB_S2005_06_0201</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>IHC Břeclav</t>
+          <t>HK Slovan Rosice ,HK Kroměříž VTJ B ,HC Žraloci Vyškov ukončena činnost</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>IHC Břeclav</t>
+          <t>HK Slovan Rosice ,HK Kroměříž VTJ B ,HC Žraloci Vyškov ukončena činnost</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -24708,39 +24959,39 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0214</t>
+          <t>CLUB_S2004_05_0213</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Břeclav = IHC Břeclav (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **IHC** = post-revolucni Independent Hockey Club. Patterns: HC Colligo Břeclav. city Břeclav.</t>
+          <t>Rosice = TJ Dynamo Rosice B (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Rosice u Brna (Jihomoravsky/Brno-venkov, banicke), Rosice nL Labem (Vychodocesky/Pardubice). 'B' = druzstvo. K overeni. city Rosice.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>IHC Břeclav</t>
+          <t>Rosice</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0194</t>
+          <t>CLUB_S2005_06_0202</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HK Slovan Rosice</t>
+          <t>SK Karviná</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>HK Slovan Rosice</t>
+          <t>SK Karviná</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Zlín</t>
+          <t>30_Severomoravský</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -24750,39 +25001,39 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0213</t>
+          <t>CLUB_S2004_05_0223</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Rosice = TJ Dynamo Rosice B (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Rosice u Brna (Jihomoravsky/Brno-venkov, banicke), Rosice nL Labem (Vychodocesky/Pardubice). 'B' = druzstvo. K overeni. city Rosice.</t>
+          <t>Dukla Stalingrad. Almanach uvádí „(Dukla Karviná)" - identita k vyjasneni Pavlem (možná předchozí název, ale NEPOTVRZENO). city k vyjasneni. || Karviná = HC Baník Karviná (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. POZN: HC Banik Ostrava se pristehoval do Karvine 1995. city Karviná. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Rosice</t>
+          <t>Karviná</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0195</t>
+          <t>CLUB_S2005_06_0203</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>HK Kroměříž VTJ B (ZLI)</t>
+          <t>TJ Horní Benešov</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>HK Kroměříž VTJ B (ZLI)</t>
+          <t>TJ Horní Benešov</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Zlín</t>
+          <t>30_Severomoravský</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -24792,39 +25043,39 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0216</t>
+          <t>CLUB_S2004_05_0220</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Odstranění suffixu „A" (kolegova nedůslednost). Rozšíření „Val.Meziříčí" → „Valašské Meziříčí" (plný název v clean i city). || PS Valašské Meziříčí 52/53. PS = Poz.stavby? Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Valašské Meziříčí = mesto v Zlinsky kraji (Gottwaldovský/Zlinsky), Vsetinsky/Roznovsky region. Tatran Val.Meziříčí, PS, Tesla Val.Meziříčí. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || PS Valašské Meziříčí 52/53. PS = Poz.stavby. Valašské Meziříčí = JINÉ MĚSTO od Velké Meziříčí! Mesto v Zlinsky kraji, Vsetinsky region. Wiki D42 - Pavlovo 04/2026. city Valašské Meziříčí. || Valašské Meziříčí = HC Bobři Valašské Meziříčí (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Zlinsky kraj. Tesla Valašské Meziříčí (podnik) -&gt; PS Valašské Meziříčí (Pozemni stavby) -&gt; TJ -&gt; Bobri. POZOR: NE Velke Mezirici (Vysocina). city Valašské Meziříčí.</t>
+          <t>Brano Horní Benešov 52/53 (20_Ostravský). Brano = strojirensky podnik. Horní Benešov + Dolní Benešov = JINE MESTO od Benesov u Prahy (Stredocesky)! Horní Benešov / Dolní Benešov jsou obce ve Slezsku (Bruntal/Opava) - Ostravsky kraj. Brano Horní Benešov = strojirensky podnik Brano. MSA Dolní Benešov = MSA strojirenstvi. Wiki D42 - Pavlovo upresneni 04/2026. NE Benesov u Prahy chain! || Brano Horní Benešov 52/53 (20_Ostravský). Brano = Brany podnik. Horní Benešov / Dolní Benešov = JINÉ MĚSTO od Benešov (Stredocesky). Horní Benešov = mesto v okrese Bruntal (Olomoucky/Moravskoslezsky). Dolní Benešov = mesto v okrese Opava (Moravskoslezsky). Brano = Brany podnik (Horni Benesov, vyroba dveri). MSA = Moravskoslezska armaturka (Dolni Benesov). Wiki D42 - Pavlovo upresneni 04/2026. city Horní Benešov / Dolní Benešov (NIKDY neni Stredocesky Benesov). || Horní Benešov = Spartak Horní Benešov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). POZOR: Dolni Benesov u Opavy! Vsichni Benešovi v okrese - Horni, Dolni, Benesov u Prahy. city Horní Benešov.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Valašské Meziříčí</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0196</t>
+          <t>CLUB_S2005_06_0204</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HC Žraloci Vyškov</t>
+          <t>HC Kopřivnice</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>HC Žraloci Vyškov</t>
+          <t>HC Kopřivnice</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Zlín</t>
+          <t>30_Severomoravský</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -24834,39 +25085,39 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0215</t>
+          <t>CLUB_S2004_05_0219</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem. || Vyškov = Hokej Vyškov (Wiki - registr ustavy 04/2026). Jihomoravsky kraj. Mensi okresni klub - liga. city Vyškov.</t>
+          <t>Kopřivnice = HC ISMM Kopřivnice (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Mestske TATRA - automobilka. Patterns: Tatra Koprivnice, ISMM. city Kopřivnice.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Tatra Kopřivnice</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0197</t>
+          <t>CLUB_S2005_06_0205</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TJ Lokomotiva Uherský Ostroh (ZLI)</t>
+          <t>HC Frýdek Místek</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TJ Lokomotiva Uherský Ostroh (ZLI)</t>
+          <t>HC Frýdek Místek</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Zlín</t>
+          <t>30_Severomoravský</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -24876,39 +25127,39 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0218</t>
+          <t>CLUB_S2004_05_0222</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>TJ Tatran Uherský Ostroh. Oprava clean+city: "Uhersky" → "Uherský" (diakritika). prev k overeni Pavlem - mozny kandidat 55/56 0037 Tatran Uherský Ostroh (stejny clean!). || Uherský Ostroh = Tatran Uherský Ostroh (Wiki D42 - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj (okres Uherske Hradiste). Dyas = podnik. city Uherský Ostroh.</t>
+          <t>Frýdek-Místek = TJ Slezan Frýdek Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. city Frýdek-Místek.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Uherský Ostroh</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0198</t>
+          <t>CLUB_S2005_06_0206</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HLC Bulldogs Brno</t>
+          <t>HC Studénka</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>HLC Bulldogs Brno</t>
+          <t>HC Studénka</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Zlín</t>
+          <t>30_Severomoravský</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -24918,39 +25169,39 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0217</t>
+          <t>CLUB_S2004_05_0224</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Brno = HLC Bulldogs Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. Patterns: HLC Brno + Bulldogs Brno. city Brno. || TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>Studénka = Tatra Studénka (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). Tatra Studenka = vagonka (zelezniční vagony). 'Studenka Pardubice' = nedopatrena dvojnost. city Studénka.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Bulldogs Brno</t>
+          <t>Studénka</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0201</t>
+          <t>CLUB_S2005_06_0207</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>HK Slovan Rosice ,HK Kroměříž VTJ B ,HC Žraloci Vyškov ukončena činnost</t>
+          <t>HC Krnov</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>HK Slovan Rosice ,HK Kroměříž VTJ B ,HC Žraloci Vyškov ukončena činnost</t>
+          <t>HC Krnov</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Zlín</t>
+          <t>30_Severomoravský</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -24960,267 +25211,15 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0213</t>
+          <t>CLUB_S2004_05_0221</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Rosice = TJ Dynamo Rosice B (Wiki D42 - registr ustavy 04/2026). POZOR: vícero - Rosice u Brna (Jihomoravsky/Brno-venkov, banicke), Rosice nL Labem (Vychodocesky/Pardubice). 'B' = druzstvo. K overeni. city Rosice.</t>
+          <t>Krnov = HK Krnov (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Slezky klub. POZN: 2000 prodali druholigovou licenci do HC Stadion Teplice. city Krnov. || Gottwaldov = Zlín = RI Okna Berani Zlín / PSG Zlín (Wiki D42 - registr ustavy 04/2026). Mesto se 1949-1990 jmenovalo Gottwaldov! Hlavni chain: SK Zlín -&gt; Sokol Bata -&gt; Svit Gottwaldov (Svit = Bata) -&gt; Spartak Gottwaldov -&gt; TJ Gottwaldov -&gt; 1990 prejmenovani na PSG Zlín -&gt; Berani Zlín. I. Gottwaldov / II. Gottwaldov = skupiny tymu. city Zlín.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
-        <is>
-          <t>Rosice</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0202</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SK Karviná</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>SK Karviná</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>30_Severomoravský</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>L40</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0223</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Dukla Stalingrad. Almanach uvádí „(Dukla Karviná)" - identita k vyjasneni Pavlem (možná předchozí název, ale NEPOTVRZENO). city k vyjasneni. || Karviná = HC Baník Karviná (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. POZN: HC Banik Ostrava se pristehoval do Karvine 1995. city Karviná. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>Karviná</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0203</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>TJ Horní Benešov</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>TJ Horní Benešov</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>30_Severomoravský</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>L40</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0220</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Brano Horní Benešov 52/53 (20_Ostravský). Brano = strojirensky podnik. Horní Benešov + Dolní Benešov = JINE MESTO od Benesov u Prahy (Stredocesky)! Horní Benešov / Dolní Benešov jsou obce ve Slezsku (Bruntal/Opava) - Ostravsky kraj. Brano Horní Benešov = strojirensky podnik Brano. MSA Dolní Benešov = MSA strojirenstvi. Wiki D42 - Pavlovo upresneni 04/2026. NE Benesov u Prahy chain! || Brano Horní Benešov 52/53 (20_Ostravský). Brano = Brany podnik. Horní Benešov / Dolní Benešov = JINÉ MĚSTO od Benešov (Stredocesky). Horní Benešov = mesto v okrese Bruntal (Olomoucky/Moravskoslezsky). Dolní Benešov = mesto v okrese Opava (Moravskoslezsky). Brano = Brany podnik (Horni Benesov, vyroba dveri). MSA = Moravskoslezska armaturka (Dolni Benesov). Wiki D42 - Pavlovo upresneni 04/2026. city Horní Benešov / Dolní Benešov (NIKDY neni Stredocesky Benesov). || Horní Benešov = Spartak Horní Benešov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). POZOR: Dolni Benesov u Opavy! Vsichni Benešovi v okrese - Horni, Dolni, Benesov u Prahy. city Horní Benešov.</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>Horní Benešov</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0204</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>HC Kopřivnice</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>HC Kopřivnice</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>30_Severomoravský</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>L40</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0219</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Kopřivnice = HC ISMM Kopřivnice (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Mestske TATRA - automobilka. Patterns: Tatra Koprivnice, ISMM. city Kopřivnice.</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>Tatra Kopřivnice</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0205</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>HC Frýdek Místek</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>HC Frýdek Místek</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>30_Severomoravský</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>L40</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0222</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Frýdek-Místek = TJ Slezan Frýdek Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. city Frýdek-Místek.</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>Frýdek Místek</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0206</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>HC Studénka</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>HC Studénka</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>30_Severomoravský</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>L40</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0224</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Studénka = Tatra Studénka (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). Tatra Studenka = vagonka (zelezniční vagony). 'Studenka Pardubice' = nedopatrena dvojnost. city Studénka.</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>Studénka</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0207</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>HC Krnov</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>HC Krnov</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>30_Severomoravský</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>L40</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0221</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Krnov = HK Krnov (Wiki - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Slezky klub. POZN: 2000 prodali druholigovou licenci do HC Stadion Teplice. city Krnov. || Gottwaldov = Zlín = RI Okna Berani Zlín / PSG Zlín (Wiki D42 - registr ustavy 04/2026). Mesto se 1949-1990 jmenovalo Gottwaldov! Hlavni chain: SK Zlín -&gt; Sokol Bata -&gt; Svit Gottwaldov (Svit = Bata) -&gt; Spartak Gottwaldov -&gt; TJ Gottwaldov -&gt; 1990 prejmenovani na PSG Zlín -&gt; Berani Zlín. I. Gottwaldov / II. Gottwaldov = skupiny tymu. city Zlín.</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
         <is>
           <t>Krnov</t>
         </is>
@@ -27538,7 +27537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27612,12 +27611,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0008</t>
+          <t>CLUB_S2005_06_0020</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27632,12 +27631,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0017</t>
+          <t>CLUB_S2005_06_0028</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27652,12 +27651,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0020</t>
+          <t>CLUB_S2005_06_0030</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27672,12 +27671,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0021</t>
+          <t>CLUB_S2005_06_0058</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27692,12 +27691,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0028</t>
+          <t>CLUB_S2005_06_0062</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27712,12 +27711,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0030</t>
+          <t>CLUB_S2005_06_0069</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -27732,12 +27731,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0036</t>
+          <t>CLUB_S2005_06_0118</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chotěboř' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27752,12 +27751,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0058</t>
+          <t>CLUB_S2005_06_0145</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27772,12 +27771,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0062</t>
+          <t>CLUB_S2005_06_0157</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -27792,12 +27791,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0069</t>
+          <t>CLUB_S2005_06_0168</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -27812,12 +27811,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0118</t>
+          <t>CLUB_S2005_06_0173</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27832,12 +27831,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0118</t>
+          <t>CLUB_S2005_06_0196</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -27852,157 +27851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0127</t>
+          <t>CLUB_S2005_06_0198</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0145</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0157</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0168</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0173</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0192</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0196</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0198</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
           <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F22"/>
+  <autoFilter ref="A1:F15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33085,7 +32944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -33305,51 +33164,37 @@
       <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HC Cormoran-auto Krásný  - VTJ Ještěd Liberec 4:1, 7:4</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Kvalifikace o postup do II.ligy</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>NODE_S2005_06_0029</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>L15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0034</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0139</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>TR_S2005_06_00036</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Kvalifikace o postup do II.ligy / 2. kolo</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33357,16 +33202,42 @@
           <t>T</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem  - HC Rokycany 2:0, 4:4</t>
-        </is>
+          <t>HHK Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>Kvalifikace o postup do II.ligy</t>
@@ -33384,17 +33255,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0035</t>
+          <t>CLUB_S2005_06_0186</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0137</t>
+          <t>CLUB_S2004_05_0043</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>TR_S2005_06_00037</t>
+          <t>TR_S2005_06_00043</t>
         </is>
       </c>
     </row>
@@ -33404,16 +33275,42 @@
           <t>T</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HC Chotěboř  - HC Hluboká nad Vltavou  8:5, 7:3</t>
-        </is>
+          <t>SK Karviná</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>17</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>Kvalifikace o postup do II.ligy</t>
@@ -33431,17 +33328,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0036</t>
+          <t>CLUB_S2005_06_0202</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0181</t>
+          <t>CLUB_S2004_05_0223</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>TR_S2005_06_00038</t>
+          <t>TR_S2005_06_00044</t>
         </is>
       </c>
     </row>
@@ -33451,16 +33348,42 @@
           <t>T</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HC Dvůr Králové nad Labem  - HC Mělník  2:2, 2:4</t>
-        </is>
+          <t>HC Uherské Hradiště</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>22</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>Kvalifikace o postup do II.ligy</t>
@@ -33478,52 +33401,92 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0037</t>
+          <t>CLUB_S2005_06_0043</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0166</t>
+          <t>CLUB_S2004_05_0212</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>TR_S2005_06_00039</t>
+          <t>TR_S2005_06_00045</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Kvalifikace o postup do II.ligy / 2. kolo</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2" t="n"/>
-      <c r="T8" s="2" t="n"/>
-      <c r="U8" s="2" t="n"/>
-      <c r="V8" s="2" t="n"/>
-      <c r="W8" s="2" t="n"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HHK Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>33</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>22</v>
+      </c>
+      <c r="M8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Kvalifikace o postup do II.ligy</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0029</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L15</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0186</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>CLUB_S2004_05_0043</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00047</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33531,16 +33494,42 @@
           <t>T</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HC Mělník - HC Chotěboř 5:0, 2:3</t>
-        </is>
+          <t>HC Žďár nad Sázavou (II)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>37</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>24</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10</v>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>Kvalifikace o postup do II.ligy</t>
@@ -33558,17 +33547,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0038</t>
+          <t>CLUB_S2005_06_0045</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0181</t>
+          <t>CLUB_S2004_05_0081</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>TR_S2005_06_00040</t>
+          <t>TR_S2005_06_00048</t>
         </is>
       </c>
     </row>
@@ -33578,16 +33567,42 @@
           <t>T</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HC Cormoran-auto Krásný - HC Roudnice nad Labem 3:2, 2:6</t>
-        </is>
+          <t>HC Mělník</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>38</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
+      <c r="L10" t="n">
+        <v>28</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>Kvalifikace o postup do II.ligy</t>
@@ -33605,17 +33620,17 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0039</t>
+          <t>CLUB_S2005_06_0046</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0137</t>
+          <t>CLUB_S2004_05_0100</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>TR_S2005_06_00041</t>
+          <t>TR_S2005_06_00049</t>
         </is>
       </c>
     </row>
@@ -33627,28 +33642,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí</t>
+          <t>HC Uničov (II)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -33656,10 +33671,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -33678,17 +33693,17 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0186</t>
+          <t>CLUB_S2005_06_0047</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0043</t>
+          <t>CLUB_S2004_05_0096</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>TR_S2005_06_00043</t>
+          <t>TR_S2005_06_00050</t>
         </is>
       </c>
     </row>
@@ -33700,40 +33715,40 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SK Karviná</t>
+          <t>HC Roudnice nad Labem</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>62</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>17</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>Kvalifikace o postup do II.ligy</t>
@@ -33751,453 +33766,15 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CLUB_S2005_06_0202</t>
+          <t>CLUB_S2005_06_0135</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CLUB_S2004_05_0223</t>
+          <t>CLUB_S2004_05_0119</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>TR_S2005_06_00044</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HC Uherské Hradiště</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>11</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>22</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Kvalifikace o postup do II.ligy</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>NODE_S2005_06_0029</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>L15</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0043</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0212</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>TR_S2005_06_00045</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HHK Velké Meziříčí</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>33</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>22</v>
-      </c>
-      <c r="M14" t="n">
-        <v>12</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Kvalifikace o postup do II.ligy</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>NODE_S2005_06_0029</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>L15</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0186</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0043</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>TR_S2005_06_00047</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HC Žďár nad Sázavou (II)</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>37</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>24</v>
-      </c>
-      <c r="M15" t="n">
-        <v>10</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Kvalifikace o postup do II.ligy</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>NODE_S2005_06_0029</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>L15</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0045</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0081</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>TR_S2005_06_00048</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HC Mělník</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>38</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>28</v>
-      </c>
-      <c r="M16" t="n">
-        <v>10</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Kvalifikace o postup do II.ligy</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>NODE_S2005_06_0029</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>L15</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0046</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0100</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>TR_S2005_06_00049</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HC Uničov (II)</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>32</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>17</v>
-      </c>
-      <c r="M17" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Kvalifikace o postup do II.ligy</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>NODE_S2005_06_0029</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>L15</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0047</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0096</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>TR_S2005_06_00050</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>HC Roudnice nad Labem</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>8</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>13</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>62</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Kvalifikace o postup do II.ligy</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>NODE_S2005_06_0029</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>L15</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>CLUB_S2005_06_0135</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>CLUB_S2004_05_0119</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
         <is>
           <t>TR_S2005_06_00051</t>
         </is>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -10513,7 +10513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10577,6 +10577,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14134,8 +14144,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -14265,7 +14273,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -10765,6 +10765,16 @@
           <t>NODE_S2005_06_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -10779,6 +10789,14 @@
         <is>
           <t>NODE_S2004_05_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -10953,6 +10971,16 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -10967,6 +10995,14 @@
         <is>
           <t>NODE_S2004_05_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -11047,6 +11083,16 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11061,6 +11107,14 @@
         <is>
           <t>NODE_S2004_05_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -11094,6 +11148,16 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11108,6 +11172,14 @@
         <is>
           <t>NODE_S2004_05_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -11141,6 +11213,8 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11155,6 +11229,14 @@
         <is>
           <t>NODE_S2004_05_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -11188,6 +11270,8 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11202,6 +11286,14 @@
         <is>
           <t>NODE_S2004_05_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -11235,6 +11327,8 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11249,6 +11343,14 @@
         <is>
           <t>NODE_S2004_05_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -11282,6 +11384,8 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11296,6 +11400,14 @@
         <is>
           <t>NODE_S2004_05_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -11329,6 +11441,8 @@
           <t>NODE_S2005_06_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11343,6 +11457,14 @@
         <is>
           <t>NODE_S2004_05_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -11376,6 +11498,8 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11390,6 +11514,14 @@
         <is>
           <t>NODE_S2004_05_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -11423,6 +11555,8 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11437,6 +11571,14 @@
         <is>
           <t>NODE_S2004_05_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -11470,6 +11612,16 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11484,6 +11636,14 @@
         <is>
           <t>NODE_S2004_05_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -11611,6 +11771,16 @@
           <t>NODE_S2005_06_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11625,6 +11795,14 @@
         <is>
           <t>NODE_S2004_05_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -11658,6 +11836,16 @@
           <t>NODE_S2005_06_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11672,6 +11860,14 @@
         <is>
           <t>NODE_S2004_05_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -11705,6 +11901,12 @@
           <t>NODE_S2005_06_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11719,6 +11921,14 @@
         <is>
           <t>NODE_S2004_05_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -11752,6 +11962,12 @@
           <t>NODE_S2005_06_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11766,6 +11982,14 @@
         <is>
           <t>NODE_S2004_05_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -11799,6 +12023,8 @@
           <t>NODE_S2005_06_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11813,6 +12039,14 @@
         <is>
           <t>NODE_S2004_05_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -11846,6 +12080,8 @@
           <t>NODE_S2005_06_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11860,6 +12096,14 @@
         <is>
           <t>NODE_S2004_05_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -12123,6 +12367,8 @@
           <t>NODE_S2005_06_0032</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12137,6 +12383,14 @@
         <is>
           <t>NODE_S2004_05_0033</t>
         </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -12212,6 +12466,8 @@
           <t>NODE_S2005_06_0032</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12221,6 +12477,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -12395,6 +12659,12 @@
           <t>NODE_S2005_06_0036</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0040</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12409,6 +12679,14 @@
         <is>
           <t>NODE_S2004_05_0039</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -12442,6 +12720,12 @@
           <t>NODE_S2005_06_0036</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0041</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12456,6 +12740,14 @@
         <is>
           <t>NODE_S2004_05_0040</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -12489,6 +12781,8 @@
           <t>NODE_S2005_06_0036</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12503,6 +12797,14 @@
         <is>
           <t>NODE_S2004_05_0041</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -12630,6 +12932,8 @@
           <t>NODE_S2005_06_0036</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12644,6 +12948,14 @@
         <is>
           <t>NODE_S2004_05_0044</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -12771,6 +13083,12 @@
           <t>NODE_S2005_06_0036</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0039</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12785,6 +13103,14 @@
         <is>
           <t>NODE_S2004_05_0047</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -12912,6 +13238,12 @@
           <t>NODE_S2005_06_0049</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0051</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12926,6 +13258,14 @@
         <is>
           <t>NODE_S2004_05_0054</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -12959,6 +13299,8 @@
           <t>NODE_S2005_06_0049</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12973,6 +13315,14 @@
         <is>
           <t>NODE_S2004_05_0055</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -13048,6 +13398,12 @@
           <t>NODE_S2005_06_0052</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0054</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13057,6 +13413,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -13090,6 +13454,8 @@
           <t>NODE_S2005_06_0052</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13099,6 +13465,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -13347,6 +13721,8 @@
           <t>NODE_S2005_06_0055</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13356,6 +13732,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -13525,6 +13909,8 @@
           <t>NODE_S2005_06_0063</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13534,6 +13920,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -13567,6 +13961,8 @@
           <t>NODE_S2005_06_0063</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13576,6 +13972,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -13651,6 +14055,12 @@
           <t>NODE_S2005_06_0066</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0069</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13660,6 +14070,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -13693,6 +14111,8 @@
           <t>NODE_S2005_06_0066</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13702,6 +14122,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -13735,6 +14163,8 @@
           <t>NODE_S2005_06_0066</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13744,6 +14174,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -13824,6 +14262,12 @@
           <t>NODE_S2005_06_0070</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0072</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13838,6 +14282,14 @@
         <is>
           <t>NODE_S2004_05_0068</t>
         </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -13871,6 +14323,8 @@
           <t>NODE_S2005_06_0070</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13885,6 +14339,14 @@
         <is>
           <t>NODE_S2004_05_0069</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -13913,6 +14375,12 @@
           <t>REG_JMZ</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0075</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13927,6 +14395,14 @@
         <is>
           <t>Kontejner L40</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -14002,6 +14478,8 @@
           <t>NODE_S2005_06_0073</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14011,6 +14489,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -14044,6 +14530,8 @@
           <t>NODE_S2005_06_0073</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14053,6 +14541,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -14144,6 +14640,8 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
+    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -14273,6 +14771,7 @@
         </is>
       </c>
     </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -1140,6 +1140,11 @@
           <t>HC Sparta Praha (C)</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F10" t="n">
         <v>52</v>
       </c>
@@ -11213,8 +11218,6 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11270,8 +11273,6 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11327,8 +11328,6 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11384,8 +11383,6 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11441,8 +11438,6 @@
           <t>NODE_S2005_06_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11498,8 +11493,6 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11555,8 +11548,6 @@
           <t>NODE_S2005_06_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11906,7 +11897,6 @@
           <t>NODE_S2005_06_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11967,7 +11957,6 @@
           <t>NODE_S2005_06_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12023,8 +12012,6 @@
           <t>NODE_S2005_06_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12080,8 +12067,6 @@
           <t>NODE_S2005_06_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12367,8 +12352,6 @@
           <t>NODE_S2005_06_0032</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12466,8 +12449,6 @@
           <t>NODE_S2005_06_0032</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12664,7 +12645,6 @@
           <t>NODE_S2005_06_0040</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12725,7 +12705,6 @@
           <t>NODE_S2005_06_0041</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12781,8 +12760,6 @@
           <t>NODE_S2005_06_0036</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12932,8 +12909,6 @@
           <t>NODE_S2005_06_0036</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13088,7 +13063,6 @@
           <t>NODE_S2005_06_0039</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13243,7 +13217,6 @@
           <t>NODE_S2005_06_0051</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13299,8 +13272,6 @@
           <t>NODE_S2005_06_0049</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13403,7 +13374,6 @@
           <t>NODE_S2005_06_0054</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13454,8 +13424,6 @@
           <t>NODE_S2005_06_0052</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13721,8 +13689,6 @@
           <t>NODE_S2005_06_0055</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13909,8 +13875,6 @@
           <t>NODE_S2005_06_0063</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13961,8 +13925,6 @@
           <t>NODE_S2005_06_0063</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14060,7 +14022,6 @@
           <t>NODE_S2005_06_0069</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14111,8 +14072,6 @@
           <t>NODE_S2005_06_0066</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14163,8 +14122,6 @@
           <t>NODE_S2005_06_0066</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14267,7 +14224,6 @@
           <t>NODE_S2005_06_0072</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14323,8 +14279,6 @@
           <t>NODE_S2005_06_0070</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14380,7 +14334,6 @@
           <t>NODE_S2005_06_0075</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14478,8 +14431,6 @@
           <t>NODE_S2005_06_0073</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14530,8 +14481,6 @@
           <t>NODE_S2005_06_0073</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14640,8 +14589,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -14771,7 +14718,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -27849,7 +27795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28029,6 +27975,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>1 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Sparta Praha</t>
         </is>
       </c>
     </row>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -14589,6 +14589,8 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
+    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -14718,6 +14720,7 @@
         </is>
       </c>
     </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -4661,7 +4661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6832,6 +6832,613 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0243</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0244</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0245</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0246</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00304</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0247</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0248</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0249</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00307</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0250</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00308</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0251</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00309</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0252</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00310</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>11</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0253</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00311</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0254</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00312</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>13</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0255</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00313</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6843,7 +7450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7842,6 +8449,973 @@
       <c r="V18" t="inlineStr">
         <is>
           <t>SER_S2005_06_0026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HC Slavkovice</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0256</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00314</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0257</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00315</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0258</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00316</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Reinpo</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0259</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00317</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0260</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00318</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0261</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00319</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0262</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00320</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Čebín</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0263</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00321</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0264</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00322</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HC Gremis</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0265</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00323</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0266</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00324</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0267</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00325</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sokol Lipník</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0268</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00326</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sokol Pokojovice</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0269</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00327</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0270</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00328</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TJ Náměšť</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0271</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00329</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sokol Moravské Budějovice</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0272</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00330</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0273</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00331</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TJ Vladislav</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0274</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00332</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sokol Želetava</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0275</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00333</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>9</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TJ Mohelno</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0276</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00334</t>
         </is>
       </c>
     </row>
@@ -9627,7 +11201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10281,6 +11855,298 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0084</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HC Lipina Markvartovice</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0084</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0277</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00335</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HC Hať</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0084</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0278</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00336</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TJ Sokol Těškovice</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0084</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0279</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00337</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0084</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0280</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00338</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SK HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0084</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0281</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00339</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HC Bijci Opava</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0084</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0282</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00340</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10518,7 +12384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N93"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14746,6 +16612,208 @@
       <c r="A93" t="inlineStr">
         <is>
           <t>II.liga: Západ/Střed/Východ + 8F/QF/SF/finále.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0079</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Středočeský – Okres Kladno</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Jihočeský – Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>REG_JHC</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0049</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0082</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Pardubický – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0066</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0083</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Vysočina – Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0070</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0084</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Severomoravský – Opava</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>REG_SVM</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0077</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -17881,7 +19949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J184"/>
+  <dimension ref="A1:J259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -25677,6 +27745,2406 @@
       <c r="J184" t="inlineStr">
         <is>
           <t>Krnov</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0208</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>HC Benátky nad Jizerou B</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>HC Benátky nad Jizerou B</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0209</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0210</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0211</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SK Velc Žilina</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SK Velc Žilina</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0212</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Ford VM Kladno</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ford VM Kladno</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0213</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou B</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou B</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0214</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0215</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Slavoj V.Popovice B</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Slavoj V.Popovice B</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0216</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Sokol Votice</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Sokol Votice</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0217</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Sokol Mezno</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Sokol Mezno</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0218</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>HC Jesenice B</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>HC Jesenice B</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0219</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0220</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Sokol Popovice</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Sokol Popovice</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0221</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0222</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0223</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>TJ Felbabka B</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>TJ Felbabka B</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0224</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0225</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0226</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0227</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0228</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0229</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0230</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0231</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0232</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0233</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0234</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0235</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Větřní</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Větřní</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0236</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Praktik Český Krumlov</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Praktik Český Krumlov</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0237</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0238</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SHK Hluboká</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SHK Hluboká</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0239</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Jeremys České Budějovice</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Jeremys České Budějovice</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0240</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Hluboká nad Vltavou Knights B</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Hluboká nad Vltavou Knights B</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0241</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0242</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0243</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0244</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0245</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0246</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0247</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0248</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0249</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0250</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0251</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0252</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0253</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0254</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0255</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0256</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>HC Slavkovice</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>HC Slavkovice</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0257</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0258</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0259</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Reinpo</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Reinpo</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0260</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0261</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0262</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0263</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Čebín</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Čebín</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0264</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0265</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>HC Gremis</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>HC Gremis</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0266</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0267</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0268</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Sokol Lipník</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Sokol Lipník</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0269</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sokol Pokojovice</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Sokol Pokojovice</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0270</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0271</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>TJ Náměšť</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>TJ Náměšť</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0272</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Sokol Moravské Budějovice</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Sokol Moravské Budějovice</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0273</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0274</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>TJ Vladislav</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>TJ Vladislav</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0275</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Sokol Želetava</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Sokol Želetava</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0276</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>TJ Mohelno</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>TJ Mohelno</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0277</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>HC Lipina Markvartovice</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>HC Lipina Markvartovice</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0278</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>HC Hať</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>HC Hať</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0279</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>TJ Sokol Těškovice</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>TJ Sokol Těškovice</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0280</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0281</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>SK HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SK HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0282</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>HC Bijci Opava</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>HC Bijci Opava</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>
@@ -34258,7 +38726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -35955,6 +40423,73 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0079</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HC Benátky nad Jizerou B</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0079</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0208</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00266</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35966,7 +40501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -37948,6 +42483,829 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0209</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00267</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0210</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00268</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SK Velc Žilina</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0211</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00269</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ford VM Kladno</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0212</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00270</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou B</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0213</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0214</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00272</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Slavoj V.Popovice B</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0215</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00273</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sokol Votice</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0216</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00274</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sokol Mezno</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0217</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00275</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HC Jesenice B</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0218</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00276</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0219</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00277</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sokol Popovice</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0220</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00278</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0221</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00279</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0222</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00280</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TJ Felbabka B</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0223</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00281</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0224</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00282</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0225</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00283</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Okres Kladno</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0080</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0226</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00284</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37959,7 +43317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -39375,6 +44733,748 @@
       <c r="V24" t="inlineStr">
         <is>
           <t>SER_S2005_06_0007</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0227</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00285</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0228</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00286</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0229</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00287</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0230</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00288</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0231</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0232</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00290</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0233</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0234</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Větřní</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0235</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00293</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Praktik Český Krumlov</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0236</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00294</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0237</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SHK Hluboká</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0238</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jeremys České Budějovice</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0239</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Hluboká nad Vltavou Knights B</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0240</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0241</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Jindřichův Hradec</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0081</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2005_06_0242</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2005_06_00300</t>
         </is>
       </c>
     </row>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -39,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +85,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,6 +114,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -16455,8 +16466,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -16586,7 +16595,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -32472,7 +32480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -32529,7 +32537,7 @@
           <t>CLUB_S2005_06_0007</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -32549,7 +32557,7 @@
           <t>CLUB_S2005_06_0020</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -32569,7 +32577,7 @@
           <t>CLUB_S2005_06_0028</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -32589,7 +32597,7 @@
           <t>CLUB_S2005_06_0030</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -32609,7 +32617,7 @@
           <t>CLUB_S2005_06_0058</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -32629,7 +32637,7 @@
           <t>CLUB_S2005_06_0062</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -32649,7 +32657,7 @@
           <t>CLUB_S2005_06_0069</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -32669,7 +32677,7 @@
           <t>CLUB_S2005_06_0118</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -32689,7 +32697,7 @@
           <t>CLUB_S2005_06_0145</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -32709,7 +32717,7 @@
           <t>CLUB_S2005_06_0157</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -32729,7 +32737,7 @@
           <t>CLUB_S2005_06_0168</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -32749,7 +32757,7 @@
           <t>CLUB_S2005_06_0173</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'SB Světlá nad Sázavou' → 'Světlá nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -32769,7 +32777,7 @@
           <t>CLUB_S2005_06_0196</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -32789,11 +32797,63 @@
           <t>CLUB_S2005_06_0198</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'HLC Bulldogs Brno' → 'Bulldogs Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor · NODE_S2005_06_0079</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC Benátky nad Jizerou B), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>30_Jihomoravský-Zlín L40 finále · NODE_S2005_06_0076</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HK Slovan Rosice ,HK Kroměříž VTJ B ,HC Žraloci Vyškov ukončena činnost), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F15"/>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +116,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12169,7 +12172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12379,6 +12382,40 @@
         </is>
       </c>
       <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0079</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC Benátky nad Jizerou B), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NODE_S2005_06_0076</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HK Slovan Rosice ,HK Kroměříž VTJ B ,HC Žraloci Vyškov ukončena činnost), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -32817,7 +32854,7 @@
           <t>Praha – Pražský přebor · NODE_S2005_06_0079</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC Benátky nad Jizerou B), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -32843,7 +32880,7 @@
           <t>30_Jihomoravský-Zlín L40 finále · NODE_S2005_06_0076</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (HK Slovan Rosice ,HK Kroměříž VTJ B ,HC Žraloci Vyškov ukončena činnost), chybí výsledek / odveta  [torzo-audit]</t>
         </is>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -14112,7 +14112,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L40 základní část</t>
+          <t>Praha, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L40 finálová skupina</t>
+          <t>Praha, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L40 skupina o 5.-9.místo</t>
+          <t>Praha, 4. úroveň, skupina o 5.-9.místo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 finále</t>
+          <t>Jihočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Liberecký-Ústecký L40</t>
+          <t>Liberecký-Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Liberecký-Ústecký L40 základní část</t>
+          <t>Liberecký-Ústecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Liberecký-Ústecký L40 Finále Ústecký kraj</t>
+          <t>Liberecký-Ústecký, 4. úroveň, Finále Ústecký kraj</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Západočeský krajský přebor</t>
+          <t>Plzeňský, 4. úroveň Západočeský krajský přebor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina A</t>
+          <t>Plzeňský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina B</t>
+          <t>Plzeňský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 finálová skupina</t>
+          <t>Plzeňský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -15580,7 +15580,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina o 7.-12.místo</t>
+          <t>Plzeňský, 4. úroveň, skupina o 7.-12.místo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40 základní část</t>
+          <t>Karlovarský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 základní část</t>
+          <t>Hradecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina o 5.-9.místo</t>
+          <t>Hradecký, 4. úroveň, skupina o 5.-9.místo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 základní část</t>
+          <t>Pardubický, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina o 5.-11.místo</t>
+          <t>Pardubický, 4. úroveň, skupina o 5.-11.místo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 finále</t>
+          <t>Pardubický, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Vysočina L40 základní část</t>
+          <t>Vysočina, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Vysočina L40 finále</t>
+          <t>Vysočina, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Zlín L40</t>
+          <t>Jihomoravský-Zlín, 4. úroveň</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -16280,7 +16280,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Zlín L40 Jihomoravský kraj</t>
+          <t>Jihomoravský-Zlín, 4. úroveň Jihomoravský kraj</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Zlín L40 finále</t>
+          <t>Jihomoravský-Zlín, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Zlín L40 finále</t>
+          <t>Jihomoravský-Zlín, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 Severomoravský krajský přebor</t>
+          <t>Severomoravský, 4. úroveň Severomoravský krajský přebor</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -16503,6 +16503,8 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
+    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -16535,7 +16537,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -16632,6 +16634,7 @@
         </is>
       </c>
     </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>

--- a/data/S2005_06_FINAL.xlsx
+++ b/data/S2005_06_FINAL.xlsx
@@ -3892,7 +3892,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -16503,8 +16503,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
-    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -16634,7 +16632,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
@@ -30499,7 +30496,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -30582,7 +30579,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -30660,7 +30657,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -30738,7 +30735,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -30816,7 +30813,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -30894,7 +30891,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -30972,7 +30969,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -31050,7 +31047,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -31128,7 +31125,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -31206,7 +31203,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -31284,7 +31281,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -31362,7 +31359,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -31445,7 +31442,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -31528,7 +31525,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -33828,7 +33825,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -33906,7 +33903,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -33984,7 +33981,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -34062,7 +34059,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -34177,7 +34174,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -34255,7 +34252,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -34333,7 +34330,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -34411,7 +34408,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -35509,7 +35506,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -35587,7 +35584,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -35665,7 +35662,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -35743,7 +35740,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -37390,7 +37387,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -37468,7 +37465,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -37546,7 +37543,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -39114,7 +39111,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -39192,7 +39189,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -39270,7 +39267,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -39348,7 +39345,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -39426,7 +39423,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -39504,7 +39501,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -39582,7 +39579,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -39660,7 +39657,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -39738,7 +39735,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -47206,7 +47203,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -47284,7 +47281,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -47362,7 +47359,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -47440,7 +47437,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -47518,7 +47515,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -47596,7 +47593,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
